--- a/Vergleich_Ergebnisse_Vorlage.xlsx
+++ b/Vergleich_Ergebnisse_Vorlage.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\01-Arbeit\06-FENES\09-P2X3\FENES_P2X\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C91D1ED3-3F25-4338-9B8C-86C626FB1646}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBB708E8-1D0C-487F-A380-AEB094DF7D1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="23520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-30828" yWindow="-2400" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ergebnisse" sheetId="5" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="796" uniqueCount="376">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="854" uniqueCount="398">
   <si>
     <t>PEM Elektrolyse</t>
   </si>
@@ -1166,6 +1166,72 @@
   </si>
   <si>
     <t>P</t>
+  </si>
+  <si>
+    <t>Methanisierung</t>
+  </si>
+  <si>
+    <t>annuity_mg</t>
+  </si>
+  <si>
+    <t>result_mg_flowsum_ch4out</t>
+  </si>
+  <si>
+    <t>result_mg_flowsum_h2in</t>
+  </si>
+  <si>
+    <t>result_mg_flowsum_co2in</t>
+  </si>
+  <si>
+    <t>result_mg_flowsum_elin</t>
+  </si>
+  <si>
+    <t>calc_gesamtinvest_mg</t>
+  </si>
+  <si>
+    <t>calc_opex_fix_mg</t>
+  </si>
+  <si>
+    <t>calc_annuity_mg</t>
+  </si>
+  <si>
+    <t>calc_verzinstinvest_mg</t>
+  </si>
+  <si>
+    <t>calc_cost_mg</t>
+  </si>
+  <si>
+    <t>MG</t>
+  </si>
+  <si>
+    <t>Levelized Cost of Methane</t>
+  </si>
+  <si>
+    <t>calc_lcof_mg</t>
+  </si>
+  <si>
+    <t>Gesamtkosten pro t Methan</t>
+  </si>
+  <si>
+    <t>calc_cost_ch4</t>
+  </si>
+  <si>
+    <t>Methane Verkauf</t>
+  </si>
+  <si>
+    <t>Methaneverkauf</t>
+  </si>
+  <si>
+    <t>Einnahmen aus Methaneverkauf</t>
+  </si>
+  <si>
+    <t>result_ch4verkauf_flowsum</t>
+  </si>
+  <si>
+    <t>calc_einnahmen_ch4verkauf</t>
+  </si>
+  <si>
+    <t>CH4</t>
   </si>
 </sst>
 </file>
@@ -1267,7 +1333,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1339,25 +1405,13 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1381,29 +1435,44 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1685,7 +1754,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83AB2E79-6F94-41B5-A552-C40EC4890194}">
-  <dimension ref="A1:F218"/>
+  <dimension ref="A1:F234"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.5546875" style="3" customWidth="1"/>
@@ -1718,10 +1787,10 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="35" t="s">
+      <c r="A2" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="45" t="s">
+      <c r="B2" s="41" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="18" t="s">
@@ -1738,8 +1807,8 @@
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="36"/>
-      <c r="B3" s="43"/>
+      <c r="A3" s="49"/>
+      <c r="B3" s="39"/>
       <c r="C3" s="18" t="s">
         <v>351</v>
       </c>
@@ -1754,8 +1823,8 @@
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="36"/>
-      <c r="B4" s="43"/>
+      <c r="A4" s="49"/>
+      <c r="B4" s="39"/>
       <c r="C4" s="18" t="s">
         <v>351</v>
       </c>
@@ -1770,8 +1839,8 @@
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="36"/>
-      <c r="B5" s="43"/>
+      <c r="A5" s="49"/>
+      <c r="B5" s="39"/>
       <c r="C5" s="18" t="s">
         <v>351</v>
       </c>
@@ -1786,8 +1855,8 @@
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="36"/>
-      <c r="B6" s="43"/>
+      <c r="A6" s="49"/>
+      <c r="B6" s="39"/>
       <c r="C6" s="18" t="s">
         <v>351</v>
       </c>
@@ -1802,8 +1871,8 @@
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" s="36"/>
-      <c r="B7" s="43"/>
+      <c r="A7" s="49"/>
+      <c r="B7" s="39"/>
       <c r="C7" s="18" t="s">
         <v>351</v>
       </c>
@@ -1818,8 +1887,8 @@
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="36"/>
-      <c r="B8" s="43"/>
+      <c r="A8" s="49"/>
+      <c r="B8" s="39"/>
       <c r="C8" s="18" t="s">
         <v>351</v>
       </c>
@@ -1834,8 +1903,8 @@
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" s="36"/>
-      <c r="B9" s="43"/>
+      <c r="A9" s="49"/>
+      <c r="B9" s="39"/>
       <c r="C9" s="18" t="s">
         <v>351</v>
       </c>
@@ -1850,8 +1919,8 @@
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="36"/>
-      <c r="B10" s="43"/>
+      <c r="A10" s="49"/>
+      <c r="B10" s="39"/>
       <c r="C10" s="18" t="s">
         <v>351</v>
       </c>
@@ -1866,13 +1935,13 @@
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="36"/>
-      <c r="B11" s="44"/>
+      <c r="A11" s="49"/>
+      <c r="B11" s="40"/>
       <c r="C11" s="18"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="36"/>
-      <c r="B12" s="42" t="s">
+      <c r="A12" s="49"/>
+      <c r="B12" s="38" t="s">
         <v>151</v>
       </c>
       <c r="C12" s="19" t="s">
@@ -1889,8 +1958,8 @@
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13" s="36"/>
-      <c r="B13" s="43"/>
+      <c r="A13" s="49"/>
+      <c r="B13" s="39"/>
       <c r="C13" s="18" t="s">
         <v>352</v>
       </c>
@@ -1905,8 +1974,8 @@
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14" s="36"/>
-      <c r="B14" s="43"/>
+      <c r="A14" s="49"/>
+      <c r="B14" s="39"/>
       <c r="C14" s="18" t="s">
         <v>352</v>
       </c>
@@ -1921,8 +1990,8 @@
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A15" s="36"/>
-      <c r="B15" s="43"/>
+      <c r="A15" s="49"/>
+      <c r="B15" s="39"/>
       <c r="C15" s="18" t="s">
         <v>352</v>
       </c>
@@ -1937,8 +2006,8 @@
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A16" s="36"/>
-      <c r="B16" s="43"/>
+      <c r="A16" s="49"/>
+      <c r="B16" s="39"/>
       <c r="C16" s="18" t="s">
         <v>352</v>
       </c>
@@ -1953,8 +2022,8 @@
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="36"/>
-      <c r="B17" s="43"/>
+      <c r="A17" s="49"/>
+      <c r="B17" s="39"/>
       <c r="C17" s="18" t="s">
         <v>352</v>
       </c>
@@ -1969,8 +2038,8 @@
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="36"/>
-      <c r="B18" s="43"/>
+      <c r="A18" s="49"/>
+      <c r="B18" s="39"/>
       <c r="C18" s="18" t="s">
         <v>352</v>
       </c>
@@ -1985,8 +2054,8 @@
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" s="36"/>
-      <c r="B19" s="43"/>
+      <c r="A19" s="49"/>
+      <c r="B19" s="39"/>
       <c r="C19" s="18" t="s">
         <v>352</v>
       </c>
@@ -2001,8 +2070,8 @@
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20" s="36"/>
-      <c r="B20" s="43"/>
+      <c r="A20" s="49"/>
+      <c r="B20" s="39"/>
       <c r="C20" s="18" t="s">
         <v>352</v>
       </c>
@@ -2017,8 +2086,8 @@
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21" s="36"/>
-      <c r="B21" s="43"/>
+      <c r="A21" s="49"/>
+      <c r="B21" s="39"/>
       <c r="C21" s="18" t="s">
         <v>352</v>
       </c>
@@ -2033,13 +2102,13 @@
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22" s="36"/>
-      <c r="B22" s="44"/>
+      <c r="A22" s="49"/>
+      <c r="B22" s="40"/>
       <c r="C22" s="18"/>
     </row>
     <row r="23" spans="1:6" s="11" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="36"/>
-      <c r="B23" s="46" t="s">
+      <c r="A23" s="49"/>
+      <c r="B23" s="42" t="s">
         <v>256</v>
       </c>
       <c r="C23" s="20" t="s">
@@ -2056,8 +2125,8 @@
       </c>
     </row>
     <row r="24" spans="1:6" s="11" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="36"/>
-      <c r="B24" s="47"/>
+      <c r="A24" s="49"/>
+      <c r="B24" s="43"/>
       <c r="C24" s="21" t="s">
         <v>353</v>
       </c>
@@ -2072,8 +2141,8 @@
       </c>
     </row>
     <row r="25" spans="1:6" s="11" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="36"/>
-      <c r="B25" s="47"/>
+      <c r="A25" s="49"/>
+      <c r="B25" s="43"/>
       <c r="C25" s="21" t="s">
         <v>353</v>
       </c>
@@ -2088,8 +2157,8 @@
       </c>
     </row>
     <row r="26" spans="1:6" s="11" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="36"/>
-      <c r="B26" s="47"/>
+      <c r="A26" s="49"/>
+      <c r="B26" s="43"/>
       <c r="C26" s="21" t="s">
         <v>353</v>
       </c>
@@ -2104,8 +2173,8 @@
       </c>
     </row>
     <row r="27" spans="1:6" s="11" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="36"/>
-      <c r="B27" s="47"/>
+      <c r="A27" s="49"/>
+      <c r="B27" s="43"/>
       <c r="C27" s="21" t="s">
         <v>353</v>
       </c>
@@ -2120,8 +2189,8 @@
       </c>
     </row>
     <row r="28" spans="1:6" s="11" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="36"/>
-      <c r="B28" s="47"/>
+      <c r="A28" s="49"/>
+      <c r="B28" s="43"/>
       <c r="C28" s="21" t="s">
         <v>353</v>
       </c>
@@ -2136,8 +2205,8 @@
       </c>
     </row>
     <row r="29" spans="1:6" s="11" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="36"/>
-      <c r="B29" s="47"/>
+      <c r="A29" s="49"/>
+      <c r="B29" s="43"/>
       <c r="C29" s="21" t="s">
         <v>353</v>
       </c>
@@ -2152,8 +2221,8 @@
       </c>
     </row>
     <row r="30" spans="1:6" s="11" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="36"/>
-      <c r="B30" s="47"/>
+      <c r="A30" s="49"/>
+      <c r="B30" s="43"/>
       <c r="C30" s="21" t="s">
         <v>353</v>
       </c>
@@ -2168,8 +2237,8 @@
       </c>
     </row>
     <row r="31" spans="1:6" s="11" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="36"/>
-      <c r="B31" s="47"/>
+      <c r="A31" s="49"/>
+      <c r="B31" s="43"/>
       <c r="C31" s="21" t="s">
         <v>353</v>
       </c>
@@ -2184,8 +2253,8 @@
       </c>
     </row>
     <row r="32" spans="1:6" s="11" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="36"/>
-      <c r="B32" s="47"/>
+      <c r="A32" s="49"/>
+      <c r="B32" s="43"/>
       <c r="C32" s="21" t="s">
         <v>353</v>
       </c>
@@ -2200,16 +2269,16 @@
       </c>
     </row>
     <row r="33" spans="1:6" s="11" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="36"/>
-      <c r="B33" s="48"/>
+      <c r="A33" s="49"/>
+      <c r="B33" s="44"/>
       <c r="C33" s="22"/>
       <c r="D33" s="13"/>
       <c r="E33" s="13"/>
       <c r="F33" s="13"/>
     </row>
     <row r="34" spans="1:6" s="11" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="36"/>
-      <c r="B34" s="54" t="s">
+      <c r="A34" s="49"/>
+      <c r="B34" s="35" t="s">
         <v>257</v>
       </c>
       <c r="C34" s="23" t="s">
@@ -2226,8 +2295,8 @@
       </c>
     </row>
     <row r="35" spans="1:6" s="11" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="36"/>
-      <c r="B35" s="55"/>
+      <c r="A35" s="49"/>
+      <c r="B35" s="36"/>
       <c r="C35" s="24" t="s">
         <v>354</v>
       </c>
@@ -2242,8 +2311,8 @@
       </c>
     </row>
     <row r="36" spans="1:6" s="11" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="36"/>
-      <c r="B36" s="55"/>
+      <c r="A36" s="49"/>
+      <c r="B36" s="36"/>
       <c r="C36" s="24" t="s">
         <v>354</v>
       </c>
@@ -2258,8 +2327,8 @@
       </c>
     </row>
     <row r="37" spans="1:6" s="11" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="36"/>
-      <c r="B37" s="55"/>
+      <c r="A37" s="49"/>
+      <c r="B37" s="36"/>
       <c r="C37" s="24" t="s">
         <v>354</v>
       </c>
@@ -2274,8 +2343,8 @@
       </c>
     </row>
     <row r="38" spans="1:6" s="11" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="36"/>
-      <c r="B38" s="55"/>
+      <c r="A38" s="49"/>
+      <c r="B38" s="36"/>
       <c r="C38" s="24" t="s">
         <v>354</v>
       </c>
@@ -2290,8 +2359,8 @@
       </c>
     </row>
     <row r="39" spans="1:6" s="11" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="36"/>
-      <c r="B39" s="55"/>
+      <c r="A39" s="49"/>
+      <c r="B39" s="36"/>
       <c r="C39" s="24" t="s">
         <v>354</v>
       </c>
@@ -2306,8 +2375,8 @@
       </c>
     </row>
     <row r="40" spans="1:6" s="11" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="36"/>
-      <c r="B40" s="55"/>
+      <c r="A40" s="49"/>
+      <c r="B40" s="36"/>
       <c r="C40" s="24" t="s">
         <v>354</v>
       </c>
@@ -2322,8 +2391,8 @@
       </c>
     </row>
     <row r="41" spans="1:6" s="11" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="36"/>
-      <c r="B41" s="55"/>
+      <c r="A41" s="49"/>
+      <c r="B41" s="36"/>
       <c r="C41" s="24" t="s">
         <v>354</v>
       </c>
@@ -2338,8 +2407,8 @@
       </c>
     </row>
     <row r="42" spans="1:6" s="11" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="36"/>
-      <c r="B42" s="55"/>
+      <c r="A42" s="49"/>
+      <c r="B42" s="36"/>
       <c r="C42" s="24" t="s">
         <v>354</v>
       </c>
@@ -2354,16 +2423,16 @@
       </c>
     </row>
     <row r="43" spans="1:6" s="11" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="36"/>
-      <c r="B43" s="56"/>
+      <c r="A43" s="49"/>
+      <c r="B43" s="37"/>
       <c r="C43" s="25"/>
       <c r="D43" s="13"/>
       <c r="E43" s="13"/>
       <c r="F43" s="13"/>
     </row>
     <row r="44" spans="1:6" s="11" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="36"/>
-      <c r="B44" s="46" t="s">
+      <c r="A44" s="49"/>
+      <c r="B44" s="42" t="s">
         <v>285</v>
       </c>
       <c r="C44" s="20" t="s">
@@ -2380,8 +2449,8 @@
       </c>
     </row>
     <row r="45" spans="1:6" s="11" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="36"/>
-      <c r="B45" s="47"/>
+      <c r="A45" s="49"/>
+      <c r="B45" s="43"/>
       <c r="C45" s="21" t="s">
         <v>355</v>
       </c>
@@ -2396,8 +2465,8 @@
       </c>
     </row>
     <row r="46" spans="1:6" s="11" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="36"/>
-      <c r="B46" s="47"/>
+      <c r="A46" s="49"/>
+      <c r="B46" s="43"/>
       <c r="C46" s="21" t="s">
         <v>355</v>
       </c>
@@ -2412,8 +2481,8 @@
       </c>
     </row>
     <row r="47" spans="1:6" s="11" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="36"/>
-      <c r="B47" s="47"/>
+      <c r="A47" s="49"/>
+      <c r="B47" s="43"/>
       <c r="C47" s="21" t="s">
         <v>355</v>
       </c>
@@ -2428,8 +2497,8 @@
       </c>
     </row>
     <row r="48" spans="1:6" s="11" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="36"/>
-      <c r="B48" s="47"/>
+      <c r="A48" s="49"/>
+      <c r="B48" s="43"/>
       <c r="C48" s="21" t="s">
         <v>355</v>
       </c>
@@ -2444,8 +2513,8 @@
       </c>
     </row>
     <row r="49" spans="1:6" s="11" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="36"/>
-      <c r="B49" s="47"/>
+      <c r="A49" s="49"/>
+      <c r="B49" s="43"/>
       <c r="C49" s="21" t="s">
         <v>355</v>
       </c>
@@ -2460,8 +2529,8 @@
       </c>
     </row>
     <row r="50" spans="1:6" s="11" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="36"/>
-      <c r="B50" s="47"/>
+      <c r="A50" s="49"/>
+      <c r="B50" s="43"/>
       <c r="C50" s="21" t="s">
         <v>355</v>
       </c>
@@ -2476,8 +2545,8 @@
       </c>
     </row>
     <row r="51" spans="1:6" s="11" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="36"/>
-      <c r="B51" s="47"/>
+      <c r="A51" s="49"/>
+      <c r="B51" s="43"/>
       <c r="C51" s="21" t="s">
         <v>355</v>
       </c>
@@ -2492,8 +2561,8 @@
       </c>
     </row>
     <row r="52" spans="1:6" s="11" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="36"/>
-      <c r="B52" s="47"/>
+      <c r="A52" s="49"/>
+      <c r="B52" s="43"/>
       <c r="C52" s="21" t="s">
         <v>355</v>
       </c>
@@ -2508,8 +2577,8 @@
       </c>
     </row>
     <row r="53" spans="1:6" s="11" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="36"/>
-      <c r="B53" s="47"/>
+      <c r="A53" s="49"/>
+      <c r="B53" s="43"/>
       <c r="C53" s="21" t="s">
         <v>355</v>
       </c>
@@ -2524,8 +2593,8 @@
       </c>
     </row>
     <row r="54" spans="1:6" s="11" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="36"/>
-      <c r="B54" s="47"/>
+      <c r="A54" s="49"/>
+      <c r="B54" s="43"/>
       <c r="C54" s="21" t="s">
         <v>355</v>
       </c>
@@ -2540,16 +2609,16 @@
       </c>
     </row>
     <row r="55" spans="1:6" s="11" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="36"/>
-      <c r="B55" s="48"/>
+      <c r="A55" s="49"/>
+      <c r="B55" s="44"/>
       <c r="C55" s="22"/>
       <c r="D55" s="13"/>
       <c r="E55" s="13"/>
       <c r="F55" s="13"/>
     </row>
     <row r="56" spans="1:6" s="11" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="36"/>
-      <c r="B56" s="38" t="s">
+      <c r="A56" s="49"/>
+      <c r="B56" s="45" t="s">
         <v>301</v>
       </c>
       <c r="C56" s="26" t="s">
@@ -2566,8 +2635,8 @@
       </c>
     </row>
     <row r="57" spans="1:6" s="11" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="36"/>
-      <c r="B57" s="39"/>
+      <c r="A57" s="49"/>
+      <c r="B57" s="46"/>
       <c r="C57" s="27" t="s">
         <v>356</v>
       </c>
@@ -2582,8 +2651,8 @@
       </c>
     </row>
     <row r="58" spans="1:6" s="11" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="36"/>
-      <c r="B58" s="39"/>
+      <c r="A58" s="49"/>
+      <c r="B58" s="46"/>
       <c r="C58" s="27" t="s">
         <v>356</v>
       </c>
@@ -2598,8 +2667,8 @@
       </c>
     </row>
     <row r="59" spans="1:6" s="11" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="36"/>
-      <c r="B59" s="39"/>
+      <c r="A59" s="49"/>
+      <c r="B59" s="46"/>
       <c r="C59" s="27" t="s">
         <v>356</v>
       </c>
@@ -2614,8 +2683,8 @@
       </c>
     </row>
     <row r="60" spans="1:6" s="11" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="36"/>
-      <c r="B60" s="39"/>
+      <c r="A60" s="49"/>
+      <c r="B60" s="46"/>
       <c r="C60" s="27" t="s">
         <v>356</v>
       </c>
@@ -2630,8 +2699,8 @@
       </c>
     </row>
     <row r="61" spans="1:6" s="11" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="36"/>
-      <c r="B61" s="39"/>
+      <c r="A61" s="49"/>
+      <c r="B61" s="46"/>
       <c r="C61" s="27" t="s">
         <v>356</v>
       </c>
@@ -2646,8 +2715,8 @@
       </c>
     </row>
     <row r="62" spans="1:6" s="11" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="36"/>
-      <c r="B62" s="39"/>
+      <c r="A62" s="49"/>
+      <c r="B62" s="46"/>
       <c r="C62" s="27" t="s">
         <v>356</v>
       </c>
@@ -2662,8 +2731,8 @@
       </c>
     </row>
     <row r="63" spans="1:6" s="11" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="36"/>
-      <c r="B63" s="39"/>
+      <c r="A63" s="49"/>
+      <c r="B63" s="46"/>
       <c r="C63" s="27" t="s">
         <v>356</v>
       </c>
@@ -2678,8 +2747,8 @@
       </c>
     </row>
     <row r="64" spans="1:6" s="11" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="36"/>
-      <c r="B64" s="39"/>
+      <c r="A64" s="49"/>
+      <c r="B64" s="46"/>
       <c r="C64" s="27" t="s">
         <v>356</v>
       </c>
@@ -2694,8 +2763,8 @@
       </c>
     </row>
     <row r="65" spans="1:6" s="11" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="36"/>
-      <c r="B65" s="39"/>
+      <c r="A65" s="49"/>
+      <c r="B65" s="46"/>
       <c r="C65" s="27" t="s">
         <v>356</v>
       </c>
@@ -2710,8 +2779,8 @@
       </c>
     </row>
     <row r="66" spans="1:6" s="11" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="36"/>
-      <c r="B66" s="39"/>
+      <c r="A66" s="49"/>
+      <c r="B66" s="46"/>
       <c r="C66" s="27" t="s">
         <v>356</v>
       </c>
@@ -2726,8 +2795,8 @@
       </c>
     </row>
     <row r="67" spans="1:6" s="11" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="36"/>
-      <c r="B67" s="39"/>
+      <c r="A67" s="49"/>
+      <c r="B67" s="46"/>
       <c r="C67" s="27" t="s">
         <v>356</v>
       </c>
@@ -2742,16 +2811,16 @@
       </c>
     </row>
     <row r="68" spans="1:6" s="11" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="36"/>
-      <c r="B68" s="40"/>
+      <c r="A68" s="49"/>
+      <c r="B68" s="47"/>
       <c r="C68" s="28"/>
       <c r="D68" s="13"/>
       <c r="E68" s="13"/>
       <c r="F68" s="13"/>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A69" s="36"/>
-      <c r="B69" s="42" t="s">
+      <c r="A69" s="49"/>
+      <c r="B69" s="38" t="s">
         <v>186</v>
       </c>
       <c r="C69" s="18" t="s">
@@ -2768,8 +2837,8 @@
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A70" s="36"/>
-      <c r="B70" s="43"/>
+      <c r="A70" s="49"/>
+      <c r="B70" s="39"/>
       <c r="C70" s="18" t="s">
         <v>357</v>
       </c>
@@ -2784,8 +2853,8 @@
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A71" s="36"/>
-      <c r="B71" s="43"/>
+      <c r="A71" s="49"/>
+      <c r="B71" s="39"/>
       <c r="C71" s="18" t="s">
         <v>357</v>
       </c>
@@ -2800,8 +2869,8 @@
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A72" s="36"/>
-      <c r="B72" s="43"/>
+      <c r="A72" s="49"/>
+      <c r="B72" s="39"/>
       <c r="C72" s="18" t="s">
         <v>357</v>
       </c>
@@ -2816,8 +2885,8 @@
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A73" s="36"/>
-      <c r="B73" s="43"/>
+      <c r="A73" s="49"/>
+      <c r="B73" s="39"/>
       <c r="C73" s="18" t="s">
         <v>357</v>
       </c>
@@ -2832,8 +2901,8 @@
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A74" s="36"/>
-      <c r="B74" s="43"/>
+      <c r="A74" s="49"/>
+      <c r="B74" s="39"/>
       <c r="C74" s="18" t="s">
         <v>357</v>
       </c>
@@ -2848,8 +2917,8 @@
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A75" s="36"/>
-      <c r="B75" s="43"/>
+      <c r="A75" s="49"/>
+      <c r="B75" s="39"/>
       <c r="C75" s="18" t="s">
         <v>357</v>
       </c>
@@ -2864,8 +2933,8 @@
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A76" s="36"/>
-      <c r="B76" s="43"/>
+      <c r="A76" s="49"/>
+      <c r="B76" s="39"/>
       <c r="C76" s="18" t="s">
         <v>357</v>
       </c>
@@ -2880,8 +2949,8 @@
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A77" s="36"/>
-      <c r="B77" s="43"/>
+      <c r="A77" s="49"/>
+      <c r="B77" s="39"/>
       <c r="C77" s="18" t="s">
         <v>357</v>
       </c>
@@ -2896,2146 +2965,2392 @@
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A78" s="36"/>
-      <c r="B78" s="44"/>
+      <c r="A78" s="49"/>
+      <c r="B78" s="40"/>
       <c r="C78" s="29"/>
       <c r="D78" s="7"/>
       <c r="E78" s="7"/>
       <c r="F78" s="7"/>
     </row>
     <row r="79" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A79" s="36"/>
-      <c r="B79" s="38" t="s">
+      <c r="A79" s="49"/>
+      <c r="B79" s="45" t="s">
         <v>150</v>
       </c>
-      <c r="C79" s="27" t="s">
+      <c r="C79" s="26" t="s">
         <v>358</v>
       </c>
-      <c r="D79" s="3" t="s">
+      <c r="D79" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="E79" s="3" t="s">
+      <c r="E79" s="6" t="s">
         <v>165</v>
       </c>
-      <c r="F79" s="3" t="s">
+      <c r="F79" s="6" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A80" s="36"/>
-      <c r="B80" s="52"/>
+      <c r="A80" s="49"/>
+      <c r="B80" s="46"/>
       <c r="C80" s="27" t="s">
         <v>358</v>
       </c>
-      <c r="D80" s="3" t="s">
+      <c r="D80" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="E80" s="3" t="s">
+      <c r="E80" s="9" t="s">
         <v>166</v>
       </c>
-      <c r="F80" s="3" t="s">
+      <c r="F80" s="9" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A81" s="36"/>
-      <c r="B81" s="52"/>
+      <c r="A81" s="49"/>
+      <c r="B81" s="46"/>
       <c r="C81" s="27" t="s">
         <v>358</v>
       </c>
-      <c r="D81" s="3" t="s">
+      <c r="D81" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="E81" s="3" t="s">
+      <c r="E81" s="9" t="s">
         <v>167</v>
       </c>
-      <c r="F81" s="3" t="s">
+      <c r="F81" s="9" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A82" s="36"/>
-      <c r="B82" s="52"/>
+      <c r="A82" s="49"/>
+      <c r="B82" s="46"/>
       <c r="C82" s="27" t="s">
         <v>358</v>
       </c>
-      <c r="D82" s="3" t="s">
+      <c r="D82" s="9" t="s">
         <v>187</v>
       </c>
-      <c r="E82" s="3" t="s">
+      <c r="E82" s="9" t="s">
         <v>202</v>
       </c>
-      <c r="F82" s="3" t="s">
+      <c r="F82" s="9" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A83" s="36"/>
-      <c r="B83" s="52"/>
+      <c r="A83" s="49"/>
+      <c r="B83" s="46"/>
       <c r="C83" s="27" t="s">
         <v>358</v>
       </c>
-      <c r="D83" s="3" t="s">
+      <c r="D83" s="9" t="s">
         <v>173</v>
       </c>
-      <c r="E83" s="3" t="s">
+      <c r="E83" s="9" t="s">
         <v>201</v>
       </c>
-      <c r="F83" s="3" t="s">
+      <c r="F83" s="9" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A84" s="36"/>
-      <c r="B84" s="52"/>
+      <c r="A84" s="49"/>
+      <c r="B84" s="46"/>
       <c r="C84" s="27" t="s">
         <v>358</v>
       </c>
-      <c r="D84" s="3" t="s">
+      <c r="D84" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="E84" s="3" t="s">
+      <c r="E84" s="9" t="s">
         <v>168</v>
       </c>
-      <c r="F84" s="3" t="s">
+      <c r="F84" s="9" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A85" s="36"/>
-      <c r="B85" s="52"/>
+      <c r="A85" s="49"/>
+      <c r="B85" s="46"/>
       <c r="C85" s="27" t="s">
         <v>358</v>
       </c>
-      <c r="D85" s="3" t="s">
+      <c r="D85" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="E85" s="3" t="s">
+      <c r="E85" s="9" t="s">
         <v>169</v>
       </c>
-      <c r="F85" s="3" t="s">
+      <c r="F85" s="9" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A86" s="36"/>
-      <c r="B86" s="52"/>
+      <c r="A86" s="49"/>
+      <c r="B86" s="46"/>
       <c r="C86" s="27" t="s">
         <v>358</v>
       </c>
-      <c r="D86" s="3" t="s">
+      <c r="D86" s="9" t="s">
         <v>118</v>
       </c>
-      <c r="E86" s="3" t="s">
+      <c r="E86" s="9" t="s">
         <v>170</v>
       </c>
-      <c r="F86" s="3" t="s">
+      <c r="F86" s="9" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A87" s="36"/>
-      <c r="B87" s="52"/>
+      <c r="A87" s="49"/>
+      <c r="B87" s="46"/>
       <c r="C87" s="27" t="s">
         <v>358</v>
       </c>
-      <c r="D87" s="3" t="s">
+      <c r="D87" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="E87" s="3" t="s">
+      <c r="E87" s="9" t="s">
         <v>171</v>
       </c>
-      <c r="F87" s="3" t="s">
+      <c r="F87" s="9" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A88" s="36"/>
-      <c r="B88" s="52"/>
+      <c r="A88" s="49"/>
+      <c r="B88" s="46"/>
       <c r="C88" s="27" t="s">
         <v>358</v>
       </c>
-      <c r="D88" s="3" t="s">
+      <c r="D88" s="9" t="s">
         <v>110</v>
       </c>
-      <c r="E88" s="3" t="s">
+      <c r="E88" s="9" t="s">
         <v>172</v>
       </c>
-      <c r="F88" s="3" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="89" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A89" s="37"/>
-      <c r="B89" s="41"/>
-      <c r="C89" s="27"/>
-    </row>
-    <row r="90" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A90" s="35" t="s">
+      <c r="F88" s="9" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A89" s="49"/>
+      <c r="B89" s="47"/>
+      <c r="C89" s="28"/>
+      <c r="D89" s="7"/>
+      <c r="E89" s="7"/>
+      <c r="F89" s="7"/>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A90" s="49"/>
+      <c r="B90" s="43" t="s">
+        <v>376</v>
+      </c>
+      <c r="C90" s="27" t="s">
+        <v>387</v>
+      </c>
+      <c r="D90" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="E90" s="14" t="s">
+        <v>377</v>
+      </c>
+      <c r="F90" s="14" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A91" s="49"/>
+      <c r="B91" s="54"/>
+      <c r="C91" s="27" t="s">
+        <v>387</v>
+      </c>
+      <c r="D91" s="11" t="s">
+        <v>160</v>
+      </c>
+      <c r="E91" s="11" t="s">
+        <v>378</v>
+      </c>
+      <c r="F91" s="11" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A92" s="49"/>
+      <c r="B92" s="54"/>
+      <c r="C92" s="27" t="s">
+        <v>387</v>
+      </c>
+      <c r="D92" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="E92" s="11" t="s">
+        <v>379</v>
+      </c>
+      <c r="F92" s="12" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A93" s="49"/>
+      <c r="B93" s="54"/>
+      <c r="C93" s="27" t="s">
+        <v>387</v>
+      </c>
+      <c r="D93" s="11" t="s">
+        <v>161</v>
+      </c>
+      <c r="E93" s="11" t="s">
+        <v>380</v>
+      </c>
+      <c r="F93" s="11" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A94" s="49"/>
+      <c r="B94" s="54"/>
+      <c r="C94" s="27" t="s">
+        <v>387</v>
+      </c>
+      <c r="D94" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="E94" s="11" t="s">
+        <v>381</v>
+      </c>
+      <c r="F94" s="11" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A95" s="49"/>
+      <c r="B95" s="54"/>
+      <c r="C95" s="27" t="s">
+        <v>387</v>
+      </c>
+      <c r="D95" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="E95" s="11" t="s">
+        <v>382</v>
+      </c>
+      <c r="F95" s="11" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A96" s="49"/>
+      <c r="B96" s="54"/>
+      <c r="C96" s="27" t="s">
+        <v>387</v>
+      </c>
+      <c r="D96" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="E96" s="11" t="s">
+        <v>383</v>
+      </c>
+      <c r="F96" s="11" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A97" s="49"/>
+      <c r="B97" s="54"/>
+      <c r="C97" s="27" t="s">
+        <v>387</v>
+      </c>
+      <c r="D97" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="E97" s="11" t="s">
+        <v>384</v>
+      </c>
+      <c r="F97" s="11" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A98" s="49"/>
+      <c r="B98" s="54"/>
+      <c r="C98" s="27" t="s">
+        <v>387</v>
+      </c>
+      <c r="D98" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="E98" s="11" t="s">
+        <v>385</v>
+      </c>
+      <c r="F98" s="11" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A99" s="49"/>
+      <c r="B99" s="54"/>
+      <c r="C99" s="27" t="s">
+        <v>387</v>
+      </c>
+      <c r="D99" s="11" t="s">
+        <v>110</v>
+      </c>
+      <c r="E99" s="11" t="s">
+        <v>386</v>
+      </c>
+      <c r="F99" s="11" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A100" s="50"/>
+      <c r="B100" s="56"/>
+      <c r="C100" s="27"/>
+    </row>
+    <row r="101" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A101" s="48" t="s">
         <v>13</v>
       </c>
-      <c r="B90" s="53" t="s">
+      <c r="B101" s="53" t="s">
         <v>3</v>
       </c>
-      <c r="C90" s="30" t="s">
+      <c r="C101" s="30" t="s">
         <v>359</v>
       </c>
-      <c r="D90" s="4" t="s">
+      <c r="D101" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="E90" s="4" t="s">
+      <c r="E101" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="F90" s="4" t="s">
+      <c r="F101" s="4" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A91" s="36"/>
-      <c r="B91" s="39"/>
-      <c r="C91" s="27" t="s">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A102" s="49"/>
+      <c r="B102" s="46"/>
+      <c r="C102" s="27" t="s">
         <v>359</v>
       </c>
-      <c r="D91" s="3" t="s">
+      <c r="D102" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="E91" s="3" t="s">
+      <c r="E102" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="F91" s="3" t="s">
+      <c r="F102" s="3" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A92" s="36"/>
-      <c r="B92" s="39"/>
-      <c r="C92" s="27" t="s">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A103" s="49"/>
+      <c r="B103" s="46"/>
+      <c r="C103" s="27" t="s">
         <v>359</v>
       </c>
-      <c r="D92" s="3" t="s">
+      <c r="D103" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="E92" s="3" t="s">
+      <c r="E103" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="F92" s="3" t="s">
+      <c r="F103" s="3" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A93" s="36"/>
-      <c r="B93" s="39"/>
-      <c r="C93" s="27" t="s">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A104" s="49"/>
+      <c r="B104" s="46"/>
+      <c r="C104" s="27" t="s">
         <v>359</v>
       </c>
-      <c r="D93" s="3" t="s">
+      <c r="D104" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="E93" s="3" t="s">
+      <c r="E104" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="F93" s="3" t="s">
+      <c r="F104" s="3" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A94" s="36"/>
-      <c r="B94" s="39"/>
-      <c r="C94" s="27" t="s">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A105" s="49"/>
+      <c r="B105" s="46"/>
+      <c r="C105" s="27" t="s">
         <v>359</v>
       </c>
-      <c r="D94" s="3" t="s">
+      <c r="D105" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="E94" s="3" t="s">
+      <c r="E105" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="F94" s="3" t="s">
+      <c r="F105" s="3" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A95" s="36"/>
-      <c r="B95" s="39"/>
-      <c r="C95" s="27" t="s">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A106" s="49"/>
+      <c r="B106" s="46"/>
+      <c r="C106" s="27" t="s">
         <v>359</v>
       </c>
-      <c r="D95" s="3" t="s">
+      <c r="D106" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="E95" s="3" t="s">
+      <c r="E106" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="F95" s="3" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A96" s="36"/>
-      <c r="B96" s="39"/>
-      <c r="C96" s="27" t="s">
+      <c r="F106" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A107" s="49"/>
+      <c r="B107" s="46"/>
+      <c r="C107" s="27" t="s">
         <v>359</v>
       </c>
-      <c r="D96" s="3" t="s">
+      <c r="D107" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="E96" s="3" t="s">
+      <c r="E107" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="F96" s="3" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A97" s="36"/>
-      <c r="B97" s="39"/>
-      <c r="C97" s="27" t="s">
+      <c r="F107" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A108" s="49"/>
+      <c r="B108" s="46"/>
+      <c r="C108" s="27" t="s">
         <v>359</v>
       </c>
-      <c r="D97" s="3" t="s">
+      <c r="D108" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="E97" s="3" t="s">
+      <c r="E108" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="F97" s="3" t="s">
+      <c r="F108" s="3" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A98" s="36"/>
-      <c r="B98" s="39"/>
-      <c r="C98" s="27" t="s">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A109" s="49"/>
+      <c r="B109" s="46"/>
+      <c r="C109" s="27" t="s">
         <v>359</v>
       </c>
-      <c r="D98" s="3" t="s">
+      <c r="D109" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="E98" s="3" t="s">
+      <c r="E109" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="F98" s="3" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A99" s="36"/>
-      <c r="B99" s="40"/>
-      <c r="C99" s="28"/>
-      <c r="D99" s="7"/>
-      <c r="E99" s="7"/>
-      <c r="F99" s="7"/>
-    </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A100" s="36"/>
-      <c r="B100" s="38" t="s">
+      <c r="F109" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A110" s="49"/>
+      <c r="B110" s="47"/>
+      <c r="C110" s="28"/>
+      <c r="D110" s="7"/>
+      <c r="E110" s="7"/>
+      <c r="F110" s="7"/>
+    </row>
+    <row r="111" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A111" s="49"/>
+      <c r="B111" s="45" t="s">
         <v>218</v>
       </c>
-      <c r="C100" s="27" t="s">
+      <c r="C111" s="27" t="s">
         <v>360</v>
-      </c>
-      <c r="D100" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="E100" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="F100" s="3" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A101" s="36"/>
-      <c r="B101" s="52"/>
-      <c r="C101" s="27" t="s">
-        <v>360</v>
-      </c>
-      <c r="D101" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="E101" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="F101" s="3" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A102" s="36"/>
-      <c r="B102" s="52"/>
-      <c r="C102" s="27" t="s">
-        <v>360</v>
-      </c>
-      <c r="D102" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="E102" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="F102" s="3" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A103" s="36"/>
-      <c r="B103" s="52"/>
-      <c r="C103" s="27" t="s">
-        <v>360</v>
-      </c>
-      <c r="D103" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="E103" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="F103" s="3" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A104" s="36"/>
-      <c r="B104" s="52"/>
-      <c r="C104" s="27" t="s">
-        <v>360</v>
-      </c>
-      <c r="D104" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="E104" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="F104" s="3" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A105" s="36"/>
-      <c r="B105" s="52"/>
-      <c r="C105" s="27" t="s">
-        <v>360</v>
-      </c>
-      <c r="D105" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="E105" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="F105" s="3" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A106" s="36"/>
-      <c r="B106" s="52"/>
-      <c r="C106" s="27" t="s">
-        <v>360</v>
-      </c>
-      <c r="D106" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="E106" s="3" t="s">
-        <v>225</v>
-      </c>
-      <c r="F106" s="3" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A107" s="36"/>
-      <c r="B107" s="52"/>
-      <c r="C107" s="27" t="s">
-        <v>360</v>
-      </c>
-      <c r="D107" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="E107" s="3" t="s">
-        <v>226</v>
-      </c>
-      <c r="F107" s="3" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A108" s="36"/>
-      <c r="B108" s="52"/>
-      <c r="C108" s="27" t="s">
-        <v>360</v>
-      </c>
-      <c r="D108" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="E108" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="F108" s="3" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A109" s="36"/>
-      <c r="B109" s="40"/>
-      <c r="C109" s="27"/>
-    </row>
-    <row r="110" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A110" s="36"/>
-      <c r="B110" s="38" t="s">
-        <v>6</v>
-      </c>
-      <c r="C110" s="26" t="s">
-        <v>361</v>
-      </c>
-      <c r="D110" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E110" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="F110" s="6" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A111" s="36"/>
-      <c r="B111" s="39"/>
-      <c r="C111" s="27" t="s">
-        <v>361</v>
       </c>
       <c r="D111" s="3" t="s">
         <v>36</v>
       </c>
       <c r="E111" s="3" t="s">
-        <v>25</v>
+        <v>219</v>
       </c>
       <c r="F111" s="3" t="s">
-        <v>28</v>
+        <v>232</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A112" s="36"/>
-      <c r="B112" s="39"/>
+      <c r="A112" s="49"/>
+      <c r="B112" s="51"/>
       <c r="C112" s="27" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="D112" s="3" t="s">
         <v>34</v>
       </c>
       <c r="E112" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="F112" s="3" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A113" s="49"/>
+      <c r="B113" s="51"/>
+      <c r="C113" s="27" t="s">
+        <v>360</v>
+      </c>
+      <c r="D113" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="E113" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="F113" s="3" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A114" s="49"/>
+      <c r="B114" s="51"/>
+      <c r="C114" s="27" t="s">
+        <v>360</v>
+      </c>
+      <c r="D114" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E114" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="F114" s="3" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A115" s="49"/>
+      <c r="B115" s="51"/>
+      <c r="C115" s="27" t="s">
+        <v>360</v>
+      </c>
+      <c r="D115" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="E115" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="F115" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A116" s="49"/>
+      <c r="B116" s="51"/>
+      <c r="C116" s="27" t="s">
+        <v>360</v>
+      </c>
+      <c r="D116" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="E116" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="F116" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A117" s="49"/>
+      <c r="B117" s="51"/>
+      <c r="C117" s="27" t="s">
+        <v>360</v>
+      </c>
+      <c r="D117" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="E117" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="F117" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A118" s="49"/>
+      <c r="B118" s="51"/>
+      <c r="C118" s="27" t="s">
+        <v>360</v>
+      </c>
+      <c r="D118" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="E118" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="F118" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A119" s="49"/>
+      <c r="B119" s="51"/>
+      <c r="C119" s="27" t="s">
+        <v>360</v>
+      </c>
+      <c r="D119" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="E119" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="F119" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="120" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A120" s="49"/>
+      <c r="B120" s="47"/>
+      <c r="C120" s="27"/>
+    </row>
+    <row r="121" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A121" s="49"/>
+      <c r="B121" s="45" t="s">
+        <v>6</v>
+      </c>
+      <c r="C121" s="26" t="s">
+        <v>361</v>
+      </c>
+      <c r="D121" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="E121" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="F121" s="6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A122" s="49"/>
+      <c r="B122" s="46"/>
+      <c r="C122" s="27" t="s">
+        <v>361</v>
+      </c>
+      <c r="D122" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E122" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F122" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="123" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A123" s="49"/>
+      <c r="B123" s="46"/>
+      <c r="C123" s="27" t="s">
+        <v>361</v>
+      </c>
+      <c r="D123" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E123" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="F112" s="3" t="s">
+      <c r="F123" s="3" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A113" s="36"/>
-      <c r="B113" s="39"/>
-      <c r="C113" s="27" t="s">
+    <row r="124" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A124" s="49"/>
+      <c r="B124" s="46"/>
+      <c r="C124" s="27" t="s">
         <v>361</v>
       </c>
-      <c r="D113" s="3" t="s">
+      <c r="D124" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="E113" s="3" t="s">
+      <c r="E124" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="F113" s="3" t="s">
+      <c r="F124" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A114" s="36"/>
-      <c r="B114" s="39"/>
-      <c r="C114" s="27" t="s">
+    <row r="125" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A125" s="49"/>
+      <c r="B125" s="46"/>
+      <c r="C125" s="27" t="s">
         <v>361</v>
       </c>
-      <c r="D114" s="3" t="s">
+      <c r="D125" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="E114" s="3" t="s">
+      <c r="E125" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="F114" s="3" t="s">
+      <c r="F125" s="3" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A115" s="36"/>
-      <c r="B115" s="39"/>
-      <c r="C115" s="27" t="s">
+    <row r="126" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A126" s="49"/>
+      <c r="B126" s="46"/>
+      <c r="C126" s="27" t="s">
         <v>361</v>
       </c>
-      <c r="D115" s="3" t="s">
+      <c r="D126" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="E115" s="3" t="s">
+      <c r="E126" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="F115" s="3" t="s">
+      <c r="F126" s="3" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A116" s="36"/>
-      <c r="B116" s="39"/>
-      <c r="C116" s="27" t="s">
+    <row r="127" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A127" s="49"/>
+      <c r="B127" s="46"/>
+      <c r="C127" s="27" t="s">
         <v>361</v>
       </c>
-      <c r="D116" s="3" t="s">
+      <c r="D127" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="E116" s="3" t="s">
+      <c r="E127" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="F116" s="3" t="s">
+      <c r="F127" s="3" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A117" s="36"/>
-      <c r="B117" s="39"/>
-      <c r="C117" s="27" t="s">
+    <row r="128" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A128" s="49"/>
+      <c r="B128" s="46"/>
+      <c r="C128" s="27" t="s">
         <v>361</v>
       </c>
-      <c r="D117" s="3" t="s">
+      <c r="D128" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="E117" s="3" t="s">
+      <c r="E128" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="F117" s="3" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A118" s="36"/>
-      <c r="B118" s="39"/>
-      <c r="C118" s="27" t="s">
+      <c r="F128" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A129" s="49"/>
+      <c r="B129" s="46"/>
+      <c r="C129" s="27" t="s">
         <v>361</v>
       </c>
-      <c r="D118" s="3" t="s">
+      <c r="D129" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="E118" s="3" t="s">
+      <c r="E129" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="F118" s="3" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A119" s="36"/>
-      <c r="B119" s="39"/>
-      <c r="C119" s="27" t="s">
+      <c r="F129" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A130" s="49"/>
+      <c r="B130" s="46"/>
+      <c r="C130" s="27" t="s">
         <v>361</v>
       </c>
-      <c r="D119" s="3" t="s">
+      <c r="D130" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="E119" s="3" t="s">
+      <c r="E130" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="F119" s="3" t="s">
+      <c r="F130" s="3" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A120" s="36"/>
-      <c r="B120" s="39"/>
-      <c r="C120" s="27" t="s">
+    <row r="131" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A131" s="49"/>
+      <c r="B131" s="46"/>
+      <c r="C131" s="27" t="s">
         <v>361</v>
       </c>
-      <c r="D120" s="3" t="s">
+      <c r="D131" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="E120" s="3" t="s">
+      <c r="E131" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="F120" s="3" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="121" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A121" s="37"/>
-      <c r="B121" s="41"/>
-      <c r="C121" s="31"/>
-      <c r="D121" s="8"/>
-      <c r="E121" s="8"/>
-      <c r="F121" s="8"/>
-    </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A122" s="35" t="s">
+      <c r="F131" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A132" s="50"/>
+      <c r="B132" s="52"/>
+      <c r="C132" s="31"/>
+      <c r="D132" s="8"/>
+      <c r="E132" s="8"/>
+      <c r="F132" s="8"/>
+    </row>
+    <row r="133" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A133" s="48" t="s">
         <v>14</v>
       </c>
-      <c r="B122" s="45" t="s">
+      <c r="B133" s="41" t="s">
         <v>15</v>
       </c>
-      <c r="C122" s="17" t="s">
+      <c r="C133" s="17" t="s">
         <v>362</v>
       </c>
-      <c r="D122" s="4" t="s">
+      <c r="D133" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="E122" s="4" t="s">
+      <c r="E133" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="F122" s="4" t="s">
+      <c r="F133" s="4" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A123" s="36"/>
-      <c r="B123" s="43"/>
-      <c r="C123" s="18" t="s">
+    <row r="134" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A134" s="49"/>
+      <c r="B134" s="39"/>
+      <c r="C134" s="18" t="s">
         <v>362</v>
       </c>
-      <c r="D123" s="9" t="s">
+      <c r="D134" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="E123" s="9" t="s">
+      <c r="E134" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="F123" s="9" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A124" s="36"/>
-      <c r="B124" s="44"/>
-      <c r="C124" s="29"/>
-      <c r="D124" s="7"/>
-      <c r="E124" s="7"/>
-      <c r="F124" s="7"/>
-    </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A125" s="36"/>
-      <c r="B125" s="42" t="s">
+      <c r="F134" s="9" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="135" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A135" s="49"/>
+      <c r="B135" s="40"/>
+      <c r="C135" s="29"/>
+      <c r="D135" s="7"/>
+      <c r="E135" s="7"/>
+      <c r="F135" s="7"/>
+    </row>
+    <row r="136" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A136" s="49"/>
+      <c r="B136" s="38" t="s">
         <v>271</v>
       </c>
-      <c r="C125" s="18" t="s">
+      <c r="C136" s="18" t="s">
         <v>363</v>
       </c>
-      <c r="D125" s="9" t="s">
+      <c r="D136" s="9" t="s">
         <v>268</v>
       </c>
-      <c r="E125" s="9" t="s">
+      <c r="E136" s="9" t="s">
         <v>269</v>
       </c>
-      <c r="F125" s="9" t="s">
+      <c r="F136" s="9" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A126" s="36"/>
-      <c r="B126" s="43"/>
-      <c r="C126" s="18" t="s">
+    <row r="137" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A137" s="49"/>
+      <c r="B137" s="39"/>
+      <c r="C137" s="18" t="s">
         <v>363</v>
       </c>
-      <c r="D126" s="9" t="s">
+      <c r="D137" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="E126" s="9" t="s">
+      <c r="E137" s="9" t="s">
         <v>270</v>
       </c>
-      <c r="F126" s="9" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A127" s="36"/>
-      <c r="B127" s="44"/>
-      <c r="C127" s="29"/>
-      <c r="D127" s="7"/>
-      <c r="E127" s="7"/>
-      <c r="F127" s="7"/>
-    </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A128" s="36"/>
-      <c r="B128" s="42" t="s">
+      <c r="F137" s="9" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A138" s="49"/>
+      <c r="B138" s="40"/>
+      <c r="C138" s="29"/>
+      <c r="D138" s="7"/>
+      <c r="E138" s="7"/>
+      <c r="F138" s="7"/>
+    </row>
+    <row r="139" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A139" s="49"/>
+      <c r="B139" s="38" t="s">
         <v>316</v>
       </c>
-      <c r="C128" s="19" t="s">
+      <c r="C139" s="19" t="s">
         <v>364</v>
       </c>
-      <c r="D128" s="6" t="s">
+      <c r="D139" s="6" t="s">
         <v>317</v>
       </c>
-      <c r="E128" s="6" t="s">
+      <c r="E139" s="6" t="s">
         <v>318</v>
       </c>
-      <c r="F128" s="6" t="s">
+      <c r="F139" s="6" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A129" s="36"/>
-      <c r="B129" s="43"/>
-      <c r="C129" s="18" t="s">
+    <row r="140" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A140" s="49"/>
+      <c r="B140" s="39"/>
+      <c r="C140" s="18" t="s">
         <v>364</v>
       </c>
-      <c r="D129" s="3" t="s">
+      <c r="D140" s="3" t="s">
         <v>319</v>
       </c>
-      <c r="E129" s="3" t="s">
+      <c r="E140" s="3" t="s">
         <v>320</v>
       </c>
-      <c r="F129" s="3" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A130" s="36"/>
-      <c r="B130" s="44"/>
-      <c r="C130" s="29"/>
-      <c r="D130" s="7"/>
-      <c r="E130" s="7"/>
-      <c r="F130" s="7"/>
-    </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A131" s="36"/>
-      <c r="B131" s="42" t="s">
+      <c r="F140" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="141" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A141" s="49"/>
+      <c r="B141" s="40"/>
+      <c r="C141" s="29"/>
+      <c r="D141" s="7"/>
+      <c r="E141" s="7"/>
+      <c r="F141" s="7"/>
+    </row>
+    <row r="142" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A142" s="49"/>
+      <c r="B142" s="38" t="s">
         <v>321</v>
       </c>
-      <c r="C131" s="18" t="s">
+      <c r="C142" s="18" t="s">
         <v>365</v>
       </c>
-      <c r="D131" s="3" t="s">
+      <c r="D142" s="3" t="s">
         <v>322</v>
       </c>
-      <c r="E131" s="3" t="s">
+      <c r="E142" s="3" t="s">
         <v>323</v>
       </c>
-      <c r="F131" s="3" t="s">
+      <c r="F142" s="3" t="s">
         <v>324</v>
       </c>
     </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A132" s="36"/>
-      <c r="B132" s="51"/>
-      <c r="C132" s="32" t="s">
+    <row r="143" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A143" s="49"/>
+      <c r="B143" s="55"/>
+      <c r="C143" s="32" t="s">
         <v>365</v>
       </c>
-      <c r="D132" s="3" t="s">
+      <c r="D143" s="3" t="s">
         <v>325</v>
       </c>
-      <c r="E132" s="3" t="s">
+      <c r="E143" s="3" t="s">
         <v>326</v>
       </c>
-      <c r="F132" s="3" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A133" s="36"/>
-      <c r="B133" s="44"/>
-      <c r="C133" s="18"/>
-    </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A134" s="36"/>
-      <c r="B134" s="38" t="s">
+      <c r="F143" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="144" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A144" s="49"/>
+      <c r="B144" s="40"/>
+      <c r="C144" s="18"/>
+    </row>
+    <row r="145" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A145" s="49"/>
+      <c r="B145" s="45" t="s">
         <v>4</v>
       </c>
-      <c r="C134" s="26" t="s">
+      <c r="C145" s="26" t="s">
         <v>4</v>
       </c>
-      <c r="D134" s="6" t="s">
+      <c r="D145" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="E134" s="6" t="s">
+      <c r="E145" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="F134" s="6" t="s">
+      <c r="F145" s="6" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A135" s="36"/>
-      <c r="B135" s="39"/>
-      <c r="C135" s="27" t="s">
+    <row r="146" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A146" s="49"/>
+      <c r="B146" s="46"/>
+      <c r="C146" s="27" t="s">
         <v>4</v>
       </c>
-      <c r="D135" s="3" t="s">
+      <c r="D146" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="E135" s="3" t="s">
+      <c r="E146" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="F135" s="3" t="s">
+      <c r="F146" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A136" s="36"/>
-      <c r="B136" s="39"/>
-      <c r="C136" s="27" t="s">
+    <row r="147" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A147" s="49"/>
+      <c r="B147" s="46"/>
+      <c r="C147" s="27" t="s">
         <v>4</v>
       </c>
-      <c r="D136" s="3" t="s">
+      <c r="D147" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="E136" s="3" t="s">
+      <c r="E147" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="F136" s="3" t="s">
+      <c r="F147" s="3" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A137" s="36"/>
-      <c r="B137" s="39"/>
-      <c r="C137" s="27" t="s">
+    <row r="148" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A148" s="49"/>
+      <c r="B148" s="46"/>
+      <c r="C148" s="27" t="s">
         <v>4</v>
       </c>
-      <c r="D137" s="3" t="s">
+      <c r="D148" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="E137" s="3" t="s">
+      <c r="E148" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="F137" s="3" t="s">
+      <c r="F148" s="3" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A138" s="36"/>
-      <c r="B138" s="39"/>
-      <c r="C138" s="27" t="s">
+    <row r="149" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A149" s="49"/>
+      <c r="B149" s="46"/>
+      <c r="C149" s="27" t="s">
         <v>4</v>
       </c>
-      <c r="D138" s="3" t="s">
+      <c r="D149" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="E138" s="3" t="s">
+      <c r="E149" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="F138" s="3" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A139" s="36"/>
-      <c r="B139" s="39"/>
-      <c r="C139" s="27" t="s">
+      <c r="F149" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="150" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A150" s="49"/>
+      <c r="B150" s="46"/>
+      <c r="C150" s="27" t="s">
         <v>4</v>
       </c>
-      <c r="D139" s="3" t="s">
+      <c r="D150" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="E139" s="3" t="s">
+      <c r="E150" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="F139" s="3" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A140" s="36"/>
-      <c r="B140" s="39"/>
-      <c r="C140" s="27" t="s">
+      <c r="F150" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="151" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A151" s="49"/>
+      <c r="B151" s="46"/>
+      <c r="C151" s="27" t="s">
         <v>4</v>
       </c>
-      <c r="D140" s="3" t="s">
+      <c r="D151" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="E140" s="3" t="s">
+      <c r="E151" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="F140" s="3" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A141" s="36"/>
-      <c r="B141" s="39"/>
-      <c r="C141" s="27" t="s">
+      <c r="F151" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="152" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A152" s="49"/>
+      <c r="B152" s="46"/>
+      <c r="C152" s="27" t="s">
         <v>4</v>
       </c>
-      <c r="D141" s="3" t="s">
+      <c r="D152" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="E141" s="3" t="s">
+      <c r="E152" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="F141" s="3" t="s">
+      <c r="F152" s="3" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A142" s="36"/>
-      <c r="B142" s="39"/>
-      <c r="C142" s="27" t="s">
+    <row r="153" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A153" s="49"/>
+      <c r="B153" s="46"/>
+      <c r="C153" s="27" t="s">
         <v>4</v>
       </c>
-      <c r="D142" s="3" t="s">
+      <c r="D153" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="E142" s="3" t="s">
+      <c r="E153" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="F142" s="3" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A143" s="36"/>
-      <c r="B143" s="40"/>
-      <c r="C143" s="27"/>
-    </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A144" s="36"/>
-      <c r="B144" s="38" t="s">
+      <c r="F153" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="154" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A154" s="49"/>
+      <c r="B154" s="47"/>
+      <c r="C154" s="27"/>
+    </row>
+    <row r="155" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A155" s="49"/>
+      <c r="B155" s="45" t="s">
         <v>5</v>
       </c>
-      <c r="C144" s="26" t="s">
+      <c r="C155" s="26" t="s">
         <v>366</v>
       </c>
-      <c r="D144" s="6" t="s">
+      <c r="D155" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="E144" s="6" t="s">
+      <c r="E155" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="F144" s="6" t="s">
+      <c r="F155" s="6" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A145" s="36"/>
-      <c r="B145" s="39"/>
-      <c r="C145" s="27" t="s">
+    <row r="156" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A156" s="49"/>
+      <c r="B156" s="46"/>
+      <c r="C156" s="27" t="s">
         <v>366</v>
       </c>
-      <c r="D145" s="3" t="s">
+      <c r="D156" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="E145" s="3" t="s">
+      <c r="E156" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="F145" s="3" t="s">
+      <c r="F156" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="146" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A146" s="36"/>
-      <c r="B146" s="39"/>
-      <c r="C146" s="27" t="s">
+    <row r="157" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A157" s="49"/>
+      <c r="B157" s="46"/>
+      <c r="C157" s="27" t="s">
         <v>366</v>
       </c>
-      <c r="D146" s="3" t="s">
+      <c r="D157" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="E146" s="3" t="s">
+      <c r="E157" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="F146" s="3" t="s">
+      <c r="F157" s="3" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="147" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A147" s="36"/>
-      <c r="B147" s="39"/>
-      <c r="C147" s="27" t="s">
+    <row r="158" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A158" s="49"/>
+      <c r="B158" s="46"/>
+      <c r="C158" s="27" t="s">
         <v>366</v>
       </c>
-      <c r="D147" s="3" t="s">
+      <c r="D158" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="E147" s="3" t="s">
+      <c r="E158" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="F147" s="3" t="s">
+      <c r="F158" s="3" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="148" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A148" s="36"/>
-      <c r="B148" s="39"/>
-      <c r="C148" s="27" t="s">
+    <row r="159" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A159" s="49"/>
+      <c r="B159" s="46"/>
+      <c r="C159" s="27" t="s">
         <v>366</v>
       </c>
-      <c r="D148" s="3" t="s">
+      <c r="D159" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="E148" s="3" t="s">
+      <c r="E159" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="F148" s="3" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A149" s="36"/>
-      <c r="B149" s="39"/>
-      <c r="C149" s="27" t="s">
+      <c r="F159" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="160" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A160" s="49"/>
+      <c r="B160" s="46"/>
+      <c r="C160" s="27" t="s">
         <v>366</v>
       </c>
-      <c r="D149" s="3" t="s">
+      <c r="D160" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="E149" s="3" t="s">
+      <c r="E160" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="F149" s="3" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="150" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A150" s="36"/>
-      <c r="B150" s="39"/>
-      <c r="C150" s="27" t="s">
+      <c r="F160" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="161" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A161" s="49"/>
+      <c r="B161" s="46"/>
+      <c r="C161" s="27" t="s">
         <v>366</v>
       </c>
-      <c r="D150" s="3" t="s">
+      <c r="D161" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="E150" s="3" t="s">
+      <c r="E161" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="F150" s="3" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="151" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A151" s="36"/>
-      <c r="B151" s="39"/>
-      <c r="C151" s="27" t="s">
+      <c r="F161" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="162" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A162" s="49"/>
+      <c r="B162" s="46"/>
+      <c r="C162" s="27" t="s">
         <v>366</v>
       </c>
-      <c r="D151" s="3" t="s">
+      <c r="D162" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="E151" s="3" t="s">
+      <c r="E162" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="F151" s="3" t="s">
+      <c r="F162" s="3" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="152" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A152" s="36"/>
-      <c r="B152" s="39"/>
-      <c r="C152" s="27" t="s">
+    <row r="163" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A163" s="49"/>
+      <c r="B163" s="46"/>
+      <c r="C163" s="27" t="s">
         <v>366</v>
       </c>
-      <c r="D152" s="3" t="s">
+      <c r="D163" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="E152" s="3" t="s">
+      <c r="E163" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="F152" s="3" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="153" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A153" s="37"/>
-      <c r="B153" s="41"/>
-      <c r="C153" s="27"/>
-    </row>
-    <row r="154" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A154" s="35" t="s">
+      <c r="F163" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="164" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A164" s="50"/>
+      <c r="B164" s="52"/>
+      <c r="C164" s="27"/>
+    </row>
+    <row r="165" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A165" s="48" t="s">
         <v>16</v>
       </c>
-      <c r="B154" s="45" t="s">
+      <c r="B165" s="41" t="s">
         <v>15</v>
       </c>
-      <c r="C154" s="17" t="s">
+      <c r="C165" s="17" t="s">
         <v>362</v>
       </c>
-      <c r="D154" s="4" t="s">
+      <c r="D165" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="E154" s="4" t="s">
+      <c r="E165" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="F154" s="4" t="s">
+      <c r="F165" s="4" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="155" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A155" s="36"/>
-      <c r="B155" s="43"/>
-      <c r="C155" s="18" t="s">
+    <row r="166" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A166" s="49"/>
+      <c r="B166" s="39"/>
+      <c r="C166" s="18" t="s">
         <v>362</v>
       </c>
-      <c r="D155" s="3" t="s">
+      <c r="D166" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="E155" s="3" t="s">
+      <c r="E166" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="F155" s="3" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="156" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A156" s="36"/>
-      <c r="B156" s="43"/>
-      <c r="C156" s="18" t="s">
+      <c r="F166" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="167" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A167" s="49"/>
+      <c r="B167" s="39"/>
+      <c r="C167" s="18" t="s">
         <v>362</v>
       </c>
-      <c r="D156" s="3" t="s">
+      <c r="D167" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="E156" s="3" t="s">
+      <c r="E167" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="F156" s="3" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="157" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A157" s="36"/>
-      <c r="B157" s="44"/>
-      <c r="C157" s="29"/>
-      <c r="D157" s="7"/>
-      <c r="E157" s="7"/>
-      <c r="F157" s="7"/>
-    </row>
-    <row r="158" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A158" s="36"/>
-      <c r="B158" s="42" t="s">
+      <c r="F167" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="168" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A168" s="49"/>
+      <c r="B168" s="40"/>
+      <c r="C168" s="29"/>
+      <c r="D168" s="7"/>
+      <c r="E168" s="7"/>
+      <c r="F168" s="7"/>
+    </row>
+    <row r="169" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A169" s="49"/>
+      <c r="B169" s="38" t="s">
         <v>204</v>
       </c>
-      <c r="C158" s="18" t="s">
+      <c r="C169" s="18" t="s">
         <v>367</v>
       </c>
-      <c r="D158" s="3" t="s">
+      <c r="D169" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="E158" s="3" t="s">
+      <c r="E169" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="F158" s="3" t="s">
+      <c r="F169" s="3" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="159" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A159" s="36"/>
-      <c r="B159" s="43"/>
-      <c r="C159" s="18" t="s">
+    <row r="170" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A170" s="49"/>
+      <c r="B170" s="39"/>
+      <c r="C170" s="18" t="s">
         <v>367</v>
       </c>
-      <c r="D159" s="3" t="s">
+      <c r="D170" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="E159" s="3" t="s">
+      <c r="E170" s="3" t="s">
         <v>207</v>
       </c>
-      <c r="F159" s="3" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="160" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A160" s="36"/>
-      <c r="B160" s="43"/>
-      <c r="C160" s="18" t="s">
+      <c r="F170" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="171" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A171" s="49"/>
+      <c r="B171" s="39"/>
+      <c r="C171" s="18" t="s">
         <v>367</v>
       </c>
-      <c r="D160" s="3" t="s">
+      <c r="D171" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="E160" s="3" t="s">
+      <c r="E171" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="F160" s="3" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="161" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A161" s="36"/>
-      <c r="B161" s="44"/>
-      <c r="C161" s="18"/>
-    </row>
-    <row r="162" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A162" s="36"/>
-      <c r="B162" s="42" t="s">
+      <c r="F171" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="172" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A172" s="49"/>
+      <c r="B172" s="40"/>
+      <c r="C172" s="18"/>
+    </row>
+    <row r="173" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A173" s="49"/>
+      <c r="B173" s="38" t="s">
         <v>17</v>
       </c>
-      <c r="C162" s="19" t="s">
+      <c r="C173" s="19" t="s">
         <v>364</v>
       </c>
-      <c r="D162" s="6" t="s">
+      <c r="D173" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="E162" s="6" t="s">
+      <c r="E173" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="F162" s="6" t="s">
+      <c r="F173" s="6" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="163" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A163" s="36"/>
-      <c r="B163" s="43"/>
-      <c r="C163" s="18" t="s">
+    <row r="174" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A174" s="49"/>
+      <c r="B174" s="39"/>
+      <c r="C174" s="18" t="s">
         <v>364</v>
       </c>
-      <c r="D163" s="3" t="s">
+      <c r="D174" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="E163" s="3" t="s">
+      <c r="E174" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="F163" s="3" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="164" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A164" s="36"/>
-      <c r="B164" s="44"/>
-      <c r="C164" s="29"/>
-      <c r="D164" s="7"/>
-      <c r="E164" s="7"/>
-      <c r="F164" s="7"/>
-    </row>
-    <row r="165" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A165" s="36"/>
-      <c r="B165" s="42" t="s">
+      <c r="F174" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="175" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A175" s="49"/>
+      <c r="B175" s="40"/>
+      <c r="C175" s="29"/>
+      <c r="D175" s="7"/>
+      <c r="E175" s="7"/>
+      <c r="F175" s="7"/>
+    </row>
+    <row r="176" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A176" s="49"/>
+      <c r="B176" s="38" t="s">
         <v>175</v>
       </c>
-      <c r="C165" s="19" t="s">
+      <c r="C176" s="19" t="s">
         <v>368</v>
       </c>
-      <c r="D165" s="6" t="s">
+      <c r="D176" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="E165" s="6" t="s">
+      <c r="E176" s="6" t="s">
         <v>177</v>
       </c>
-      <c r="F165" s="6" t="s">
+      <c r="F176" s="6" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="166" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A166" s="36"/>
-      <c r="B166" s="43"/>
-      <c r="C166" s="18" t="s">
+    <row r="177" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A177" s="49"/>
+      <c r="B177" s="39"/>
+      <c r="C177" s="18" t="s">
         <v>368</v>
       </c>
-      <c r="D166" s="9" t="s">
+      <c r="D177" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="E166" s="9" t="s">
+      <c r="E177" s="9" t="s">
         <v>178</v>
       </c>
-      <c r="F166" s="9" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="167" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A167" s="36"/>
-      <c r="B167" s="44"/>
-      <c r="C167" s="29"/>
-      <c r="D167" s="7"/>
-      <c r="E167" s="7"/>
-      <c r="F167" s="7"/>
-    </row>
-    <row r="168" spans="1:6" s="11" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A168" s="36"/>
-      <c r="B168" s="46" t="s">
+      <c r="F177" s="9" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="178" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A178" s="49"/>
+      <c r="B178" s="40"/>
+      <c r="C178" s="29"/>
+      <c r="D178" s="7"/>
+      <c r="E178" s="7"/>
+      <c r="F178" s="7"/>
+    </row>
+    <row r="179" spans="1:6" s="11" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A179" s="49"/>
+      <c r="B179" s="42" t="s">
         <v>272</v>
       </c>
-      <c r="C168" s="21" t="s">
+      <c r="C179" s="21" t="s">
         <v>369</v>
       </c>
-      <c r="D168" s="14" t="s">
+      <c r="D179" s="14" t="s">
         <v>273</v>
       </c>
-      <c r="E168" s="14" t="s">
+      <c r="E179" s="14" t="s">
         <v>274</v>
       </c>
-      <c r="F168" s="14" t="s">
+      <c r="F179" s="14" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="169" spans="1:6" s="11" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A169" s="36"/>
-      <c r="B169" s="47"/>
-      <c r="C169" s="21" t="s">
+    <row r="180" spans="1:6" s="11" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A180" s="49"/>
+      <c r="B180" s="43"/>
+      <c r="C180" s="21" t="s">
         <v>369</v>
       </c>
-      <c r="D169" s="14" t="s">
+      <c r="D180" s="14" t="s">
         <v>275</v>
       </c>
-      <c r="E169" s="14" t="s">
+      <c r="E180" s="14" t="s">
         <v>276</v>
       </c>
-      <c r="F169" s="14" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="170" spans="1:6" s="11" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A170" s="36"/>
-      <c r="B170" s="48"/>
-      <c r="C170" s="22"/>
-      <c r="D170" s="13"/>
-      <c r="E170" s="13"/>
-      <c r="F170" s="13"/>
-    </row>
-    <row r="171" spans="1:6" s="11" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A171" s="36"/>
-      <c r="B171" s="46" t="s">
+      <c r="F180" s="14" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="181" spans="1:6" s="11" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A181" s="49"/>
+      <c r="B181" s="44"/>
+      <c r="C181" s="22"/>
+      <c r="D181" s="13"/>
+      <c r="E181" s="13"/>
+      <c r="F181" s="13"/>
+    </row>
+    <row r="182" spans="1:6" s="11" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A182" s="49"/>
+      <c r="B182" s="42" t="s">
         <v>327</v>
       </c>
-      <c r="C171" s="20" t="s">
+      <c r="C182" s="20" t="s">
         <v>370</v>
       </c>
-      <c r="D171" s="10" t="s">
+      <c r="D182" s="10" t="s">
         <v>328</v>
       </c>
-      <c r="E171" s="10" t="s">
+      <c r="E182" s="10" t="s">
         <v>329</v>
       </c>
-      <c r="F171" s="10" t="s">
+      <c r="F182" s="10" t="s">
         <v>292</v>
       </c>
     </row>
-    <row r="172" spans="1:6" s="11" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A172" s="36"/>
-      <c r="B172" s="47"/>
-      <c r="C172" s="21" t="s">
+    <row r="183" spans="1:6" s="11" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A183" s="49"/>
+      <c r="B183" s="43"/>
+      <c r="C183" s="21" t="s">
         <v>370</v>
       </c>
-      <c r="D172" s="11" t="s">
+      <c r="D183" s="11" t="s">
         <v>330</v>
       </c>
-      <c r="E172" s="11" t="s">
+      <c r="E183" s="11" t="s">
         <v>331</v>
       </c>
-      <c r="F172" s="11" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="173" spans="1:6" s="11" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A173" s="36"/>
-      <c r="B173" s="48"/>
-      <c r="C173" s="22"/>
-      <c r="D173" s="13"/>
-      <c r="E173" s="13"/>
-      <c r="F173" s="13"/>
-    </row>
-    <row r="174" spans="1:6" s="11" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A174" s="36"/>
-      <c r="B174" s="46" t="s">
+      <c r="F183" s="11" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="184" spans="1:6" s="11" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A184" s="49"/>
+      <c r="B184" s="44"/>
+      <c r="C184" s="22"/>
+      <c r="D184" s="13"/>
+      <c r="E184" s="13"/>
+      <c r="F184" s="13"/>
+    </row>
+    <row r="185" spans="1:6" s="11" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A185" s="49"/>
+      <c r="B185" s="42" t="s">
         <v>332</v>
       </c>
-      <c r="C174" s="21" t="s">
+      <c r="C185" s="20" t="s">
         <v>371</v>
       </c>
-      <c r="D174" s="11" t="s">
+      <c r="D185" s="10" t="s">
         <v>333</v>
       </c>
-      <c r="E174" s="11" t="s">
+      <c r="E185" s="10" t="s">
         <v>334</v>
       </c>
-      <c r="F174" s="11" t="s">
+      <c r="F185" s="10" t="s">
         <v>289</v>
       </c>
     </row>
-    <row r="175" spans="1:6" s="11" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A175" s="36"/>
-      <c r="B175" s="49"/>
-      <c r="C175" s="33" t="s">
+    <row r="186" spans="1:6" s="11" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A186" s="49"/>
+      <c r="B186" s="43"/>
+      <c r="C186" s="21" t="s">
         <v>371</v>
       </c>
-      <c r="D175" s="11" t="s">
+      <c r="D186" s="14" t="s">
         <v>335</v>
       </c>
-      <c r="E175" s="11" t="s">
+      <c r="E186" s="14" t="s">
         <v>336</v>
       </c>
-      <c r="F175" s="11" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="176" spans="1:6" s="11" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A176" s="37"/>
-      <c r="B176" s="50"/>
-      <c r="C176" s="34"/>
-      <c r="D176" s="16"/>
-      <c r="E176" s="16"/>
-      <c r="F176" s="16"/>
-    </row>
-    <row r="177" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A177" s="35" t="s">
+      <c r="F186" s="14" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="187" spans="1:6" s="11" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A187" s="49"/>
+      <c r="B187" s="44"/>
+      <c r="C187" s="22"/>
+      <c r="D187" s="13"/>
+      <c r="E187" s="13"/>
+      <c r="F187" s="13"/>
+    </row>
+    <row r="188" spans="1:6" s="11" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A188" s="49"/>
+      <c r="B188" s="43" t="s">
+        <v>392</v>
+      </c>
+      <c r="C188" s="33" t="s">
+        <v>397</v>
+      </c>
+      <c r="D188" s="11" t="s">
+        <v>393</v>
+      </c>
+      <c r="E188" s="11" t="s">
+        <v>395</v>
+      </c>
+      <c r="F188" s="11" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="189" spans="1:6" s="11" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A189" s="49"/>
+      <c r="B189" s="54"/>
+      <c r="C189" s="33" t="s">
+        <v>397</v>
+      </c>
+      <c r="D189" s="11" t="s">
+        <v>394</v>
+      </c>
+      <c r="E189" s="11" t="s">
+        <v>396</v>
+      </c>
+      <c r="F189" s="11" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="190" spans="1:6" s="11" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A190" s="50"/>
+      <c r="B190" s="57"/>
+      <c r="C190" s="34"/>
+      <c r="D190" s="16"/>
+      <c r="E190" s="16"/>
+      <c r="F190" s="16"/>
+    </row>
+    <row r="191" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A191" s="48" t="s">
         <v>86</v>
       </c>
-      <c r="B177" s="45" t="s">
+      <c r="B191" s="41" t="s">
         <v>7</v>
       </c>
-      <c r="C177" s="17" t="s">
+      <c r="C191" s="17" t="s">
         <v>372</v>
       </c>
-      <c r="D177" s="4" t="s">
+      <c r="D191" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="E177" s="4" t="s">
+      <c r="E191" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="F177" s="4" t="s">
+      <c r="F191" s="4" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="178" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A178" s="36"/>
-      <c r="B178" s="43"/>
-      <c r="C178" s="18" t="s">
+    <row r="192" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A192" s="49"/>
+      <c r="B192" s="39"/>
+      <c r="C192" s="18" t="s">
         <v>372</v>
       </c>
-      <c r="D178" s="3" t="s">
+      <c r="D192" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="E178" s="3" t="s">
+      <c r="E192" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="F178" s="3" t="s">
+      <c r="F192" s="3" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="179" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A179" s="36"/>
-      <c r="B179" s="44"/>
-      <c r="C179" s="29"/>
-      <c r="D179" s="7"/>
-      <c r="E179" s="7"/>
-      <c r="F179" s="7"/>
-    </row>
-    <row r="180" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A180" s="36"/>
-      <c r="B180" s="42" t="s">
+    <row r="193" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A193" s="49"/>
+      <c r="B193" s="40"/>
+      <c r="C193" s="29"/>
+      <c r="D193" s="7"/>
+      <c r="E193" s="7"/>
+      <c r="F193" s="7"/>
+    </row>
+    <row r="194" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A194" s="49"/>
+      <c r="B194" s="38" t="s">
         <v>106</v>
       </c>
-      <c r="C180" s="18" t="s">
+      <c r="C194" s="18" t="s">
         <v>372</v>
       </c>
-      <c r="D180" s="3" t="s">
+      <c r="D194" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="E180" s="3" t="s">
+      <c r="E194" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="F180" s="3" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="181" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A181" s="36"/>
-      <c r="B181" s="43"/>
-      <c r="C181" s="18" t="s">
+      <c r="F194" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="195" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A195" s="49"/>
+      <c r="B195" s="39"/>
+      <c r="C195" s="18" t="s">
         <v>372</v>
       </c>
-      <c r="D181" s="3" t="s">
+      <c r="D195" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="E181" s="3" t="s">
+      <c r="E195" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="F181" s="3" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="182" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A182" s="36"/>
-      <c r="B182" s="43"/>
-      <c r="C182" s="18" t="s">
+      <c r="F195" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="196" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A196" s="49"/>
+      <c r="B196" s="39"/>
+      <c r="C196" s="18" t="s">
         <v>372</v>
       </c>
-      <c r="D182" s="3" t="s">
+      <c r="D196" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="E182" s="3" t="s">
+      <c r="E196" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="F182" s="3" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="183" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A183" s="36"/>
-      <c r="B183" s="43"/>
-      <c r="C183" s="18" t="s">
+      <c r="F196" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="197" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A197" s="49"/>
+      <c r="B197" s="39"/>
+      <c r="C197" s="18" t="s">
         <v>372</v>
       </c>
-      <c r="D183" s="3" t="s">
+      <c r="D197" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="E183" s="3" t="s">
+      <c r="E197" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="F183" s="3" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="184" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A184" s="36"/>
-      <c r="B184" s="43"/>
-      <c r="C184" s="18" t="s">
+      <c r="F197" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="198" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A198" s="49"/>
+      <c r="B198" s="39"/>
+      <c r="C198" s="18" t="s">
         <v>372</v>
       </c>
-      <c r="D184" s="3" t="s">
+      <c r="D198" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="E184" s="3" t="s">
+      <c r="E198" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="F184" s="3" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="185" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A185" s="36"/>
-      <c r="B185" s="43"/>
-      <c r="C185" s="18" t="s">
+      <c r="F198" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="199" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A199" s="49"/>
+      <c r="B199" s="39"/>
+      <c r="C199" s="18" t="s">
         <v>372</v>
       </c>
-      <c r="D185" s="3" t="s">
+      <c r="D199" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="E185" s="3" t="s">
+      <c r="E199" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="F185" s="3" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="186" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A186" s="36"/>
-      <c r="B186" s="44"/>
-      <c r="C186" s="18"/>
-    </row>
-    <row r="187" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A187" s="36"/>
-      <c r="B187" s="42" t="s">
+      <c r="F199" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="200" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A200" s="49"/>
+      <c r="B200" s="40"/>
+      <c r="C200" s="18"/>
+    </row>
+    <row r="201" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A201" s="49"/>
+      <c r="B201" s="38" t="s">
         <v>127</v>
       </c>
-      <c r="C187" s="19" t="s">
+      <c r="C201" s="19" t="s">
         <v>373</v>
       </c>
-      <c r="D187" s="6" t="s">
+      <c r="D201" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="E187" s="6" t="s">
+      <c r="E201" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="F187" s="6" t="s">
+      <c r="F201" s="6" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="188" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A188" s="36"/>
-      <c r="B188" s="43"/>
-      <c r="C188" s="18" t="s">
-        <v>373</v>
-      </c>
-      <c r="D188" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="E188" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="F188" s="3" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="189" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A189" s="36"/>
-      <c r="B189" s="43"/>
-      <c r="C189" s="18" t="s">
-        <v>373</v>
-      </c>
-      <c r="D189" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="E189" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="F189" s="3" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="190" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A190" s="36"/>
-      <c r="B190" s="43"/>
-      <c r="C190" s="18" t="s">
-        <v>373</v>
-      </c>
-      <c r="D190" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="E190" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="F190" s="3" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="191" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A191" s="36"/>
-      <c r="B191" s="43"/>
-      <c r="C191" s="18" t="s">
-        <v>373</v>
-      </c>
-      <c r="D191" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="E191" s="3" t="s">
-        <v>214</v>
-      </c>
-      <c r="F191" s="3" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="192" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A192" s="36"/>
-      <c r="B192" s="43"/>
-      <c r="C192" s="18" t="s">
-        <v>373</v>
-      </c>
-      <c r="D192" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="E192" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="F192" s="3" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="193" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A193" s="36"/>
-      <c r="B193" s="43"/>
-      <c r="C193" s="18" t="s">
-        <v>373</v>
-      </c>
-      <c r="D193" s="3" t="s">
-        <v>230</v>
-      </c>
-      <c r="E193" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="F193" s="3" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="194" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A194" s="36"/>
-      <c r="B194" s="43"/>
-      <c r="C194" s="18" t="s">
-        <v>373</v>
-      </c>
-      <c r="D194" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="E194" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="F194" s="3" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="195" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A195" s="36"/>
-      <c r="B195" s="43"/>
-      <c r="C195" s="18" t="s">
-        <v>373</v>
-      </c>
-      <c r="D195" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="E195" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="F195" s="3" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="196" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A196" s="36"/>
-      <c r="B196" s="43"/>
-      <c r="C196" s="18" t="s">
-        <v>373</v>
-      </c>
-      <c r="D196" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="E196" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="F196" s="3" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="197" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A197" s="36"/>
-      <c r="B197" s="43"/>
-      <c r="C197" s="18" t="s">
-        <v>373</v>
-      </c>
-      <c r="D197" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="E197" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="F197" s="3" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="198" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A198" s="36"/>
-      <c r="B198" s="43"/>
-      <c r="C198" s="18" t="s">
-        <v>373</v>
-      </c>
-      <c r="D198" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="E198" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="F198" s="3" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="199" spans="1:6" s="11" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A199" s="36"/>
-      <c r="B199" s="43"/>
-      <c r="C199" s="18" t="s">
-        <v>373</v>
-      </c>
-      <c r="D199" s="11" t="s">
-        <v>277</v>
-      </c>
-      <c r="E199" s="11" t="s">
-        <v>278</v>
-      </c>
-      <c r="F199" s="11" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="200" spans="1:6" s="11" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A200" s="36"/>
-      <c r="B200" s="43"/>
-      <c r="C200" s="18" t="s">
-        <v>373</v>
-      </c>
-      <c r="D200" s="11" t="s">
-        <v>279</v>
-      </c>
-      <c r="E200" s="11" t="s">
-        <v>280</v>
-      </c>
-      <c r="F200" s="11" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="201" spans="1:6" s="11" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A201" s="36"/>
-      <c r="B201" s="43"/>
-      <c r="C201" s="18" t="s">
-        <v>373</v>
-      </c>
-      <c r="D201" s="11" t="s">
-        <v>179</v>
-      </c>
-      <c r="E201" s="11" t="s">
-        <v>337</v>
-      </c>
-      <c r="F201" s="11" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="202" spans="1:6" s="11" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A202" s="36"/>
-      <c r="B202" s="43"/>
+    <row r="202" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A202" s="49"/>
+      <c r="B202" s="39"/>
       <c r="C202" s="18" t="s">
         <v>373</v>
       </c>
-      <c r="D202" s="11" t="s">
-        <v>338</v>
-      </c>
-      <c r="E202" s="11" t="s">
-        <v>339</v>
-      </c>
-      <c r="F202" s="11" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="203" spans="1:6" s="11" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A203" s="36"/>
-      <c r="B203" s="43"/>
+      <c r="D202" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="E202" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="F202" s="3" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="203" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A203" s="49"/>
+      <c r="B203" s="39"/>
       <c r="C203" s="18" t="s">
         <v>373</v>
       </c>
-      <c r="D203" s="11" t="s">
-        <v>340</v>
-      </c>
-      <c r="E203" s="11" t="s">
-        <v>341</v>
-      </c>
-      <c r="F203" s="11" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="204" spans="1:6" s="11" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A204" s="36"/>
-      <c r="B204" s="43"/>
+      <c r="D203" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="E203" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="F203" s="3" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="204" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A204" s="49"/>
+      <c r="B204" s="39"/>
       <c r="C204" s="18" t="s">
         <v>373</v>
       </c>
-      <c r="D204" s="11" t="s">
-        <v>342</v>
-      </c>
-      <c r="E204" s="11" t="s">
-        <v>343</v>
-      </c>
-      <c r="F204" s="11" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="205" spans="1:6" s="11" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A205" s="36"/>
-      <c r="B205" s="43"/>
+      <c r="D204" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="E204" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="F204" s="3" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="205" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A205" s="49"/>
+      <c r="B205" s="39"/>
       <c r="C205" s="18" t="s">
         <v>373</v>
       </c>
       <c r="D205" s="3" t="s">
-        <v>348</v>
-      </c>
-      <c r="E205" s="11" t="s">
-        <v>346</v>
+        <v>213</v>
+      </c>
+      <c r="E205" s="3" t="s">
+        <v>214</v>
       </c>
       <c r="F205" s="3" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="206" spans="1:6" s="11" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A206" s="36"/>
-      <c r="B206" s="43"/>
+        <v>217</v>
+      </c>
+    </row>
+    <row r="206" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A206" s="49"/>
+      <c r="B206" s="39"/>
       <c r="C206" s="18" t="s">
         <v>373</v>
       </c>
       <c r="D206" s="3" t="s">
-        <v>349</v>
-      </c>
-      <c r="E206" s="11" t="s">
-        <v>347</v>
+        <v>228</v>
+      </c>
+      <c r="E206" s="3" t="s">
+        <v>229</v>
       </c>
       <c r="F206" s="3" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="207" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A207" s="49"/>
+      <c r="B207" s="39"/>
+      <c r="C207" s="18" t="s">
+        <v>373</v>
+      </c>
+      <c r="D207" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="E207" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="F207" s="3" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="208" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A208" s="49"/>
+      <c r="B208" s="39"/>
+      <c r="C208" s="18" t="s">
+        <v>373</v>
+      </c>
+      <c r="D208" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="E208" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="F208" s="3" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="209" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A209" s="49"/>
+      <c r="B209" s="39"/>
+      <c r="C209" s="18" t="s">
+        <v>373</v>
+      </c>
+      <c r="D209" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="E209" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="F209" s="3" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="207" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A207" s="36"/>
-      <c r="B207" s="44"/>
-      <c r="C207" s="18"/>
-    </row>
-    <row r="208" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A208" s="36"/>
-      <c r="B208" s="42" t="s">
-        <v>143</v>
-      </c>
-      <c r="C208" s="19" t="s">
-        <v>374</v>
-      </c>
-      <c r="D208" s="6" t="s">
-        <v>145</v>
-      </c>
-      <c r="E208" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="F208" s="6" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="209" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A209" s="36"/>
-      <c r="B209" s="43"/>
-      <c r="C209" s="18" t="s">
-        <v>374</v>
-      </c>
-      <c r="D209" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="E209" s="3" t="s">
-        <v>216</v>
-      </c>
-      <c r="F209" s="3" t="s">
-        <v>217</v>
-      </c>
-    </row>
     <row r="210" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A210" s="36"/>
-      <c r="B210" s="43"/>
+      <c r="A210" s="49"/>
+      <c r="B210" s="39"/>
       <c r="C210" s="18" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="D210" s="3" t="s">
-        <v>146</v>
+        <v>123</v>
       </c>
       <c r="E210" s="3" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="F210" s="3" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="211" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A211" s="36"/>
-      <c r="B211" s="43"/>
+      <c r="A211" s="49"/>
+      <c r="B211" s="39"/>
       <c r="C211" s="18" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="D211" s="3" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="E211" s="3" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="F211" s="3" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="212" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A212" s="36"/>
-      <c r="B212" s="43"/>
+      <c r="A212" s="49"/>
+      <c r="B212" s="39"/>
       <c r="C212" s="18" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="D212" s="3" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="E212" s="3" t="s">
-        <v>211</v>
+        <v>181</v>
       </c>
       <c r="F212" s="3" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="213" spans="1:6" s="11" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A213" s="36"/>
-      <c r="B213" s="43"/>
+      <c r="A213" s="49"/>
+      <c r="B213" s="39"/>
       <c r="C213" s="18" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="D213" s="11" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="E213" s="11" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="F213" s="11" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="214" spans="1:6" s="11" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A214" s="36"/>
-      <c r="B214" s="43"/>
+      <c r="A214" s="49"/>
+      <c r="B214" s="39"/>
       <c r="C214" s="18" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="D214" s="11" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="E214" s="11" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="F214" s="11" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="215" spans="1:6" s="11" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A215" s="36"/>
-      <c r="B215" s="43"/>
+      <c r="A215" s="49"/>
+      <c r="B215" s="39"/>
       <c r="C215" s="18" t="s">
+        <v>373</v>
+      </c>
+      <c r="D215" s="11" t="s">
+        <v>179</v>
+      </c>
+      <c r="E215" s="11" t="s">
+        <v>337</v>
+      </c>
+      <c r="F215" s="11" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="216" spans="1:6" s="11" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A216" s="49"/>
+      <c r="B216" s="39"/>
+      <c r="C216" s="18" t="s">
+        <v>373</v>
+      </c>
+      <c r="D216" s="11" t="s">
+        <v>338</v>
+      </c>
+      <c r="E216" s="11" t="s">
+        <v>339</v>
+      </c>
+      <c r="F216" s="11" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="217" spans="1:6" s="11" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A217" s="49"/>
+      <c r="B217" s="39"/>
+      <c r="C217" s="18" t="s">
+        <v>373</v>
+      </c>
+      <c r="D217" s="11" t="s">
+        <v>340</v>
+      </c>
+      <c r="E217" s="11" t="s">
+        <v>341</v>
+      </c>
+      <c r="F217" s="11" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="218" spans="1:6" s="11" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A218" s="49"/>
+      <c r="B218" s="39"/>
+      <c r="C218" s="18" t="s">
+        <v>373</v>
+      </c>
+      <c r="D218" s="11" t="s">
+        <v>342</v>
+      </c>
+      <c r="E218" s="11" t="s">
+        <v>343</v>
+      </c>
+      <c r="F218" s="11" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="219" spans="1:6" s="11" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A219" s="49"/>
+      <c r="B219" s="39"/>
+      <c r="C219" s="18" t="s">
+        <v>373</v>
+      </c>
+      <c r="D219" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="E219" s="11" t="s">
+        <v>346</v>
+      </c>
+      <c r="F219" s="3" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="220" spans="1:6" s="11" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A220" s="49"/>
+      <c r="B220" s="39"/>
+      <c r="C220" s="18" t="s">
+        <v>373</v>
+      </c>
+      <c r="D220" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="E220" s="11" t="s">
+        <v>389</v>
+      </c>
+      <c r="F220" s="3" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="221" spans="1:6" s="11" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A221" s="49"/>
+      <c r="B221" s="39"/>
+      <c r="C221" s="18" t="s">
+        <v>373</v>
+      </c>
+      <c r="D221" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="E221" s="11" t="s">
+        <v>347</v>
+      </c>
+      <c r="F221" s="3" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="222" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A222" s="49"/>
+      <c r="B222" s="40"/>
+      <c r="C222" s="18"/>
+    </row>
+    <row r="223" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A223" s="49"/>
+      <c r="B223" s="38" t="s">
+        <v>143</v>
+      </c>
+      <c r="C223" s="19" t="s">
         <v>374</v>
       </c>
-      <c r="D215" s="11" t="s">
+      <c r="D223" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="E223" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="F223" s="6" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="224" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A224" s="49"/>
+      <c r="B224" s="39"/>
+      <c r="C224" s="18" t="s">
+        <v>374</v>
+      </c>
+      <c r="D224" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="E224" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="F224" s="3" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="225" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A225" s="49"/>
+      <c r="B225" s="39"/>
+      <c r="C225" s="18" t="s">
+        <v>374</v>
+      </c>
+      <c r="D225" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="E225" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="F225" s="3" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="226" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A226" s="49"/>
+      <c r="B226" s="39"/>
+      <c r="C226" s="18" t="s">
+        <v>374</v>
+      </c>
+      <c r="D226" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="E226" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="F226" s="3" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="227" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A227" s="49"/>
+      <c r="B227" s="39"/>
+      <c r="C227" s="18" t="s">
+        <v>374</v>
+      </c>
+      <c r="D227" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="E227" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="F227" s="3" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="228" spans="1:6" s="11" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A228" s="49"/>
+      <c r="B228" s="39"/>
+      <c r="C228" s="18" t="s">
+        <v>374</v>
+      </c>
+      <c r="D228" s="11" t="s">
+        <v>281</v>
+      </c>
+      <c r="E228" s="11" t="s">
+        <v>282</v>
+      </c>
+      <c r="F228" s="11" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="229" spans="1:6" s="11" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A229" s="49"/>
+      <c r="B229" s="39"/>
+      <c r="C229" s="18" t="s">
+        <v>374</v>
+      </c>
+      <c r="D229" s="11" t="s">
+        <v>283</v>
+      </c>
+      <c r="E229" s="11" t="s">
+        <v>284</v>
+      </c>
+      <c r="F229" s="11" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="230" spans="1:6" s="11" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A230" s="49"/>
+      <c r="B230" s="39"/>
+      <c r="C230" s="18" t="s">
+        <v>374</v>
+      </c>
+      <c r="D230" s="11" t="s">
+        <v>390</v>
+      </c>
+      <c r="E230" s="11" t="s">
+        <v>391</v>
+      </c>
+      <c r="F230" s="11" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="231" spans="1:6" s="11" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A231" s="49"/>
+      <c r="B231" s="39"/>
+      <c r="C231" s="18" t="s">
+        <v>374</v>
+      </c>
+      <c r="D231" s="11" t="s">
         <v>344</v>
       </c>
-      <c r="E215" s="11" t="s">
+      <c r="E231" s="11" t="s">
         <v>345</v>
       </c>
-      <c r="F215" s="11" t="s">
+      <c r="F231" s="11" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="216" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A216" s="36"/>
-      <c r="B216" s="44"/>
-      <c r="C216" s="18"/>
-    </row>
-    <row r="217" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A217" s="36"/>
-      <c r="B217" s="42" t="s">
+    <row r="232" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A232" s="49"/>
+      <c r="B232" s="40"/>
+      <c r="C232" s="18"/>
+    </row>
+    <row r="233" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A233" s="49"/>
+      <c r="B233" s="38" t="s">
         <v>234</v>
       </c>
-      <c r="C217" s="19" t="s">
+      <c r="C233" s="19" t="s">
         <v>375</v>
       </c>
-      <c r="D217" s="6" t="s">
+      <c r="D233" s="6" t="s">
         <v>235</v>
       </c>
-      <c r="E217" s="6" t="s">
+      <c r="E233" s="6" t="s">
         <v>236</v>
       </c>
-      <c r="F217" s="6" t="s">
+      <c r="F233" s="6" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="218" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A218" s="36"/>
-      <c r="B218" s="43"/>
-      <c r="C218" s="18" t="s">
+    <row r="234" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A234" s="49"/>
+      <c r="B234" s="39"/>
+      <c r="C234" s="18" t="s">
         <v>375</v>
       </c>
-      <c r="D218" s="9" t="s">
+      <c r="D234" s="9" t="s">
         <v>237</v>
       </c>
-      <c r="E218" s="9" t="s">
+      <c r="E234" s="9" t="s">
         <v>238</v>
       </c>
-      <c r="F218" s="9" t="s">
+      <c r="F234" s="9" t="s">
         <v>133</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="34">
+  <mergeCells count="36">
+    <mergeCell ref="A133:A164"/>
+    <mergeCell ref="B145:B154"/>
+    <mergeCell ref="B155:B164"/>
+    <mergeCell ref="A165:A190"/>
+    <mergeCell ref="B173:B175"/>
+    <mergeCell ref="B165:B168"/>
+    <mergeCell ref="B169:B172"/>
+    <mergeCell ref="B179:B181"/>
+    <mergeCell ref="B176:B178"/>
+    <mergeCell ref="B182:B184"/>
+    <mergeCell ref="B139:B141"/>
+    <mergeCell ref="B142:B144"/>
+    <mergeCell ref="B188:B189"/>
+    <mergeCell ref="B185:B187"/>
+    <mergeCell ref="B233:B234"/>
+    <mergeCell ref="A191:A234"/>
+    <mergeCell ref="A2:A100"/>
+    <mergeCell ref="B2:B11"/>
+    <mergeCell ref="A101:A132"/>
+    <mergeCell ref="B121:B132"/>
+    <mergeCell ref="B69:B78"/>
+    <mergeCell ref="B101:B110"/>
+    <mergeCell ref="B111:B120"/>
+    <mergeCell ref="B194:B200"/>
+    <mergeCell ref="B201:B222"/>
+    <mergeCell ref="B191:B193"/>
+    <mergeCell ref="B223:B232"/>
+    <mergeCell ref="B12:B22"/>
+    <mergeCell ref="B23:B33"/>
     <mergeCell ref="B34:B43"/>
-    <mergeCell ref="B125:B127"/>
-    <mergeCell ref="B122:B124"/>
+    <mergeCell ref="B136:B138"/>
+    <mergeCell ref="B133:B135"/>
     <mergeCell ref="B44:B55"/>
     <mergeCell ref="B56:B68"/>
-    <mergeCell ref="B217:B218"/>
-    <mergeCell ref="A177:A218"/>
-    <mergeCell ref="A2:A89"/>
-    <mergeCell ref="B2:B11"/>
     <mergeCell ref="B79:B89"/>
-    <mergeCell ref="A90:A121"/>
-    <mergeCell ref="B110:B121"/>
-    <mergeCell ref="B69:B78"/>
     <mergeCell ref="B90:B99"/>
-    <mergeCell ref="B100:B109"/>
-    <mergeCell ref="B180:B186"/>
-    <mergeCell ref="B187:B207"/>
-    <mergeCell ref="B177:B179"/>
-    <mergeCell ref="B208:B216"/>
-    <mergeCell ref="B12:B22"/>
-    <mergeCell ref="B23:B33"/>
-    <mergeCell ref="A122:A153"/>
-    <mergeCell ref="B134:B143"/>
-    <mergeCell ref="B144:B153"/>
-    <mergeCell ref="A154:A176"/>
-    <mergeCell ref="B162:B164"/>
-    <mergeCell ref="B154:B157"/>
-    <mergeCell ref="B158:B161"/>
-    <mergeCell ref="B168:B170"/>
-    <mergeCell ref="B165:B167"/>
-    <mergeCell ref="B171:B173"/>
-    <mergeCell ref="B174:B176"/>
-    <mergeCell ref="B128:B130"/>
-    <mergeCell ref="B131:B133"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>

--- a/Vergleich_Ergebnisse_Vorlage.xlsx
+++ b/Vergleich_Ergebnisse_Vorlage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hem38994\Documents\GitHub\FENES_P2X\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BA4A940-CE17-42BA-97F2-2BDBD8ACFC5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE1DFC14-19D6-4332-9B63-BD9B2579E10A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="854" uniqueCount="400">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="854" uniqueCount="399">
   <si>
     <t>PEM Elektrolyse</t>
   </si>
@@ -626,9 +626,6 @@
   </si>
   <si>
     <t>€/ kW_th a</t>
-  </si>
-  <si>
-    <t>MWh_th/a</t>
   </si>
   <si>
     <t>Waermeproduktion</t>
@@ -1385,14 +1382,14 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -1403,20 +1400,20 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -1721,7 +1718,7 @@
         <v>2</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>9</v>
@@ -1734,14 +1731,14 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="21" t="s">
+      <c r="A2" s="27" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="31" t="s">
+      <c r="B2" s="30" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="D2" s="4" t="s">
         <v>19</v>
@@ -1754,10 +1751,10 @@
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="22"/>
-      <c r="B3" s="29"/>
+      <c r="A3" s="28"/>
+      <c r="B3" s="22"/>
       <c r="C3" s="10" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>30</v>
@@ -1770,10 +1767,10 @@
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="22"/>
-      <c r="B4" s="29"/>
+      <c r="A4" s="28"/>
+      <c r="B4" s="22"/>
       <c r="C4" s="10" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>18</v>
@@ -1786,13 +1783,13 @@
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="22"/>
-      <c r="B5" s="29"/>
+      <c r="A5" s="28"/>
+      <c r="B5" s="22"/>
       <c r="C5" s="10" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>60</v>
@@ -1802,10 +1799,10 @@
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="22"/>
-      <c r="B6" s="29"/>
+      <c r="A6" s="28"/>
+      <c r="B6" s="22"/>
       <c r="C6" s="10" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>63</v>
@@ -1818,10 +1815,10 @@
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" s="22"/>
-      <c r="B7" s="29"/>
+      <c r="A7" s="28"/>
+      <c r="B7" s="22"/>
       <c r="C7" s="10" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>77</v>
@@ -1834,10 +1831,10 @@
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="22"/>
-      <c r="B8" s="29"/>
+      <c r="A8" s="28"/>
+      <c r="B8" s="22"/>
       <c r="C8" s="10" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>117</v>
@@ -1850,10 +1847,10 @@
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" s="22"/>
-      <c r="B9" s="29"/>
+      <c r="A9" s="28"/>
+      <c r="B9" s="22"/>
       <c r="C9" s="10" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>89</v>
@@ -1866,10 +1863,10 @@
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="22"/>
-      <c r="B10" s="29"/>
+      <c r="A10" s="28"/>
+      <c r="B10" s="22"/>
       <c r="C10" s="10" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>109</v>
@@ -1882,17 +1879,17 @@
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="22"/>
-      <c r="B11" s="30"/>
+      <c r="A11" s="28"/>
+      <c r="B11" s="23"/>
       <c r="C11" s="10"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="22"/>
-      <c r="B12" s="28" t="s">
+      <c r="A12" s="28"/>
+      <c r="B12" s="21" t="s">
         <v>150</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>19</v>
@@ -1905,26 +1902,26 @@
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13" s="22"/>
-      <c r="B13" s="29"/>
+      <c r="A13" s="28"/>
+      <c r="B13" s="22"/>
       <c r="C13" s="10" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>159</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="F13" s="3" t="s">
         <v>162</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14" s="22"/>
-      <c r="B14" s="29"/>
+      <c r="A14" s="28"/>
+      <c r="B14" s="22"/>
       <c r="C14" s="10" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>61</v>
@@ -1937,10 +1934,10 @@
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A15" s="22"/>
-      <c r="B15" s="29"/>
+      <c r="A15" s="28"/>
+      <c r="B15" s="22"/>
       <c r="C15" s="10" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>160</v>
@@ -1953,10 +1950,10 @@
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A16" s="22"/>
-      <c r="B16" s="29"/>
+      <c r="A16" s="28"/>
+      <c r="B16" s="22"/>
       <c r="C16" s="10" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>18</v>
@@ -1969,10 +1966,10 @@
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="22"/>
-      <c r="B17" s="29"/>
+      <c r="A17" s="28"/>
+      <c r="B17" s="22"/>
       <c r="C17" s="10" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>63</v>
@@ -1985,10 +1982,10 @@
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="22"/>
-      <c r="B18" s="29"/>
+      <c r="A18" s="28"/>
+      <c r="B18" s="22"/>
       <c r="C18" s="10" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>77</v>
@@ -2001,10 +1998,10 @@
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" s="22"/>
-      <c r="B19" s="29"/>
+      <c r="A19" s="28"/>
+      <c r="B19" s="22"/>
       <c r="C19" s="10" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>117</v>
@@ -2017,10 +2014,10 @@
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20" s="22"/>
-      <c r="B20" s="29"/>
+      <c r="A20" s="28"/>
+      <c r="B20" s="22"/>
       <c r="C20" s="10" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>89</v>
@@ -2033,10 +2030,10 @@
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21" s="22"/>
-      <c r="B21" s="29"/>
+      <c r="A21" s="28"/>
+      <c r="B21" s="22"/>
       <c r="C21" s="10" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>109</v>
@@ -2049,328 +2046,328 @@
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22" s="22"/>
-      <c r="B22" s="30"/>
+      <c r="A22" s="28"/>
+      <c r="B22" s="23"/>
       <c r="C22" s="10"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A23" s="22"/>
-      <c r="B23" s="28" t="s">
-        <v>255</v>
+      <c r="A23" s="28"/>
+      <c r="B23" s="21" t="s">
+        <v>254</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="D23" s="6" t="s">
         <v>19</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F23" s="6" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A24" s="22"/>
-      <c r="B24" s="29"/>
+      <c r="A24" s="28"/>
+      <c r="B24" s="22"/>
       <c r="C24" s="10" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="D24" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="E24" s="3" t="s">
         <v>242</v>
       </c>
-      <c r="E24" s="3" t="s">
+      <c r="F24" s="3" t="s">
         <v>243</v>
       </c>
-      <c r="F24" s="3" t="s">
-        <v>244</v>
-      </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A25" s="22"/>
-      <c r="B25" s="29"/>
+      <c r="A25" s="28"/>
+      <c r="B25" s="22"/>
       <c r="C25" s="10" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="D25" s="3" t="s">
         <v>61</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F25" s="5" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26" s="22"/>
-      <c r="B26" s="29"/>
+      <c r="A26" s="28"/>
+      <c r="B26" s="22"/>
       <c r="C26" s="10" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="D26" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="E26" s="3" t="s">
         <v>246</v>
       </c>
-      <c r="E26" s="3" t="s">
+      <c r="F26" s="3" t="s">
         <v>247</v>
       </c>
-      <c r="F26" s="3" t="s">
-        <v>248</v>
-      </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A27" s="22"/>
-      <c r="B27" s="29"/>
+      <c r="A27" s="28"/>
+      <c r="B27" s="22"/>
       <c r="C27" s="10" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="D27" s="3" t="s">
         <v>18</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="F27" s="3" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A28" s="22"/>
-      <c r="B28" s="29"/>
+      <c r="A28" s="28"/>
+      <c r="B28" s="22"/>
       <c r="C28" s="10" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="D28" s="3" t="s">
         <v>63</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F28" s="3" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A29" s="22"/>
-      <c r="B29" s="29"/>
+      <c r="A29" s="28"/>
+      <c r="B29" s="22"/>
       <c r="C29" s="10" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>77</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F29" s="3" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A30" s="22"/>
-      <c r="B30" s="29"/>
+      <c r="A30" s="28"/>
+      <c r="B30" s="22"/>
       <c r="C30" s="10" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="D30" s="3" t="s">
         <v>117</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="F30" s="3" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A31" s="22"/>
-      <c r="B31" s="29"/>
+      <c r="A31" s="28"/>
+      <c r="B31" s="22"/>
       <c r="C31" s="10" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="D31" s="3" t="s">
         <v>89</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="F31" s="3" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A32" s="22"/>
-      <c r="B32" s="29"/>
+      <c r="A32" s="28"/>
+      <c r="B32" s="22"/>
       <c r="C32" s="10" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>109</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="F32" s="3" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A33" s="22"/>
-      <c r="B33" s="30"/>
+      <c r="A33" s="28"/>
+      <c r="B33" s="23"/>
       <c r="C33" s="12"/>
       <c r="D33" s="7"/>
       <c r="E33" s="7"/>
       <c r="F33" s="7"/>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A34" s="22"/>
+      <c r="A34" s="28"/>
       <c r="B34" s="24" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C34" s="13" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D34" s="6" t="s">
         <v>19</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A35" s="22"/>
+      <c r="A35" s="28"/>
       <c r="B35" s="25"/>
       <c r="C35" s="14" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D35" s="3" t="s">
         <v>30</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="F35" s="3" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A36" s="22"/>
+      <c r="A36" s="28"/>
       <c r="B36" s="25"/>
       <c r="C36" s="14" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D36" s="3" t="s">
         <v>18</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="F36" s="3" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A37" s="22"/>
+      <c r="A37" s="28"/>
       <c r="B37" s="25"/>
       <c r="C37" s="14" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D37" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="E37" s="3" t="s">
         <v>260</v>
       </c>
-      <c r="E37" s="3" t="s">
-        <v>261</v>
-      </c>
       <c r="F37" s="3" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A38" s="22"/>
+      <c r="A38" s="28"/>
       <c r="B38" s="25"/>
       <c r="C38" s="14" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D38" s="3" t="s">
         <v>63</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="F38" s="3" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A39" s="22"/>
+      <c r="A39" s="28"/>
       <c r="B39" s="25"/>
       <c r="C39" s="14" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D39" s="3" t="s">
         <v>77</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="F39" s="3" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A40" s="22"/>
+      <c r="A40" s="28"/>
       <c r="B40" s="25"/>
       <c r="C40" s="14" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D40" s="3" t="s">
         <v>117</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="F40" s="3" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A41" s="22"/>
+      <c r="A41" s="28"/>
       <c r="B41" s="25"/>
       <c r="C41" s="14" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D41" s="3" t="s">
         <v>89</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="F41" s="3" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A42" s="22"/>
+      <c r="A42" s="28"/>
       <c r="B42" s="25"/>
       <c r="C42" s="14" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D42" s="3" t="s">
         <v>109</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="F42" s="3" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A43" s="22"/>
+      <c r="A43" s="28"/>
       <c r="B43" s="26"/>
       <c r="C43" s="15"/>
       <c r="D43" s="7"/>
@@ -2378,387 +2375,387 @@
       <c r="F43" s="7"/>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A44" s="22"/>
-      <c r="B44" s="28" t="s">
-        <v>284</v>
+      <c r="A44" s="28"/>
+      <c r="B44" s="21" t="s">
+        <v>283</v>
       </c>
       <c r="C44" s="11" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="D44" s="6" t="s">
         <v>19</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A45" s="22"/>
-      <c r="B45" s="29"/>
+      <c r="A45" s="28"/>
+      <c r="B45" s="22"/>
       <c r="C45" s="10" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="D45" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="E45" s="3" t="s">
         <v>286</v>
       </c>
-      <c r="E45" s="3" t="s">
+      <c r="F45" s="3" t="s">
         <v>287</v>
       </c>
-      <c r="F45" s="3" t="s">
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A46" s="28"/>
+      <c r="B46" s="22"/>
+      <c r="C46" s="10" t="s">
+        <v>353</v>
+      </c>
+      <c r="D46" s="3" t="s">
         <v>288</v>
       </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A46" s="22"/>
-      <c r="B46" s="29"/>
-      <c r="C46" s="10" t="s">
-        <v>354</v>
-      </c>
-      <c r="D46" s="3" t="s">
+      <c r="E46" s="3" t="s">
         <v>289</v>
       </c>
-      <c r="E46" s="3" t="s">
+      <c r="F46" s="3" t="s">
         <v>290</v>
       </c>
-      <c r="F46" s="3" t="s">
-        <v>291</v>
-      </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A47" s="22"/>
-      <c r="B47" s="29"/>
+      <c r="A47" s="28"/>
+      <c r="B47" s="22"/>
       <c r="C47" s="10" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>61</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="F47" s="5" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A48" s="22"/>
-      <c r="B48" s="29"/>
+      <c r="A48" s="28"/>
+      <c r="B48" s="22"/>
       <c r="C48" s="10" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="D48" s="3" t="s">
         <v>160</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="F48" s="3" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A49" s="22"/>
-      <c r="B49" s="29"/>
+      <c r="A49" s="28"/>
+      <c r="B49" s="22"/>
       <c r="C49" s="10" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="D49" s="3" t="s">
         <v>18</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="F49" s="3" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A50" s="22"/>
-      <c r="B50" s="29"/>
+      <c r="A50" s="28"/>
+      <c r="B50" s="22"/>
       <c r="C50" s="10" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="D50" s="3" t="s">
         <v>63</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="F50" s="3" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A51" s="22"/>
-      <c r="B51" s="29"/>
+      <c r="A51" s="28"/>
+      <c r="B51" s="22"/>
       <c r="C51" s="10" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="D51" s="3" t="s">
         <v>77</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F51" s="3" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A52" s="22"/>
-      <c r="B52" s="29"/>
+      <c r="A52" s="28"/>
+      <c r="B52" s="22"/>
       <c r="C52" s="10" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>117</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="F52" s="3" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A53" s="22"/>
-      <c r="B53" s="29"/>
+      <c r="A53" s="28"/>
+      <c r="B53" s="22"/>
       <c r="C53" s="10" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="D53" s="3" t="s">
         <v>89</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="F53" s="3" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A54" s="22"/>
-      <c r="B54" s="29"/>
+      <c r="A54" s="28"/>
+      <c r="B54" s="22"/>
       <c r="C54" s="10" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="D54" s="3" t="s">
         <v>109</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="F54" s="3" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A55" s="22"/>
-      <c r="B55" s="30"/>
+      <c r="A55" s="28"/>
+      <c r="B55" s="23"/>
       <c r="C55" s="12"/>
       <c r="D55" s="7"/>
       <c r="E55" s="7"/>
       <c r="F55" s="7"/>
     </row>
     <row r="56" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="22"/>
+      <c r="A56" s="28"/>
       <c r="B56" s="24" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C56" s="13" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="D56" s="6" t="s">
         <v>19</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A57" s="22"/>
+      <c r="A57" s="28"/>
       <c r="B57" s="25"/>
       <c r="C57" s="14" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="D57" s="3" t="s">
         <v>30</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F57" s="3" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A58" s="22"/>
+      <c r="A58" s="28"/>
       <c r="B58" s="25"/>
       <c r="C58" s="14" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="D58" s="3" t="s">
         <v>18</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F58" s="3" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A59" s="22"/>
+      <c r="A59" s="28"/>
       <c r="B59" s="25"/>
       <c r="C59" s="14" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="D59" s="3" t="s">
         <v>186</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="F59" s="3" t="s">
-        <v>196</v>
+        <v>237</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A60" s="22"/>
+      <c r="A60" s="28"/>
       <c r="B60" s="25"/>
       <c r="C60" s="14" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="D60" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="E60" s="3" t="s">
         <v>305</v>
       </c>
-      <c r="E60" s="3" t="s">
+      <c r="F60" s="3" t="s">
         <v>306</v>
       </c>
-      <c r="F60" s="3" t="s">
-        <v>307</v>
-      </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A61" s="22"/>
+      <c r="A61" s="28"/>
       <c r="B61" s="25"/>
       <c r="C61" s="14" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="D61" s="3" t="s">
         <v>172</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="F61" s="3" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A62" s="22"/>
+      <c r="A62" s="28"/>
       <c r="B62" s="25"/>
       <c r="C62" s="14" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="D62" s="3" t="s">
         <v>63</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="F62" s="3" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A63" s="22"/>
+      <c r="A63" s="28"/>
       <c r="B63" s="25"/>
       <c r="C63" s="14" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="D63" s="3" t="s">
         <v>77</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="F63" s="3" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A64" s="22"/>
+      <c r="A64" s="28"/>
       <c r="B64" s="25"/>
       <c r="C64" s="14" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="D64" s="3" t="s">
         <v>83</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="F64" s="3" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A65" s="22"/>
+      <c r="A65" s="28"/>
       <c r="B65" s="25"/>
       <c r="C65" s="14" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="D65" s="3" t="s">
         <v>117</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="F65" s="3" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A66" s="22"/>
+      <c r="A66" s="28"/>
       <c r="B66" s="25"/>
       <c r="C66" s="14" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="D66" s="3" t="s">
         <v>89</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F66" s="3" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A67" s="22"/>
+      <c r="A67" s="28"/>
       <c r="B67" s="25"/>
       <c r="C67" s="14" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="D67" s="3" t="s">
         <v>109</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F67" s="3" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A68" s="22"/>
+      <c r="A68" s="28"/>
       <c r="B68" s="26"/>
       <c r="C68" s="15"/>
       <c r="D68" s="7"/>
@@ -2766,12 +2763,12 @@
       <c r="F68" s="7"/>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A69" s="22"/>
-      <c r="B69" s="28" t="s">
+      <c r="A69" s="28"/>
+      <c r="B69" s="21" t="s">
         <v>185</v>
       </c>
       <c r="C69" s="10" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="D69" s="3" t="s">
         <v>19</v>
@@ -2784,10 +2781,10 @@
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A70" s="22"/>
-      <c r="B70" s="29"/>
+      <c r="A70" s="28"/>
+      <c r="B70" s="22"/>
       <c r="C70" s="10" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="D70" s="3" t="s">
         <v>30</v>
@@ -2800,10 +2797,10 @@
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A71" s="22"/>
-      <c r="B71" s="29"/>
+      <c r="A71" s="28"/>
+      <c r="B71" s="22"/>
       <c r="C71" s="10" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="D71" s="3" t="s">
         <v>18</v>
@@ -2812,30 +2809,30 @@
         <v>189</v>
       </c>
       <c r="F71" s="3" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A72" s="22"/>
-      <c r="B72" s="29"/>
+      <c r="A72" s="28"/>
+      <c r="B72" s="22"/>
       <c r="C72" s="10" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="D72" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="E72" s="3" t="s">
         <v>197</v>
       </c>
-      <c r="E72" s="3" t="s">
-        <v>198</v>
-      </c>
       <c r="F72" s="3" t="s">
-        <v>196</v>
+        <v>237</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A73" s="22"/>
-      <c r="B73" s="29"/>
+      <c r="A73" s="28"/>
+      <c r="B73" s="22"/>
       <c r="C73" s="10" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="D73" s="3" t="s">
         <v>63</v>
@@ -2848,10 +2845,10 @@
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A74" s="22"/>
-      <c r="B74" s="29"/>
+      <c r="A74" s="28"/>
+      <c r="B74" s="22"/>
       <c r="C74" s="10" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="D74" s="3" t="s">
         <v>77</v>
@@ -2864,10 +2861,10 @@
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A75" s="22"/>
-      <c r="B75" s="29"/>
+      <c r="A75" s="28"/>
+      <c r="B75" s="22"/>
       <c r="C75" s="10" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="D75" s="3" t="s">
         <v>117</v>
@@ -2880,10 +2877,10 @@
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A76" s="22"/>
-      <c r="B76" s="29"/>
+      <c r="A76" s="28"/>
+      <c r="B76" s="22"/>
       <c r="C76" s="10" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="D76" s="3" t="s">
         <v>89</v>
@@ -2896,10 +2893,10 @@
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A77" s="22"/>
-      <c r="B77" s="29"/>
+      <c r="A77" s="28"/>
+      <c r="B77" s="22"/>
       <c r="C77" s="10" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="D77" s="3" t="s">
         <v>109</v>
@@ -2912,20 +2909,20 @@
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A78" s="22"/>
-      <c r="B78" s="30"/>
+      <c r="A78" s="28"/>
+      <c r="B78" s="23"/>
       <c r="C78" s="12"/>
       <c r="D78" s="7"/>
       <c r="E78" s="7"/>
       <c r="F78" s="7"/>
     </row>
     <row r="79" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A79" s="22"/>
+      <c r="A79" s="28"/>
       <c r="B79" s="24" t="s">
         <v>149</v>
       </c>
       <c r="C79" s="13" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D79" s="6" t="s">
         <v>19</v>
@@ -2938,10 +2935,10 @@
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A80" s="22"/>
+      <c r="A80" s="28"/>
       <c r="B80" s="25"/>
       <c r="C80" s="14" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D80" s="3" t="s">
         <v>30</v>
@@ -2954,10 +2951,10 @@
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A81" s="22"/>
+      <c r="A81" s="28"/>
       <c r="B81" s="25"/>
       <c r="C81" s="14" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D81" s="3" t="s">
         <v>18</v>
@@ -2970,42 +2967,42 @@
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A82" s="22"/>
+      <c r="A82" s="28"/>
       <c r="B82" s="25"/>
       <c r="C82" s="14" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D82" s="3" t="s">
         <v>186</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F82" s="3" t="s">
-        <v>196</v>
+        <v>237</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A83" s="22"/>
+      <c r="A83" s="28"/>
       <c r="B83" s="25"/>
       <c r="C83" s="14" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D83" s="3" t="s">
         <v>172</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F83" s="3" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A84" s="22"/>
+      <c r="A84" s="28"/>
       <c r="B84" s="25"/>
       <c r="C84" s="14" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D84" s="3" t="s">
         <v>63</v>
@@ -3018,10 +3015,10 @@
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A85" s="22"/>
+      <c r="A85" s="28"/>
       <c r="B85" s="25"/>
       <c r="C85" s="14" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D85" s="3" t="s">
         <v>77</v>
@@ -3034,10 +3031,10 @@
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A86" s="22"/>
+      <c r="A86" s="28"/>
       <c r="B86" s="25"/>
       <c r="C86" s="14" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D86" s="3" t="s">
         <v>117</v>
@@ -3050,10 +3047,10 @@
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A87" s="22"/>
+      <c r="A87" s="28"/>
       <c r="B87" s="25"/>
       <c r="C87" s="14" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D87" s="3" t="s">
         <v>89</v>
@@ -3066,10 +3063,10 @@
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A88" s="22"/>
+      <c r="A88" s="28"/>
       <c r="B88" s="25"/>
       <c r="C88" s="14" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D88" s="3" t="s">
         <v>109</v>
@@ -3082,7 +3079,7 @@
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A89" s="22"/>
+      <c r="A89" s="28"/>
       <c r="B89" s="26"/>
       <c r="C89" s="15"/>
       <c r="D89" s="7"/>
@@ -3090,181 +3087,181 @@
       <c r="F89" s="7"/>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A90" s="22"/>
-      <c r="B90" s="29" t="s">
-        <v>375</v>
+      <c r="A90" s="28"/>
+      <c r="B90" s="22" t="s">
+        <v>374</v>
       </c>
       <c r="C90" s="14" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="D90" s="3" t="s">
         <v>19</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="F90" s="3" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A91" s="22"/>
-      <c r="B91" s="29"/>
+      <c r="A91" s="28"/>
+      <c r="B91" s="22"/>
       <c r="C91" s="14" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="D91" s="3" t="s">
         <v>159</v>
       </c>
       <c r="E91" s="3" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="F91" s="3" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A92" s="22"/>
-      <c r="B92" s="29"/>
+      <c r="A92" s="28"/>
+      <c r="B92" s="22"/>
       <c r="C92" s="14" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="D92" s="3" t="s">
         <v>61</v>
       </c>
       <c r="E92" s="3" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="F92" s="5" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A93" s="22"/>
-      <c r="B93" s="29"/>
+      <c r="A93" s="28"/>
+      <c r="B93" s="22"/>
       <c r="C93" s="14" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="D93" s="3" t="s">
         <v>160</v>
       </c>
       <c r="E93" s="3" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="F93" s="3" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A94" s="22"/>
-      <c r="B94" s="29"/>
+      <c r="A94" s="28"/>
+      <c r="B94" s="22"/>
       <c r="C94" s="14" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="D94" s="3" t="s">
         <v>18</v>
       </c>
       <c r="E94" s="3" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="F94" s="3" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A95" s="22"/>
-      <c r="B95" s="29"/>
+      <c r="A95" s="28"/>
+      <c r="B95" s="22"/>
       <c r="C95" s="14" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="D95" s="3" t="s">
         <v>63</v>
       </c>
       <c r="E95" s="3" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="F95" s="3" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A96" s="22"/>
-      <c r="B96" s="29"/>
+      <c r="A96" s="28"/>
+      <c r="B96" s="22"/>
       <c r="C96" s="14" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="D96" s="3" t="s">
         <v>77</v>
       </c>
       <c r="E96" s="3" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="F96" s="3" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A97" s="22"/>
-      <c r="B97" s="29"/>
+      <c r="A97" s="28"/>
+      <c r="B97" s="22"/>
       <c r="C97" s="14" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="D97" s="3" t="s">
         <v>117</v>
       </c>
       <c r="E97" s="3" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="F97" s="3" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A98" s="22"/>
-      <c r="B98" s="29"/>
+      <c r="A98" s="28"/>
+      <c r="B98" s="22"/>
       <c r="C98" s="14" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="D98" s="3" t="s">
         <v>89</v>
       </c>
       <c r="E98" s="3" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="F98" s="3" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A99" s="22"/>
-      <c r="B99" s="29"/>
+      <c r="A99" s="28"/>
+      <c r="B99" s="22"/>
       <c r="C99" s="14" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="D99" s="3" t="s">
         <v>109</v>
       </c>
       <c r="E99" s="3" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="F99" s="3" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="100" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A100" s="23"/>
+      <c r="A100" s="29"/>
       <c r="B100" s="19"/>
       <c r="C100" s="14"/>
     </row>
     <row r="101" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A101" s="21" t="s">
+      <c r="A101" s="27" t="s">
         <v>13</v>
       </c>
       <c r="B101" s="32" t="s">
         <v>3</v>
       </c>
       <c r="C101" s="16" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="D101" s="4" t="s">
         <v>36</v>
@@ -3273,14 +3270,14 @@
         <v>26</v>
       </c>
       <c r="F101" s="4" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A102" s="22"/>
+      <c r="A102" s="28"/>
       <c r="B102" s="25"/>
       <c r="C102" s="14" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="D102" s="3" t="s">
         <v>34</v>
@@ -3289,14 +3286,14 @@
         <v>33</v>
       </c>
       <c r="F102" s="3" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A103" s="22"/>
+      <c r="A103" s="28"/>
       <c r="B103" s="25"/>
       <c r="C103" s="14" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="D103" s="3" t="s">
         <v>58</v>
@@ -3309,10 +3306,10 @@
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A104" s="22"/>
+      <c r="A104" s="28"/>
       <c r="B104" s="25"/>
       <c r="C104" s="14" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="D104" s="3" t="s">
         <v>59</v>
@@ -3325,10 +3322,10 @@
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A105" s="22"/>
+      <c r="A105" s="28"/>
       <c r="B105" s="25"/>
       <c r="C105" s="14" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="D105" s="3" t="s">
         <v>63</v>
@@ -3341,10 +3338,10 @@
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A106" s="22"/>
+      <c r="A106" s="28"/>
       <c r="B106" s="25"/>
       <c r="C106" s="14" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="D106" s="3" t="s">
         <v>77</v>
@@ -3357,10 +3354,10 @@
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A107" s="22"/>
+      <c r="A107" s="28"/>
       <c r="B107" s="25"/>
       <c r="C107" s="14" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="D107" s="3" t="s">
         <v>117</v>
@@ -3373,10 +3370,10 @@
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A108" s="22"/>
+      <c r="A108" s="28"/>
       <c r="B108" s="25"/>
       <c r="C108" s="14" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="D108" s="3" t="s">
         <v>89</v>
@@ -3389,10 +3386,10 @@
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A109" s="22"/>
+      <c r="A109" s="28"/>
       <c r="B109" s="25"/>
       <c r="C109" s="14" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="D109" s="3" t="s">
         <v>109</v>
@@ -3405,7 +3402,7 @@
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A110" s="22"/>
+      <c r="A110" s="28"/>
       <c r="B110" s="26"/>
       <c r="C110" s="15"/>
       <c r="D110" s="7"/>
@@ -3413,163 +3410,163 @@
       <c r="F110" s="7"/>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A111" s="22"/>
+      <c r="A111" s="28"/>
       <c r="B111" s="24" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C111" s="14" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="D111" s="3" t="s">
         <v>36</v>
       </c>
       <c r="E111" s="3" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="F111" s="3" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A112" s="22"/>
+      <c r="A112" s="28"/>
       <c r="B112" s="25"/>
       <c r="C112" s="14" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="D112" s="3" t="s">
         <v>34</v>
       </c>
       <c r="E112" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F112" s="3" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A113" s="22"/>
+      <c r="A113" s="28"/>
       <c r="B113" s="25"/>
       <c r="C113" s="14" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="D113" s="3" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="E113" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F113" s="3" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A114" s="22"/>
+      <c r="A114" s="28"/>
       <c r="B114" s="25"/>
       <c r="C114" s="14" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="D114" s="3" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="E114" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="F114" s="3" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A115" s="22"/>
+      <c r="A115" s="28"/>
       <c r="B115" s="25"/>
       <c r="C115" s="14" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="D115" s="3" t="s">
         <v>63</v>
       </c>
       <c r="E115" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="F115" s="3" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A116" s="22"/>
+      <c r="A116" s="28"/>
       <c r="B116" s="25"/>
       <c r="C116" s="14" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="D116" s="3" t="s">
         <v>77</v>
       </c>
       <c r="E116" s="3" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F116" s="3" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A117" s="22"/>
+      <c r="A117" s="28"/>
       <c r="B117" s="25"/>
       <c r="C117" s="14" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="D117" s="3" t="s">
         <v>117</v>
       </c>
       <c r="E117" s="3" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F117" s="3" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A118" s="22"/>
+      <c r="A118" s="28"/>
       <c r="B118" s="25"/>
       <c r="C118" s="14" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="D118" s="3" t="s">
         <v>89</v>
       </c>
       <c r="E118" s="3" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F118" s="3" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A119" s="22"/>
+      <c r="A119" s="28"/>
       <c r="B119" s="25"/>
       <c r="C119" s="14" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="D119" s="3" t="s">
         <v>109</v>
       </c>
       <c r="E119" s="3" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F119" s="3" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A120" s="22"/>
+      <c r="A120" s="28"/>
       <c r="B120" s="26"/>
       <c r="C120" s="14"/>
     </row>
     <row r="121" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A121" s="22"/>
+      <c r="A121" s="28"/>
       <c r="B121" s="24" t="s">
         <v>6</v>
       </c>
       <c r="C121" s="13" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="D121" s="6" t="s">
         <v>19</v>
@@ -3582,10 +3579,10 @@
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A122" s="22"/>
+      <c r="A122" s="28"/>
       <c r="B122" s="25"/>
       <c r="C122" s="14" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="D122" s="3" t="s">
         <v>36</v>
@@ -3598,10 +3595,10 @@
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A123" s="22"/>
+      <c r="A123" s="28"/>
       <c r="B123" s="25"/>
       <c r="C123" s="14" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="D123" s="3" t="s">
         <v>34</v>
@@ -3614,10 +3611,10 @@
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A124" s="22"/>
+      <c r="A124" s="28"/>
       <c r="B124" s="25"/>
       <c r="C124" s="14" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="D124" s="3" t="s">
         <v>30</v>
@@ -3630,10 +3627,10 @@
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A125" s="22"/>
+      <c r="A125" s="28"/>
       <c r="B125" s="25"/>
       <c r="C125" s="14" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="D125" s="3" t="s">
         <v>49</v>
@@ -3646,10 +3643,10 @@
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A126" s="22"/>
+      <c r="A126" s="28"/>
       <c r="B126" s="25"/>
       <c r="C126" s="14" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="D126" s="3" t="s">
         <v>50</v>
@@ -3662,10 +3659,10 @@
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A127" s="22"/>
+      <c r="A127" s="28"/>
       <c r="B127" s="25"/>
       <c r="C127" s="14" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="D127" s="3" t="s">
         <v>63</v>
@@ -3678,10 +3675,10 @@
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A128" s="22"/>
+      <c r="A128" s="28"/>
       <c r="B128" s="25"/>
       <c r="C128" s="14" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="D128" s="3" t="s">
         <v>77</v>
@@ -3694,10 +3691,10 @@
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A129" s="22"/>
+      <c r="A129" s="28"/>
       <c r="B129" s="25"/>
       <c r="C129" s="14" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="D129" s="3" t="s">
         <v>117</v>
@@ -3710,10 +3707,10 @@
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A130" s="22"/>
+      <c r="A130" s="28"/>
       <c r="B130" s="25"/>
       <c r="C130" s="14" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="D130" s="3" t="s">
         <v>89</v>
@@ -3726,10 +3723,10 @@
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A131" s="22"/>
+      <c r="A131" s="28"/>
       <c r="B131" s="25"/>
       <c r="C131" s="14" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="D131" s="3" t="s">
         <v>109</v>
@@ -3742,22 +3739,22 @@
       </c>
     </row>
     <row r="132" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A132" s="23"/>
-      <c r="B132" s="27"/>
+      <c r="A132" s="29"/>
+      <c r="B132" s="31"/>
       <c r="C132" s="17"/>
       <c r="D132" s="8"/>
       <c r="E132" s="8"/>
       <c r="F132" s="8"/>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A133" s="21" t="s">
+      <c r="A133" s="27" t="s">
         <v>14</v>
       </c>
-      <c r="B133" s="31" t="s">
+      <c r="B133" s="30" t="s">
         <v>15</v>
       </c>
       <c r="C133" s="9" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="D133" s="4" t="s">
         <v>40</v>
@@ -3770,10 +3767,10 @@
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A134" s="22"/>
-      <c r="B134" s="29"/>
+      <c r="A134" s="28"/>
+      <c r="B134" s="22"/>
       <c r="C134" s="10" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="D134" s="3" t="s">
         <v>75</v>
@@ -3786,138 +3783,138 @@
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A135" s="22"/>
-      <c r="B135" s="30"/>
+      <c r="A135" s="28"/>
+      <c r="B135" s="23"/>
       <c r="C135" s="12"/>
       <c r="D135" s="7"/>
       <c r="E135" s="7"/>
       <c r="F135" s="7"/>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A136" s="22"/>
-      <c r="B136" s="28" t="s">
-        <v>270</v>
+      <c r="A136" s="28"/>
+      <c r="B136" s="21" t="s">
+        <v>269</v>
       </c>
       <c r="C136" s="10" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="D136" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="E136" s="3" t="s">
         <v>267</v>
       </c>
-      <c r="E136" s="3" t="s">
-        <v>268</v>
-      </c>
       <c r="F136" s="3" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A137" s="22"/>
-      <c r="B137" s="29"/>
+      <c r="A137" s="28"/>
+      <c r="B137" s="22"/>
       <c r="C137" s="10" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="D137" s="3" t="s">
         <v>75</v>
       </c>
       <c r="E137" s="3" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="F137" s="3" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A138" s="22"/>
-      <c r="B138" s="30"/>
+      <c r="A138" s="28"/>
+      <c r="B138" s="23"/>
       <c r="C138" s="12"/>
       <c r="D138" s="7"/>
       <c r="E138" s="7"/>
       <c r="F138" s="7"/>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A139" s="22"/>
-      <c r="B139" s="28" t="s">
+      <c r="A139" s="28"/>
+      <c r="B139" s="21" t="s">
+        <v>314</v>
+      </c>
+      <c r="C139" s="11" t="s">
+        <v>362</v>
+      </c>
+      <c r="D139" s="6" t="s">
         <v>315</v>
       </c>
-      <c r="C139" s="11" t="s">
-        <v>363</v>
-      </c>
-      <c r="D139" s="6" t="s">
+      <c r="E139" s="6" t="s">
         <v>316</v>
-      </c>
-      <c r="E139" s="6" t="s">
-        <v>317</v>
       </c>
       <c r="F139" s="6" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A140" s="22"/>
-      <c r="B140" s="29"/>
+      <c r="A140" s="28"/>
+      <c r="B140" s="22"/>
       <c r="C140" s="10" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="D140" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="E140" s="3" t="s">
         <v>318</v>
       </c>
-      <c r="E140" s="3" t="s">
-        <v>319</v>
-      </c>
       <c r="F140" s="3" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A141" s="22"/>
-      <c r="B141" s="30"/>
+      <c r="A141" s="28"/>
+      <c r="B141" s="23"/>
       <c r="C141" s="12"/>
       <c r="D141" s="7"/>
       <c r="E141" s="7"/>
       <c r="F141" s="7"/>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A142" s="22"/>
-      <c r="B142" s="28" t="s">
+      <c r="A142" s="28"/>
+      <c r="B142" s="21" t="s">
+        <v>319</v>
+      </c>
+      <c r="C142" s="10" t="s">
+        <v>363</v>
+      </c>
+      <c r="D142" s="3" t="s">
         <v>320</v>
       </c>
-      <c r="C142" s="10" t="s">
-        <v>364</v>
-      </c>
-      <c r="D142" s="3" t="s">
+      <c r="E142" s="3" t="s">
         <v>321</v>
       </c>
-      <c r="E142" s="3" t="s">
+      <c r="F142" s="3" t="s">
         <v>322</v>
       </c>
-      <c r="F142" s="3" t="s">
+    </row>
+    <row r="143" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A143" s="28"/>
+      <c r="B143" s="22"/>
+      <c r="C143" s="10" t="s">
+        <v>363</v>
+      </c>
+      <c r="D143" s="3" t="s">
         <v>323</v>
       </c>
-    </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A143" s="22"/>
-      <c r="B143" s="29"/>
-      <c r="C143" s="10" t="s">
-        <v>364</v>
-      </c>
-      <c r="D143" s="3" t="s">
+      <c r="E143" s="3" t="s">
         <v>324</v>
       </c>
-      <c r="E143" s="3" t="s">
-        <v>325</v>
-      </c>
       <c r="F143" s="3" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A144" s="22"/>
-      <c r="B144" s="30"/>
+      <c r="A144" s="28"/>
+      <c r="B144" s="23"/>
       <c r="C144" s="10"/>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A145" s="22"/>
+      <c r="A145" s="28"/>
       <c r="B145" s="24" t="s">
         <v>4</v>
       </c>
@@ -3935,7 +3932,7 @@
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A146" s="22"/>
+      <c r="A146" s="28"/>
       <c r="B146" s="25"/>
       <c r="C146" s="14" t="s">
         <v>4</v>
@@ -3951,7 +3948,7 @@
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A147" s="22"/>
+      <c r="A147" s="28"/>
       <c r="B147" s="25"/>
       <c r="C147" s="14" t="s">
         <v>4</v>
@@ -3967,7 +3964,7 @@
       </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A148" s="22"/>
+      <c r="A148" s="28"/>
       <c r="B148" s="25"/>
       <c r="C148" s="14" t="s">
         <v>4</v>
@@ -3983,7 +3980,7 @@
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A149" s="22"/>
+      <c r="A149" s="28"/>
       <c r="B149" s="25"/>
       <c r="C149" s="14" t="s">
         <v>4</v>
@@ -3999,7 +3996,7 @@
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A150" s="22"/>
+      <c r="A150" s="28"/>
       <c r="B150" s="25"/>
       <c r="C150" s="14" t="s">
         <v>4</v>
@@ -4015,7 +4012,7 @@
       </c>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A151" s="22"/>
+      <c r="A151" s="28"/>
       <c r="B151" s="25"/>
       <c r="C151" s="14" t="s">
         <v>4</v>
@@ -4031,7 +4028,7 @@
       </c>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A152" s="22"/>
+      <c r="A152" s="28"/>
       <c r="B152" s="25"/>
       <c r="C152" s="14" t="s">
         <v>4</v>
@@ -4047,7 +4044,7 @@
       </c>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A153" s="22"/>
+      <c r="A153" s="28"/>
       <c r="B153" s="25"/>
       <c r="C153" s="14" t="s">
         <v>4</v>
@@ -4063,17 +4060,17 @@
       </c>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A154" s="22"/>
+      <c r="A154" s="28"/>
       <c r="B154" s="26"/>
       <c r="C154" s="14"/>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A155" s="22"/>
+      <c r="A155" s="28"/>
       <c r="B155" s="24" t="s">
         <v>5</v>
       </c>
       <c r="C155" s="13" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="D155" s="6" t="s">
         <v>19</v>
@@ -4086,10 +4083,10 @@
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A156" s="22"/>
+      <c r="A156" s="28"/>
       <c r="B156" s="25"/>
       <c r="C156" s="14" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="D156" s="3" t="s">
         <v>31</v>
@@ -4102,10 +4099,10 @@
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A157" s="22"/>
+      <c r="A157" s="28"/>
       <c r="B157" s="25"/>
       <c r="C157" s="14" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="D157" s="3" t="s">
         <v>43</v>
@@ -4118,10 +4115,10 @@
       </c>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A158" s="22"/>
+      <c r="A158" s="28"/>
       <c r="B158" s="25"/>
       <c r="C158" s="14" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="D158" s="3" t="s">
         <v>63</v>
@@ -4134,10 +4131,10 @@
       </c>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A159" s="22"/>
+      <c r="A159" s="28"/>
       <c r="B159" s="25"/>
       <c r="C159" s="14" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="D159" s="3" t="s">
         <v>77</v>
@@ -4150,10 +4147,10 @@
       </c>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A160" s="22"/>
+      <c r="A160" s="28"/>
       <c r="B160" s="25"/>
       <c r="C160" s="14" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="D160" s="3" t="s">
         <v>83</v>
@@ -4166,10 +4163,10 @@
       </c>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A161" s="22"/>
+      <c r="A161" s="28"/>
       <c r="B161" s="25"/>
       <c r="C161" s="14" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="D161" s="3" t="s">
         <v>117</v>
@@ -4182,10 +4179,10 @@
       </c>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A162" s="22"/>
+      <c r="A162" s="28"/>
       <c r="B162" s="25"/>
       <c r="C162" s="14" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="D162" s="3" t="s">
         <v>89</v>
@@ -4198,10 +4195,10 @@
       </c>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A163" s="22"/>
+      <c r="A163" s="28"/>
       <c r="B163" s="25"/>
       <c r="C163" s="14" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="D163" s="3" t="s">
         <v>109</v>
@@ -4214,19 +4211,19 @@
       </c>
     </row>
     <row r="164" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A164" s="23"/>
-      <c r="B164" s="27"/>
+      <c r="A164" s="29"/>
+      <c r="B164" s="31"/>
       <c r="C164" s="14"/>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A165" s="21" t="s">
+      <c r="A165" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="B165" s="31" t="s">
+      <c r="B165" s="30" t="s">
         <v>15</v>
       </c>
       <c r="C165" s="9" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="D165" s="4" t="s">
         <v>52</v>
@@ -4239,10 +4236,10 @@
       </c>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A166" s="22"/>
-      <c r="B166" s="29"/>
+      <c r="A166" s="28"/>
+      <c r="B166" s="22"/>
       <c r="C166" s="10" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="D166" s="3" t="s">
         <v>148</v>
@@ -4255,10 +4252,10 @@
       </c>
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A167" s="22"/>
-      <c r="B167" s="29"/>
+      <c r="A167" s="28"/>
+      <c r="B167" s="22"/>
       <c r="C167" s="10" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="D167" s="3" t="s">
         <v>72</v>
@@ -4271,75 +4268,75 @@
       </c>
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A168" s="22"/>
-      <c r="B168" s="30"/>
+      <c r="A168" s="28"/>
+      <c r="B168" s="23"/>
       <c r="C168" s="12"/>
       <c r="D168" s="7"/>
       <c r="E168" s="7"/>
       <c r="F168" s="7"/>
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A169" s="22"/>
-      <c r="B169" s="28" t="s">
+      <c r="A169" s="28"/>
+      <c r="B169" s="21" t="s">
+        <v>202</v>
+      </c>
+      <c r="C169" s="10" t="s">
+        <v>365</v>
+      </c>
+      <c r="D169" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="C169" s="10" t="s">
-        <v>366</v>
-      </c>
-      <c r="D169" s="3" t="s">
+      <c r="E169" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="E169" s="3" t="s">
+      <c r="F169" s="3" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="170" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A170" s="28"/>
+      <c r="B170" s="22"/>
+      <c r="C170" s="10" t="s">
+        <v>365</v>
+      </c>
+      <c r="D170" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="E170" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="F169" s="3" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="170" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A170" s="22"/>
-      <c r="B170" s="29"/>
-      <c r="C170" s="10" t="s">
-        <v>366</v>
-      </c>
-      <c r="D170" s="3" t="s">
+      <c r="F170" s="3" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="171" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A171" s="28"/>
+      <c r="B171" s="22"/>
+      <c r="C171" s="10" t="s">
+        <v>365</v>
+      </c>
+      <c r="D171" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="E170" s="3" t="s">
+      <c r="E171" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="F170" s="3" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="171" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A171" s="22"/>
-      <c r="B171" s="29"/>
-      <c r="C171" s="10" t="s">
-        <v>366</v>
-      </c>
-      <c r="D171" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="E171" s="3" t="s">
-        <v>207</v>
-      </c>
       <c r="F171" s="3" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A172" s="22"/>
-      <c r="B172" s="30"/>
+      <c r="A172" s="28"/>
+      <c r="B172" s="23"/>
       <c r="C172" s="10"/>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A173" s="22"/>
-      <c r="B173" s="28" t="s">
+      <c r="A173" s="28"/>
+      <c r="B173" s="21" t="s">
         <v>17</v>
       </c>
       <c r="C173" s="11" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="D173" s="6" t="s">
         <v>54</v>
@@ -4352,10 +4349,10 @@
       </c>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A174" s="22"/>
-      <c r="B174" s="29"/>
+      <c r="A174" s="28"/>
+      <c r="B174" s="22"/>
       <c r="C174" s="10" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="D174" s="3" t="s">
         <v>73</v>
@@ -4368,20 +4365,20 @@
       </c>
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A175" s="22"/>
-      <c r="B175" s="30"/>
+      <c r="A175" s="28"/>
+      <c r="B175" s="23"/>
       <c r="C175" s="12"/>
       <c r="D175" s="7"/>
       <c r="E175" s="7"/>
       <c r="F175" s="7"/>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A176" s="22"/>
-      <c r="B176" s="28" t="s">
+      <c r="A176" s="28"/>
+      <c r="B176" s="21" t="s">
         <v>174</v>
       </c>
       <c r="C176" s="11" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="D176" s="6" t="s">
         <v>173</v>
@@ -4394,10 +4391,10 @@
       </c>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A177" s="22"/>
-      <c r="B177" s="29"/>
+      <c r="A177" s="28"/>
+      <c r="B177" s="22"/>
       <c r="C177" s="10" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="D177" s="3" t="s">
         <v>175</v>
@@ -4410,175 +4407,175 @@
       </c>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A178" s="22"/>
-      <c r="B178" s="30"/>
+      <c r="A178" s="28"/>
+      <c r="B178" s="23"/>
       <c r="C178" s="12"/>
       <c r="D178" s="7"/>
       <c r="E178" s="7"/>
       <c r="F178" s="7"/>
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A179" s="22"/>
-      <c r="B179" s="28" t="s">
+      <c r="A179" s="28"/>
+      <c r="B179" s="21" t="s">
+        <v>270</v>
+      </c>
+      <c r="C179" s="10" t="s">
+        <v>367</v>
+      </c>
+      <c r="D179" s="3" t="s">
         <v>271</v>
       </c>
-      <c r="C179" s="10" t="s">
-        <v>368</v>
-      </c>
-      <c r="D179" s="3" t="s">
+      <c r="E179" s="3" t="s">
         <v>272</v>
       </c>
-      <c r="E179" s="3" t="s">
+      <c r="F179" s="3" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="180" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A180" s="28"/>
+      <c r="B180" s="22"/>
+      <c r="C180" s="10" t="s">
+        <v>367</v>
+      </c>
+      <c r="D180" s="3" t="s">
         <v>273</v>
       </c>
-      <c r="F179" s="3" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="180" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A180" s="22"/>
-      <c r="B180" s="29"/>
-      <c r="C180" s="10" t="s">
-        <v>368</v>
-      </c>
-      <c r="D180" s="3" t="s">
+      <c r="E180" s="3" t="s">
         <v>274</v>
       </c>
-      <c r="E180" s="3" t="s">
-        <v>275</v>
-      </c>
       <c r="F180" s="3" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A181" s="22"/>
-      <c r="B181" s="30"/>
+      <c r="A181" s="28"/>
+      <c r="B181" s="23"/>
       <c r="C181" s="12"/>
       <c r="D181" s="7"/>
       <c r="E181" s="7"/>
       <c r="F181" s="7"/>
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A182" s="22"/>
-      <c r="B182" s="28" t="s">
+      <c r="A182" s="28"/>
+      <c r="B182" s="21" t="s">
+        <v>325</v>
+      </c>
+      <c r="C182" s="11" t="s">
+        <v>368</v>
+      </c>
+      <c r="D182" s="6" t="s">
         <v>326</v>
       </c>
-      <c r="C182" s="11" t="s">
-        <v>369</v>
-      </c>
-      <c r="D182" s="6" t="s">
+      <c r="E182" s="6" t="s">
         <v>327</v>
       </c>
-      <c r="E182" s="6" t="s">
+      <c r="F182" s="6" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="183" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A183" s="28"/>
+      <c r="B183" s="22"/>
+      <c r="C183" s="10" t="s">
+        <v>368</v>
+      </c>
+      <c r="D183" s="3" t="s">
         <v>328</v>
       </c>
-      <c r="F182" s="6" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="183" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A183" s="22"/>
-      <c r="B183" s="29"/>
-      <c r="C183" s="10" t="s">
-        <v>369</v>
-      </c>
-      <c r="D183" s="3" t="s">
+      <c r="E183" s="3" t="s">
         <v>329</v>
       </c>
-      <c r="E183" s="3" t="s">
-        <v>330</v>
-      </c>
       <c r="F183" s="3" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A184" s="22"/>
-      <c r="B184" s="30"/>
+      <c r="A184" s="28"/>
+      <c r="B184" s="23"/>
       <c r="C184" s="12"/>
       <c r="D184" s="7"/>
       <c r="E184" s="7"/>
       <c r="F184" s="7"/>
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A185" s="22"/>
-      <c r="B185" s="28" t="s">
+      <c r="A185" s="28"/>
+      <c r="B185" s="21" t="s">
+        <v>330</v>
+      </c>
+      <c r="C185" s="11" t="s">
+        <v>369</v>
+      </c>
+      <c r="D185" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="C185" s="11" t="s">
-        <v>370</v>
-      </c>
-      <c r="D185" s="6" t="s">
+      <c r="E185" s="6" t="s">
         <v>332</v>
       </c>
-      <c r="E185" s="6" t="s">
+      <c r="F185" s="6" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="186" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A186" s="28"/>
+      <c r="B186" s="22"/>
+      <c r="C186" s="10" t="s">
+        <v>369</v>
+      </c>
+      <c r="D186" s="3" t="s">
         <v>333</v>
       </c>
-      <c r="F185" s="6" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="186" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A186" s="22"/>
-      <c r="B186" s="29"/>
-      <c r="C186" s="10" t="s">
-        <v>370</v>
-      </c>
-      <c r="D186" s="3" t="s">
+      <c r="E186" s="3" t="s">
         <v>334</v>
       </c>
-      <c r="E186" s="3" t="s">
-        <v>335</v>
-      </c>
       <c r="F186" s="3" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A187" s="22"/>
-      <c r="B187" s="30"/>
+      <c r="A187" s="28"/>
+      <c r="B187" s="23"/>
       <c r="C187" s="12"/>
       <c r="D187" s="7"/>
       <c r="E187" s="7"/>
       <c r="F187" s="7"/>
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A188" s="22"/>
-      <c r="B188" s="29" t="s">
+      <c r="A188" s="28"/>
+      <c r="B188" s="22" t="s">
+        <v>390</v>
+      </c>
+      <c r="C188" s="10" t="s">
+        <v>395</v>
+      </c>
+      <c r="D188" s="3" t="s">
         <v>391</v>
       </c>
-      <c r="C188" s="10" t="s">
-        <v>396</v>
-      </c>
-      <c r="D188" s="3" t="s">
+      <c r="E188" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="F188" s="3" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="189" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A189" s="28"/>
+      <c r="B189" s="22"/>
+      <c r="C189" s="10" t="s">
+        <v>395</v>
+      </c>
+      <c r="D189" s="3" t="s">
         <v>392</v>
       </c>
-      <c r="E188" s="3" t="s">
+      <c r="E189" s="3" t="s">
         <v>394</v>
       </c>
-      <c r="F188" s="3" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="189" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A189" s="22"/>
-      <c r="B189" s="29"/>
-      <c r="C189" s="10" t="s">
-        <v>396</v>
-      </c>
-      <c r="D189" s="3" t="s">
-        <v>393</v>
-      </c>
-      <c r="E189" s="3" t="s">
-        <v>395</v>
-      </c>
       <c r="F189" s="3" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="190" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A190" s="23"/>
+      <c r="A190" s="29"/>
       <c r="B190" s="20"/>
       <c r="C190" s="18"/>
       <c r="D190" s="8"/>
@@ -4586,14 +4583,14 @@
       <c r="F190" s="8"/>
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A191" s="21" t="s">
+      <c r="A191" s="27" t="s">
         <v>85</v>
       </c>
-      <c r="B191" s="31" t="s">
+      <c r="B191" s="30" t="s">
         <v>7</v>
       </c>
       <c r="C191" s="9" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="D191" s="4" t="s">
         <v>95</v>
@@ -4606,10 +4603,10 @@
       </c>
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A192" s="22"/>
-      <c r="B192" s="29"/>
+      <c r="A192" s="28"/>
+      <c r="B192" s="22"/>
       <c r="C192" s="10" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="D192" s="3" t="s">
         <v>96</v>
@@ -4622,20 +4619,20 @@
       </c>
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A193" s="22"/>
-      <c r="B193" s="30"/>
+      <c r="A193" s="28"/>
+      <c r="B193" s="23"/>
       <c r="C193" s="12"/>
       <c r="D193" s="7"/>
       <c r="E193" s="7"/>
       <c r="F193" s="7"/>
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A194" s="22"/>
-      <c r="B194" s="28" t="s">
+      <c r="A194" s="28"/>
+      <c r="B194" s="21" t="s">
         <v>105</v>
       </c>
       <c r="C194" s="10" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="D194" s="3" t="s">
         <v>87</v>
@@ -4648,26 +4645,26 @@
       </c>
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A195" s="22"/>
-      <c r="B195" s="29"/>
+      <c r="A195" s="28"/>
+      <c r="B195" s="22"/>
       <c r="C195" s="10" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="D195" s="3" t="s">
         <v>103</v>
       </c>
       <c r="E195" s="3" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F195" s="3" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A196" s="22"/>
-      <c r="B196" s="29"/>
+      <c r="A196" s="28"/>
+      <c r="B196" s="22"/>
       <c r="C196" s="10" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="D196" s="3" t="s">
         <v>99</v>
@@ -4680,10 +4677,10 @@
       </c>
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A197" s="22"/>
-      <c r="B197" s="29"/>
+      <c r="A197" s="28"/>
+      <c r="B197" s="22"/>
       <c r="C197" s="10" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="D197" s="3" t="s">
         <v>101</v>
@@ -4696,10 +4693,10 @@
       </c>
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A198" s="22"/>
-      <c r="B198" s="29"/>
+      <c r="A198" s="28"/>
+      <c r="B198" s="22"/>
       <c r="C198" s="10" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="D198" s="3" t="s">
         <v>104</v>
@@ -4712,10 +4709,10 @@
       </c>
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A199" s="22"/>
-      <c r="B199" s="29"/>
+      <c r="A199" s="28"/>
+      <c r="B199" s="22"/>
       <c r="C199" s="10" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="D199" s="3" t="s">
         <v>112</v>
@@ -4728,17 +4725,17 @@
       </c>
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A200" s="22"/>
-      <c r="B200" s="30"/>
+      <c r="A200" s="28"/>
+      <c r="B200" s="23"/>
       <c r="C200" s="10"/>
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A201" s="22"/>
-      <c r="B201" s="28" t="s">
+      <c r="A201" s="28"/>
+      <c r="B201" s="21" t="s">
         <v>126</v>
       </c>
       <c r="C201" s="11" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="D201" s="6" t="s">
         <v>123</v>
@@ -4751,10 +4748,10 @@
       </c>
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A202" s="22"/>
-      <c r="B202" s="29"/>
+      <c r="A202" s="28"/>
+      <c r="B202" s="22"/>
       <c r="C202" s="10" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="D202" s="3" t="s">
         <v>124</v>
@@ -4767,10 +4764,10 @@
       </c>
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A203" s="22"/>
-      <c r="B203" s="29"/>
+      <c r="A203" s="28"/>
+      <c r="B203" s="22"/>
       <c r="C203" s="10" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="D203" s="3" t="s">
         <v>135</v>
@@ -4783,10 +4780,10 @@
       </c>
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A204" s="22"/>
-      <c r="B204" s="29"/>
+      <c r="A204" s="28"/>
+      <c r="B204" s="22"/>
       <c r="C204" s="10" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="D204" s="3" t="s">
         <v>125</v>
@@ -4799,58 +4796,58 @@
       </c>
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A205" s="22"/>
-      <c r="B205" s="29"/>
+      <c r="A205" s="28"/>
+      <c r="B205" s="22"/>
       <c r="C205" s="10" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="D205" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="E205" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="E205" s="3" t="s">
-        <v>213</v>
-      </c>
       <c r="F205" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A206" s="22"/>
-      <c r="B206" s="29"/>
+      <c r="A206" s="28"/>
+      <c r="B206" s="22"/>
       <c r="C206" s="10" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="D206" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="E206" s="3" t="s">
         <v>227</v>
       </c>
-      <c r="E206" s="3" t="s">
+      <c r="F206" s="3" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="207" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A207" s="28"/>
+      <c r="B207" s="22"/>
+      <c r="C207" s="10" t="s">
+        <v>371</v>
+      </c>
+      <c r="D207" s="3" t="s">
         <v>228</v>
       </c>
-      <c r="F206" s="3" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="207" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A207" s="22"/>
-      <c r="B207" s="29"/>
-      <c r="C207" s="10" t="s">
-        <v>372</v>
-      </c>
-      <c r="D207" s="3" t="s">
+      <c r="E207" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="E207" s="3" t="s">
-        <v>230</v>
-      </c>
       <c r="F207" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="208" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A208" s="22"/>
-      <c r="B208" s="29"/>
+      <c r="A208" s="28"/>
+      <c r="B208" s="22"/>
       <c r="C208" s="10" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="D208" s="3" t="s">
         <v>137</v>
@@ -4863,10 +4860,10 @@
       </c>
     </row>
     <row r="209" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A209" s="22"/>
-      <c r="B209" s="29"/>
+      <c r="A209" s="28"/>
+      <c r="B209" s="22"/>
       <c r="C209" s="10" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="D209" s="3" t="s">
         <v>141</v>
@@ -4879,10 +4876,10 @@
       </c>
     </row>
     <row r="210" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A210" s="22"/>
-      <c r="B210" s="29"/>
+      <c r="A210" s="28"/>
+      <c r="B210" s="22"/>
       <c r="C210" s="10" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="D210" s="3" t="s">
         <v>122</v>
@@ -4895,10 +4892,10 @@
       </c>
     </row>
     <row r="211" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A211" s="22"/>
-      <c r="B211" s="29"/>
+      <c r="A211" s="28"/>
+      <c r="B211" s="22"/>
       <c r="C211" s="10" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="D211" s="3" t="s">
         <v>178</v>
@@ -4911,10 +4908,10 @@
       </c>
     </row>
     <row r="212" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A212" s="22"/>
-      <c r="B212" s="29"/>
+      <c r="A212" s="28"/>
+      <c r="B212" s="22"/>
       <c r="C212" s="10" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="D212" s="3" t="s">
         <v>181</v>
@@ -4927,161 +4924,161 @@
       </c>
     </row>
     <row r="213" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A213" s="22"/>
-      <c r="B213" s="29"/>
+      <c r="A213" s="28"/>
+      <c r="B213" s="22"/>
       <c r="C213" s="10" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="D213" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="E213" s="3" t="s">
         <v>276</v>
-      </c>
-      <c r="E213" s="3" t="s">
-        <v>277</v>
       </c>
       <c r="F213" s="3" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="214" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A214" s="22"/>
-      <c r="B214" s="29"/>
+      <c r="A214" s="28"/>
+      <c r="B214" s="22"/>
       <c r="C214" s="10" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="D214" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="E214" s="3" t="s">
         <v>278</v>
-      </c>
-      <c r="E214" s="3" t="s">
-        <v>279</v>
       </c>
       <c r="F214" s="3" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="215" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A215" s="22"/>
-      <c r="B215" s="29"/>
+      <c r="A215" s="28"/>
+      <c r="B215" s="22"/>
       <c r="C215" s="10" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="D215" s="3" t="s">
         <v>178</v>
       </c>
       <c r="E215" s="3" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="F215" s="3" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="216" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A216" s="22"/>
-      <c r="B216" s="29"/>
+      <c r="A216" s="28"/>
+      <c r="B216" s="22"/>
       <c r="C216" s="10" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="D216" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="E216" s="3" t="s">
         <v>337</v>
-      </c>
-      <c r="E216" s="3" t="s">
-        <v>338</v>
       </c>
       <c r="F216" s="3" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="217" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A217" s="22"/>
-      <c r="B217" s="29"/>
+      <c r="A217" s="28"/>
+      <c r="B217" s="22"/>
       <c r="C217" s="10" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="D217" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="E217" s="3" t="s">
         <v>339</v>
-      </c>
-      <c r="E217" s="3" t="s">
-        <v>340</v>
       </c>
       <c r="F217" s="3" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="218" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A218" s="22"/>
-      <c r="B218" s="29"/>
+      <c r="A218" s="28"/>
+      <c r="B218" s="22"/>
       <c r="C218" s="10" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="D218" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="E218" s="3" t="s">
         <v>341</v>
-      </c>
-      <c r="E218" s="3" t="s">
-        <v>342</v>
       </c>
       <c r="F218" s="3" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="219" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A219" s="22"/>
-      <c r="B219" s="29"/>
+      <c r="A219" s="28"/>
+      <c r="B219" s="22"/>
       <c r="C219" s="10" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="D219" s="3" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="E219" s="3" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="F219" s="3" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="220" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A220" s="22"/>
-      <c r="B220" s="29"/>
+      <c r="A220" s="28"/>
+      <c r="B220" s="22"/>
       <c r="C220" s="10" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="D220" s="3" t="s">
+        <v>386</v>
+      </c>
+      <c r="E220" s="3" t="s">
         <v>387</v>
-      </c>
-      <c r="E220" s="3" t="s">
-        <v>388</v>
       </c>
       <c r="F220" s="3" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="221" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A221" s="22"/>
-      <c r="B221" s="29"/>
+      <c r="A221" s="28"/>
+      <c r="B221" s="22"/>
       <c r="C221" s="10" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="D221" s="3" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="E221" s="3" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="F221" s="3" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="222" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A222" s="22"/>
-      <c r="B222" s="30"/>
+      <c r="A222" s="28"/>
+      <c r="B222" s="23"/>
       <c r="C222" s="10"/>
     </row>
     <row r="223" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A223" s="22"/>
-      <c r="B223" s="28" t="s">
+      <c r="A223" s="28"/>
+      <c r="B223" s="21" t="s">
         <v>142</v>
       </c>
       <c r="C223" s="11" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="D223" s="6" t="s">
         <v>144</v>
@@ -5094,26 +5091,26 @@
       </c>
     </row>
     <row r="224" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A224" s="22"/>
-      <c r="B224" s="29"/>
+      <c r="A224" s="28"/>
+      <c r="B224" s="22"/>
       <c r="C224" s="10" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="D224" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="E224" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="E224" s="3" t="s">
+      <c r="F224" s="3" t="s">
         <v>215</v>
       </c>
-      <c r="F224" s="3" t="s">
-        <v>216</v>
-      </c>
     </row>
     <row r="225" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A225" s="22"/>
-      <c r="B225" s="29"/>
+      <c r="A225" s="28"/>
+      <c r="B225" s="22"/>
       <c r="C225" s="10" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="D225" s="3" t="s">
         <v>145</v>
@@ -5126,10 +5123,10 @@
       </c>
     </row>
     <row r="226" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A226" s="22"/>
-      <c r="B226" s="29"/>
+      <c r="A226" s="28"/>
+      <c r="B226" s="22"/>
       <c r="C226" s="10" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="D226" s="3" t="s">
         <v>182</v>
@@ -5142,119 +5139,119 @@
       </c>
     </row>
     <row r="227" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A227" s="22"/>
-      <c r="B227" s="29"/>
+      <c r="A227" s="28"/>
+      <c r="B227" s="22"/>
       <c r="C227" s="10" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="D227" s="3" t="s">
         <v>184</v>
       </c>
       <c r="E227" s="3" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F227" s="3" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="228" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A228" s="22"/>
-      <c r="B228" s="29"/>
+      <c r="A228" s="28"/>
+      <c r="B228" s="22"/>
       <c r="C228" s="10" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="D228" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="E228" s="3" t="s">
         <v>280</v>
-      </c>
-      <c r="E228" s="3" t="s">
-        <v>281</v>
       </c>
       <c r="F228" s="3" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="229" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A229" s="22"/>
-      <c r="B229" s="29"/>
+      <c r="A229" s="28"/>
+      <c r="B229" s="22"/>
       <c r="C229" s="10" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="D229" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="E229" s="3" t="s">
         <v>282</v>
-      </c>
-      <c r="E229" s="3" t="s">
-        <v>283</v>
       </c>
       <c r="F229" s="3" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="230" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A230" s="22"/>
-      <c r="B230" s="29"/>
+      <c r="A230" s="28"/>
+      <c r="B230" s="22"/>
       <c r="C230" s="10" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="D230" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="E230" s="3" t="s">
         <v>389</v>
-      </c>
-      <c r="E230" s="3" t="s">
-        <v>390</v>
       </c>
       <c r="F230" s="3" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="231" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A231" s="22"/>
-      <c r="B231" s="29"/>
+      <c r="A231" s="28"/>
+      <c r="B231" s="22"/>
       <c r="C231" s="10" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="D231" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="E231" s="3" t="s">
         <v>343</v>
-      </c>
-      <c r="E231" s="3" t="s">
-        <v>344</v>
       </c>
       <c r="F231" s="3" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="232" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A232" s="22"/>
-      <c r="B232" s="30"/>
+      <c r="A232" s="28"/>
+      <c r="B232" s="23"/>
       <c r="C232" s="10"/>
     </row>
     <row r="233" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A233" s="22"/>
-      <c r="B233" s="28" t="s">
+      <c r="A233" s="28"/>
+      <c r="B233" s="21" t="s">
+        <v>232</v>
+      </c>
+      <c r="C233" s="11" t="s">
+        <v>373</v>
+      </c>
+      <c r="D233" s="6" t="s">
         <v>233</v>
       </c>
-      <c r="C233" s="11" t="s">
-        <v>374</v>
-      </c>
-      <c r="D233" s="6" t="s">
+      <c r="E233" s="6" t="s">
         <v>234</v>
-      </c>
-      <c r="E233" s="6" t="s">
-        <v>235</v>
       </c>
       <c r="F233" s="6" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="234" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A234" s="22"/>
-      <c r="B234" s="29"/>
+      <c r="A234" s="28"/>
+      <c r="B234" s="22"/>
       <c r="C234" s="10" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="D234" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="E234" s="3" t="s">
         <v>236</v>
-      </c>
-      <c r="E234" s="3" t="s">
-        <v>237</v>
       </c>
       <c r="F234" s="3" t="s">
         <v>132</v>
@@ -5262,11 +5259,15 @@
     </row>
   </sheetData>
   <mergeCells count="36">
-    <mergeCell ref="B44:B55"/>
-    <mergeCell ref="B56:B68"/>
-    <mergeCell ref="B79:B89"/>
-    <mergeCell ref="B90:B99"/>
-    <mergeCell ref="B233:B234"/>
+    <mergeCell ref="A165:A190"/>
+    <mergeCell ref="B173:B175"/>
+    <mergeCell ref="B165:B168"/>
+    <mergeCell ref="B169:B172"/>
+    <mergeCell ref="B179:B181"/>
+    <mergeCell ref="B176:B178"/>
+    <mergeCell ref="B182:B184"/>
+    <mergeCell ref="B188:B189"/>
+    <mergeCell ref="B185:B187"/>
     <mergeCell ref="A191:A234"/>
     <mergeCell ref="A2:A100"/>
     <mergeCell ref="B2:B11"/>
@@ -5283,19 +5284,15 @@
     <mergeCell ref="B23:B33"/>
     <mergeCell ref="B34:B43"/>
     <mergeCell ref="A133:A164"/>
+    <mergeCell ref="B44:B55"/>
+    <mergeCell ref="B56:B68"/>
+    <mergeCell ref="B79:B89"/>
+    <mergeCell ref="B90:B99"/>
+    <mergeCell ref="B233:B234"/>
     <mergeCell ref="B145:B154"/>
     <mergeCell ref="B155:B164"/>
-    <mergeCell ref="A165:A190"/>
-    <mergeCell ref="B173:B175"/>
-    <mergeCell ref="B165:B168"/>
-    <mergeCell ref="B169:B172"/>
-    <mergeCell ref="B179:B181"/>
-    <mergeCell ref="B176:B178"/>
-    <mergeCell ref="B182:B184"/>
     <mergeCell ref="B139:B141"/>
     <mergeCell ref="B142:B144"/>
-    <mergeCell ref="B188:B189"/>
-    <mergeCell ref="B185:B187"/>
     <mergeCell ref="B136:B138"/>
     <mergeCell ref="B133:B135"/>
   </mergeCells>

--- a/Vergleich_Ergebnisse_Vorlage.xlsx
+++ b/Vergleich_Ergebnisse_Vorlage.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hem38994\Documents\GitHub\FENES_P2X\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE1DFC14-19D6-4332-9B63-BD9B2579E10A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B248495-0F8F-4F12-8A13-480A412514F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="854" uniqueCount="399">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="854" uniqueCount="400">
   <si>
     <t>PEM Elektrolyse</t>
   </si>
@@ -1235,6 +1235,9 @@
   </si>
   <si>
     <t>Wasserstoffproduktion</t>
+  </si>
+  <si>
+    <t>€ / kg a</t>
   </si>
 </sst>
 </file>
@@ -1382,6 +1385,15 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -1391,31 +1403,22 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1731,10 +1734,10 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="27" t="s">
+      <c r="A2" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="30" t="s">
+      <c r="B2" s="27" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="10" t="s">
@@ -1751,8 +1754,8 @@
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="28"/>
-      <c r="B3" s="22"/>
+      <c r="A3" s="22"/>
+      <c r="B3" s="25"/>
       <c r="C3" s="10" t="s">
         <v>349</v>
       </c>
@@ -1767,8 +1770,8 @@
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="28"/>
-      <c r="B4" s="22"/>
+      <c r="A4" s="22"/>
+      <c r="B4" s="25"/>
       <c r="C4" s="10" t="s">
         <v>349</v>
       </c>
@@ -1783,8 +1786,8 @@
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="28"/>
-      <c r="B5" s="22"/>
+      <c r="A5" s="22"/>
+      <c r="B5" s="25"/>
       <c r="C5" s="10" t="s">
         <v>349</v>
       </c>
@@ -1799,8 +1802,8 @@
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="28"/>
-      <c r="B6" s="22"/>
+      <c r="A6" s="22"/>
+      <c r="B6" s="25"/>
       <c r="C6" s="10" t="s">
         <v>349</v>
       </c>
@@ -1815,8 +1818,8 @@
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" s="28"/>
-      <c r="B7" s="22"/>
+      <c r="A7" s="22"/>
+      <c r="B7" s="25"/>
       <c r="C7" s="10" t="s">
         <v>349</v>
       </c>
@@ -1831,8 +1834,8 @@
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="28"/>
-      <c r="B8" s="22"/>
+      <c r="A8" s="22"/>
+      <c r="B8" s="25"/>
       <c r="C8" s="10" t="s">
         <v>349</v>
       </c>
@@ -1847,8 +1850,8 @@
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" s="28"/>
-      <c r="B9" s="22"/>
+      <c r="A9" s="22"/>
+      <c r="B9" s="25"/>
       <c r="C9" s="10" t="s">
         <v>349</v>
       </c>
@@ -1863,8 +1866,8 @@
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="28"/>
-      <c r="B10" s="22"/>
+      <c r="A10" s="22"/>
+      <c r="B10" s="25"/>
       <c r="C10" s="10" t="s">
         <v>349</v>
       </c>
@@ -1879,13 +1882,13 @@
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="28"/>
-      <c r="B11" s="23"/>
+      <c r="A11" s="22"/>
+      <c r="B11" s="26"/>
       <c r="C11" s="10"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="28"/>
-      <c r="B12" s="21" t="s">
+      <c r="A12" s="22"/>
+      <c r="B12" s="24" t="s">
         <v>150</v>
       </c>
       <c r="C12" s="11" t="s">
@@ -1902,8 +1905,8 @@
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13" s="28"/>
-      <c r="B13" s="22"/>
+      <c r="A13" s="22"/>
+      <c r="B13" s="25"/>
       <c r="C13" s="10" t="s">
         <v>350</v>
       </c>
@@ -1918,8 +1921,8 @@
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14" s="28"/>
-      <c r="B14" s="22"/>
+      <c r="A14" s="22"/>
+      <c r="B14" s="25"/>
       <c r="C14" s="10" t="s">
         <v>350</v>
       </c>
@@ -1934,8 +1937,8 @@
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A15" s="28"/>
-      <c r="B15" s="22"/>
+      <c r="A15" s="22"/>
+      <c r="B15" s="25"/>
       <c r="C15" s="10" t="s">
         <v>350</v>
       </c>
@@ -1950,8 +1953,8 @@
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A16" s="28"/>
-      <c r="B16" s="22"/>
+      <c r="A16" s="22"/>
+      <c r="B16" s="25"/>
       <c r="C16" s="10" t="s">
         <v>350</v>
       </c>
@@ -1966,8 +1969,8 @@
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="28"/>
-      <c r="B17" s="22"/>
+      <c r="A17" s="22"/>
+      <c r="B17" s="25"/>
       <c r="C17" s="10" t="s">
         <v>350</v>
       </c>
@@ -1982,8 +1985,8 @@
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="28"/>
-      <c r="B18" s="22"/>
+      <c r="A18" s="22"/>
+      <c r="B18" s="25"/>
       <c r="C18" s="10" t="s">
         <v>350</v>
       </c>
@@ -1998,8 +2001,8 @@
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" s="28"/>
-      <c r="B19" s="22"/>
+      <c r="A19" s="22"/>
+      <c r="B19" s="25"/>
       <c r="C19" s="10" t="s">
         <v>350</v>
       </c>
@@ -2014,8 +2017,8 @@
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20" s="28"/>
-      <c r="B20" s="22"/>
+      <c r="A20" s="22"/>
+      <c r="B20" s="25"/>
       <c r="C20" s="10" t="s">
         <v>350</v>
       </c>
@@ -2030,8 +2033,8 @@
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21" s="28"/>
-      <c r="B21" s="22"/>
+      <c r="A21" s="22"/>
+      <c r="B21" s="25"/>
       <c r="C21" s="10" t="s">
         <v>350</v>
       </c>
@@ -2046,13 +2049,13 @@
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22" s="28"/>
-      <c r="B22" s="23"/>
+      <c r="A22" s="22"/>
+      <c r="B22" s="26"/>
       <c r="C22" s="10"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A23" s="28"/>
-      <c r="B23" s="21" t="s">
+      <c r="A23" s="22"/>
+      <c r="B23" s="24" t="s">
         <v>254</v>
       </c>
       <c r="C23" s="11" t="s">
@@ -2069,8 +2072,8 @@
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A24" s="28"/>
-      <c r="B24" s="22"/>
+      <c r="A24" s="22"/>
+      <c r="B24" s="25"/>
       <c r="C24" s="10" t="s">
         <v>351</v>
       </c>
@@ -2085,8 +2088,8 @@
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A25" s="28"/>
-      <c r="B25" s="22"/>
+      <c r="A25" s="22"/>
+      <c r="B25" s="25"/>
       <c r="C25" s="10" t="s">
         <v>351</v>
       </c>
@@ -2101,8 +2104,8 @@
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26" s="28"/>
-      <c r="B26" s="22"/>
+      <c r="A26" s="22"/>
+      <c r="B26" s="25"/>
       <c r="C26" s="10" t="s">
         <v>351</v>
       </c>
@@ -2117,8 +2120,8 @@
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A27" s="28"/>
-      <c r="B27" s="22"/>
+      <c r="A27" s="22"/>
+      <c r="B27" s="25"/>
       <c r="C27" s="10" t="s">
         <v>351</v>
       </c>
@@ -2133,8 +2136,8 @@
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A28" s="28"/>
-      <c r="B28" s="22"/>
+      <c r="A28" s="22"/>
+      <c r="B28" s="25"/>
       <c r="C28" s="10" t="s">
         <v>351</v>
       </c>
@@ -2149,8 +2152,8 @@
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A29" s="28"/>
-      <c r="B29" s="22"/>
+      <c r="A29" s="22"/>
+      <c r="B29" s="25"/>
       <c r="C29" s="10" t="s">
         <v>351</v>
       </c>
@@ -2165,8 +2168,8 @@
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A30" s="28"/>
-      <c r="B30" s="22"/>
+      <c r="A30" s="22"/>
+      <c r="B30" s="25"/>
       <c r="C30" s="10" t="s">
         <v>351</v>
       </c>
@@ -2181,8 +2184,8 @@
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A31" s="28"/>
-      <c r="B31" s="22"/>
+      <c r="A31" s="22"/>
+      <c r="B31" s="25"/>
       <c r="C31" s="10" t="s">
         <v>351</v>
       </c>
@@ -2197,8 +2200,8 @@
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A32" s="28"/>
-      <c r="B32" s="22"/>
+      <c r="A32" s="22"/>
+      <c r="B32" s="25"/>
       <c r="C32" s="10" t="s">
         <v>351</v>
       </c>
@@ -2213,16 +2216,16 @@
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A33" s="28"/>
-      <c r="B33" s="23"/>
+      <c r="A33" s="22"/>
+      <c r="B33" s="26"/>
       <c r="C33" s="12"/>
       <c r="D33" s="7"/>
       <c r="E33" s="7"/>
       <c r="F33" s="7"/>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A34" s="28"/>
-      <c r="B34" s="24" t="s">
+      <c r="A34" s="22"/>
+      <c r="B34" s="28" t="s">
         <v>255</v>
       </c>
       <c r="C34" s="13" t="s">
@@ -2239,8 +2242,8 @@
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A35" s="28"/>
-      <c r="B35" s="25"/>
+      <c r="A35" s="22"/>
+      <c r="B35" s="29"/>
       <c r="C35" s="14" t="s">
         <v>352</v>
       </c>
@@ -2255,8 +2258,8 @@
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A36" s="28"/>
-      <c r="B36" s="25"/>
+      <c r="A36" s="22"/>
+      <c r="B36" s="29"/>
       <c r="C36" s="14" t="s">
         <v>352</v>
       </c>
@@ -2271,8 +2274,8 @@
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A37" s="28"/>
-      <c r="B37" s="25"/>
+      <c r="A37" s="22"/>
+      <c r="B37" s="29"/>
       <c r="C37" s="14" t="s">
         <v>352</v>
       </c>
@@ -2287,8 +2290,8 @@
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A38" s="28"/>
-      <c r="B38" s="25"/>
+      <c r="A38" s="22"/>
+      <c r="B38" s="29"/>
       <c r="C38" s="14" t="s">
         <v>352</v>
       </c>
@@ -2303,8 +2306,8 @@
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A39" s="28"/>
-      <c r="B39" s="25"/>
+      <c r="A39" s="22"/>
+      <c r="B39" s="29"/>
       <c r="C39" s="14" t="s">
         <v>352</v>
       </c>
@@ -2319,8 +2322,8 @@
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A40" s="28"/>
-      <c r="B40" s="25"/>
+      <c r="A40" s="22"/>
+      <c r="B40" s="29"/>
       <c r="C40" s="14" t="s">
         <v>352</v>
       </c>
@@ -2335,8 +2338,8 @@
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A41" s="28"/>
-      <c r="B41" s="25"/>
+      <c r="A41" s="22"/>
+      <c r="B41" s="29"/>
       <c r="C41" s="14" t="s">
         <v>352</v>
       </c>
@@ -2351,8 +2354,8 @@
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A42" s="28"/>
-      <c r="B42" s="25"/>
+      <c r="A42" s="22"/>
+      <c r="B42" s="29"/>
       <c r="C42" s="14" t="s">
         <v>352</v>
       </c>
@@ -2367,16 +2370,16 @@
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A43" s="28"/>
-      <c r="B43" s="26"/>
+      <c r="A43" s="22"/>
+      <c r="B43" s="32"/>
       <c r="C43" s="15"/>
       <c r="D43" s="7"/>
       <c r="E43" s="7"/>
       <c r="F43" s="7"/>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A44" s="28"/>
-      <c r="B44" s="21" t="s">
+      <c r="A44" s="22"/>
+      <c r="B44" s="24" t="s">
         <v>283</v>
       </c>
       <c r="C44" s="11" t="s">
@@ -2393,8 +2396,8 @@
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A45" s="28"/>
-      <c r="B45" s="22"/>
+      <c r="A45" s="22"/>
+      <c r="B45" s="25"/>
       <c r="C45" s="10" t="s">
         <v>353</v>
       </c>
@@ -2409,8 +2412,8 @@
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A46" s="28"/>
-      <c r="B46" s="22"/>
+      <c r="A46" s="22"/>
+      <c r="B46" s="25"/>
       <c r="C46" s="10" t="s">
         <v>353</v>
       </c>
@@ -2425,8 +2428,8 @@
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A47" s="28"/>
-      <c r="B47" s="22"/>
+      <c r="A47" s="22"/>
+      <c r="B47" s="25"/>
       <c r="C47" s="10" t="s">
         <v>353</v>
       </c>
@@ -2441,8 +2444,8 @@
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A48" s="28"/>
-      <c r="B48" s="22"/>
+      <c r="A48" s="22"/>
+      <c r="B48" s="25"/>
       <c r="C48" s="10" t="s">
         <v>353</v>
       </c>
@@ -2457,8 +2460,8 @@
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A49" s="28"/>
-      <c r="B49" s="22"/>
+      <c r="A49" s="22"/>
+      <c r="B49" s="25"/>
       <c r="C49" s="10" t="s">
         <v>353</v>
       </c>
@@ -2473,8 +2476,8 @@
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A50" s="28"/>
-      <c r="B50" s="22"/>
+      <c r="A50" s="22"/>
+      <c r="B50" s="25"/>
       <c r="C50" s="10" t="s">
         <v>353</v>
       </c>
@@ -2489,8 +2492,8 @@
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A51" s="28"/>
-      <c r="B51" s="22"/>
+      <c r="A51" s="22"/>
+      <c r="B51" s="25"/>
       <c r="C51" s="10" t="s">
         <v>353</v>
       </c>
@@ -2505,8 +2508,8 @@
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A52" s="28"/>
-      <c r="B52" s="22"/>
+      <c r="A52" s="22"/>
+      <c r="B52" s="25"/>
       <c r="C52" s="10" t="s">
         <v>353</v>
       </c>
@@ -2521,8 +2524,8 @@
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A53" s="28"/>
-      <c r="B53" s="22"/>
+      <c r="A53" s="22"/>
+      <c r="B53" s="25"/>
       <c r="C53" s="10" t="s">
         <v>353</v>
       </c>
@@ -2537,8 +2540,8 @@
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A54" s="28"/>
-      <c r="B54" s="22"/>
+      <c r="A54" s="22"/>
+      <c r="B54" s="25"/>
       <c r="C54" s="10" t="s">
         <v>353</v>
       </c>
@@ -2553,16 +2556,16 @@
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A55" s="28"/>
-      <c r="B55" s="23"/>
+      <c r="A55" s="22"/>
+      <c r="B55" s="26"/>
       <c r="C55" s="12"/>
       <c r="D55" s="7"/>
       <c r="E55" s="7"/>
       <c r="F55" s="7"/>
     </row>
     <row r="56" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="28"/>
-      <c r="B56" s="24" t="s">
+      <c r="A56" s="22"/>
+      <c r="B56" s="28" t="s">
         <v>299</v>
       </c>
       <c r="C56" s="13" t="s">
@@ -2575,12 +2578,12 @@
         <v>300</v>
       </c>
       <c r="F56" s="6" t="s">
-        <v>27</v>
+        <v>399</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A57" s="28"/>
-      <c r="B57" s="25"/>
+      <c r="A57" s="22"/>
+      <c r="B57" s="29"/>
       <c r="C57" s="14" t="s">
         <v>354</v>
       </c>
@@ -2595,8 +2598,8 @@
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A58" s="28"/>
-      <c r="B58" s="25"/>
+      <c r="A58" s="22"/>
+      <c r="B58" s="29"/>
       <c r="C58" s="14" t="s">
         <v>354</v>
       </c>
@@ -2611,8 +2614,8 @@
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A59" s="28"/>
-      <c r="B59" s="25"/>
+      <c r="A59" s="22"/>
+      <c r="B59" s="29"/>
       <c r="C59" s="14" t="s">
         <v>354</v>
       </c>
@@ -2627,8 +2630,8 @@
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A60" s="28"/>
-      <c r="B60" s="25"/>
+      <c r="A60" s="22"/>
+      <c r="B60" s="29"/>
       <c r="C60" s="14" t="s">
         <v>354</v>
       </c>
@@ -2643,8 +2646,8 @@
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A61" s="28"/>
-      <c r="B61" s="25"/>
+      <c r="A61" s="22"/>
+      <c r="B61" s="29"/>
       <c r="C61" s="14" t="s">
         <v>354</v>
       </c>
@@ -2659,8 +2662,8 @@
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A62" s="28"/>
-      <c r="B62" s="25"/>
+      <c r="A62" s="22"/>
+      <c r="B62" s="29"/>
       <c r="C62" s="14" t="s">
         <v>354</v>
       </c>
@@ -2675,8 +2678,8 @@
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A63" s="28"/>
-      <c r="B63" s="25"/>
+      <c r="A63" s="22"/>
+      <c r="B63" s="29"/>
       <c r="C63" s="14" t="s">
         <v>354</v>
       </c>
@@ -2691,8 +2694,8 @@
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A64" s="28"/>
-      <c r="B64" s="25"/>
+      <c r="A64" s="22"/>
+      <c r="B64" s="29"/>
       <c r="C64" s="14" t="s">
         <v>354</v>
       </c>
@@ -2707,8 +2710,8 @@
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A65" s="28"/>
-      <c r="B65" s="25"/>
+      <c r="A65" s="22"/>
+      <c r="B65" s="29"/>
       <c r="C65" s="14" t="s">
         <v>354</v>
       </c>
@@ -2723,8 +2726,8 @@
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A66" s="28"/>
-      <c r="B66" s="25"/>
+      <c r="A66" s="22"/>
+      <c r="B66" s="29"/>
       <c r="C66" s="14" t="s">
         <v>354</v>
       </c>
@@ -2739,8 +2742,8 @@
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A67" s="28"/>
-      <c r="B67" s="25"/>
+      <c r="A67" s="22"/>
+      <c r="B67" s="29"/>
       <c r="C67" s="14" t="s">
         <v>354</v>
       </c>
@@ -2755,16 +2758,16 @@
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A68" s="28"/>
-      <c r="B68" s="26"/>
+      <c r="A68" s="22"/>
+      <c r="B68" s="32"/>
       <c r="C68" s="15"/>
       <c r="D68" s="7"/>
       <c r="E68" s="7"/>
       <c r="F68" s="7"/>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A69" s="28"/>
-      <c r="B69" s="21" t="s">
+      <c r="A69" s="22"/>
+      <c r="B69" s="24" t="s">
         <v>185</v>
       </c>
       <c r="C69" s="10" t="s">
@@ -2781,8 +2784,8 @@
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A70" s="28"/>
-      <c r="B70" s="22"/>
+      <c r="A70" s="22"/>
+      <c r="B70" s="25"/>
       <c r="C70" s="10" t="s">
         <v>355</v>
       </c>
@@ -2797,8 +2800,8 @@
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A71" s="28"/>
-      <c r="B71" s="22"/>
+      <c r="A71" s="22"/>
+      <c r="B71" s="25"/>
       <c r="C71" s="10" t="s">
         <v>355</v>
       </c>
@@ -2813,8 +2816,8 @@
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A72" s="28"/>
-      <c r="B72" s="22"/>
+      <c r="A72" s="22"/>
+      <c r="B72" s="25"/>
       <c r="C72" s="10" t="s">
         <v>355</v>
       </c>
@@ -2829,8 +2832,8 @@
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A73" s="28"/>
-      <c r="B73" s="22"/>
+      <c r="A73" s="22"/>
+      <c r="B73" s="25"/>
       <c r="C73" s="10" t="s">
         <v>355</v>
       </c>
@@ -2845,8 +2848,8 @@
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A74" s="28"/>
-      <c r="B74" s="22"/>
+      <c r="A74" s="22"/>
+      <c r="B74" s="25"/>
       <c r="C74" s="10" t="s">
         <v>355</v>
       </c>
@@ -2861,8 +2864,8 @@
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A75" s="28"/>
-      <c r="B75" s="22"/>
+      <c r="A75" s="22"/>
+      <c r="B75" s="25"/>
       <c r="C75" s="10" t="s">
         <v>355</v>
       </c>
@@ -2877,8 +2880,8 @@
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A76" s="28"/>
-      <c r="B76" s="22"/>
+      <c r="A76" s="22"/>
+      <c r="B76" s="25"/>
       <c r="C76" s="10" t="s">
         <v>355</v>
       </c>
@@ -2893,8 +2896,8 @@
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A77" s="28"/>
-      <c r="B77" s="22"/>
+      <c r="A77" s="22"/>
+      <c r="B77" s="25"/>
       <c r="C77" s="10" t="s">
         <v>355</v>
       </c>
@@ -2909,16 +2912,16 @@
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A78" s="28"/>
-      <c r="B78" s="23"/>
+      <c r="A78" s="22"/>
+      <c r="B78" s="26"/>
       <c r="C78" s="12"/>
       <c r="D78" s="7"/>
       <c r="E78" s="7"/>
       <c r="F78" s="7"/>
     </row>
     <row r="79" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A79" s="28"/>
-      <c r="B79" s="24" t="s">
+      <c r="A79" s="22"/>
+      <c r="B79" s="28" t="s">
         <v>149</v>
       </c>
       <c r="C79" s="13" t="s">
@@ -2935,8 +2938,8 @@
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A80" s="28"/>
-      <c r="B80" s="25"/>
+      <c r="A80" s="22"/>
+      <c r="B80" s="29"/>
       <c r="C80" s="14" t="s">
         <v>356</v>
       </c>
@@ -2951,8 +2954,8 @@
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A81" s="28"/>
-      <c r="B81" s="25"/>
+      <c r="A81" s="22"/>
+      <c r="B81" s="29"/>
       <c r="C81" s="14" t="s">
         <v>356</v>
       </c>
@@ -2967,8 +2970,8 @@
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A82" s="28"/>
-      <c r="B82" s="25"/>
+      <c r="A82" s="22"/>
+      <c r="B82" s="29"/>
       <c r="C82" s="14" t="s">
         <v>356</v>
       </c>
@@ -2983,8 +2986,8 @@
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A83" s="28"/>
-      <c r="B83" s="25"/>
+      <c r="A83" s="22"/>
+      <c r="B83" s="29"/>
       <c r="C83" s="14" t="s">
         <v>356</v>
       </c>
@@ -2999,8 +3002,8 @@
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A84" s="28"/>
-      <c r="B84" s="25"/>
+      <c r="A84" s="22"/>
+      <c r="B84" s="29"/>
       <c r="C84" s="14" t="s">
         <v>356</v>
       </c>
@@ -3015,8 +3018,8 @@
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A85" s="28"/>
-      <c r="B85" s="25"/>
+      <c r="A85" s="22"/>
+      <c r="B85" s="29"/>
       <c r="C85" s="14" t="s">
         <v>356</v>
       </c>
@@ -3031,8 +3034,8 @@
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A86" s="28"/>
-      <c r="B86" s="25"/>
+      <c r="A86" s="22"/>
+      <c r="B86" s="29"/>
       <c r="C86" s="14" t="s">
         <v>356</v>
       </c>
@@ -3047,8 +3050,8 @@
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A87" s="28"/>
-      <c r="B87" s="25"/>
+      <c r="A87" s="22"/>
+      <c r="B87" s="29"/>
       <c r="C87" s="14" t="s">
         <v>356</v>
       </c>
@@ -3063,8 +3066,8 @@
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A88" s="28"/>
-      <c r="B88" s="25"/>
+      <c r="A88" s="22"/>
+      <c r="B88" s="29"/>
       <c r="C88" s="14" t="s">
         <v>356</v>
       </c>
@@ -3079,16 +3082,16 @@
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A89" s="28"/>
-      <c r="B89" s="26"/>
+      <c r="A89" s="22"/>
+      <c r="B89" s="32"/>
       <c r="C89" s="15"/>
       <c r="D89" s="7"/>
       <c r="E89" s="7"/>
       <c r="F89" s="7"/>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A90" s="28"/>
-      <c r="B90" s="22" t="s">
+      <c r="A90" s="22"/>
+      <c r="B90" s="25" t="s">
         <v>374</v>
       </c>
       <c r="C90" s="14" t="s">
@@ -3105,8 +3108,8 @@
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A91" s="28"/>
-      <c r="B91" s="22"/>
+      <c r="A91" s="22"/>
+      <c r="B91" s="25"/>
       <c r="C91" s="14" t="s">
         <v>385</v>
       </c>
@@ -3121,8 +3124,8 @@
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A92" s="28"/>
-      <c r="B92" s="22"/>
+      <c r="A92" s="22"/>
+      <c r="B92" s="25"/>
       <c r="C92" s="14" t="s">
         <v>385</v>
       </c>
@@ -3137,8 +3140,8 @@
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A93" s="28"/>
-      <c r="B93" s="22"/>
+      <c r="A93" s="22"/>
+      <c r="B93" s="25"/>
       <c r="C93" s="14" t="s">
         <v>385</v>
       </c>
@@ -3153,8 +3156,8 @@
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A94" s="28"/>
-      <c r="B94" s="22"/>
+      <c r="A94" s="22"/>
+      <c r="B94" s="25"/>
       <c r="C94" s="14" t="s">
         <v>385</v>
       </c>
@@ -3169,8 +3172,8 @@
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A95" s="28"/>
-      <c r="B95" s="22"/>
+      <c r="A95" s="22"/>
+      <c r="B95" s="25"/>
       <c r="C95" s="14" t="s">
         <v>385</v>
       </c>
@@ -3185,8 +3188,8 @@
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A96" s="28"/>
-      <c r="B96" s="22"/>
+      <c r="A96" s="22"/>
+      <c r="B96" s="25"/>
       <c r="C96" s="14" t="s">
         <v>385</v>
       </c>
@@ -3201,8 +3204,8 @@
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A97" s="28"/>
-      <c r="B97" s="22"/>
+      <c r="A97" s="22"/>
+      <c r="B97" s="25"/>
       <c r="C97" s="14" t="s">
         <v>385</v>
       </c>
@@ -3217,8 +3220,8 @@
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A98" s="28"/>
-      <c r="B98" s="22"/>
+      <c r="A98" s="22"/>
+      <c r="B98" s="25"/>
       <c r="C98" s="14" t="s">
         <v>385</v>
       </c>
@@ -3233,8 +3236,8 @@
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A99" s="28"/>
-      <c r="B99" s="22"/>
+      <c r="A99" s="22"/>
+      <c r="B99" s="25"/>
       <c r="C99" s="14" t="s">
         <v>385</v>
       </c>
@@ -3249,15 +3252,15 @@
       </c>
     </row>
     <row r="100" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A100" s="29"/>
+      <c r="A100" s="23"/>
       <c r="B100" s="19"/>
       <c r="C100" s="14"/>
     </row>
     <row r="101" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A101" s="27" t="s">
+      <c r="A101" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="B101" s="32" t="s">
+      <c r="B101" s="31" t="s">
         <v>3</v>
       </c>
       <c r="C101" s="16" t="s">
@@ -3274,8 +3277,8 @@
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A102" s="28"/>
-      <c r="B102" s="25"/>
+      <c r="A102" s="22"/>
+      <c r="B102" s="29"/>
       <c r="C102" s="14" t="s">
         <v>357</v>
       </c>
@@ -3290,8 +3293,8 @@
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A103" s="28"/>
-      <c r="B103" s="25"/>
+      <c r="A103" s="22"/>
+      <c r="B103" s="29"/>
       <c r="C103" s="14" t="s">
         <v>357</v>
       </c>
@@ -3306,8 +3309,8 @@
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A104" s="28"/>
-      <c r="B104" s="25"/>
+      <c r="A104" s="22"/>
+      <c r="B104" s="29"/>
       <c r="C104" s="14" t="s">
         <v>357</v>
       </c>
@@ -3322,8 +3325,8 @@
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A105" s="28"/>
-      <c r="B105" s="25"/>
+      <c r="A105" s="22"/>
+      <c r="B105" s="29"/>
       <c r="C105" s="14" t="s">
         <v>357</v>
       </c>
@@ -3338,8 +3341,8 @@
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A106" s="28"/>
-      <c r="B106" s="25"/>
+      <c r="A106" s="22"/>
+      <c r="B106" s="29"/>
       <c r="C106" s="14" t="s">
         <v>357</v>
       </c>
@@ -3354,8 +3357,8 @@
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A107" s="28"/>
-      <c r="B107" s="25"/>
+      <c r="A107" s="22"/>
+      <c r="B107" s="29"/>
       <c r="C107" s="14" t="s">
         <v>357</v>
       </c>
@@ -3370,8 +3373,8 @@
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A108" s="28"/>
-      <c r="B108" s="25"/>
+      <c r="A108" s="22"/>
+      <c r="B108" s="29"/>
       <c r="C108" s="14" t="s">
         <v>357</v>
       </c>
@@ -3386,8 +3389,8 @@
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A109" s="28"/>
-      <c r="B109" s="25"/>
+      <c r="A109" s="22"/>
+      <c r="B109" s="29"/>
       <c r="C109" s="14" t="s">
         <v>357</v>
       </c>
@@ -3402,16 +3405,16 @@
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A110" s="28"/>
-      <c r="B110" s="26"/>
+      <c r="A110" s="22"/>
+      <c r="B110" s="32"/>
       <c r="C110" s="15"/>
       <c r="D110" s="7"/>
       <c r="E110" s="7"/>
       <c r="F110" s="7"/>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A111" s="28"/>
-      <c r="B111" s="24" t="s">
+      <c r="A111" s="22"/>
+      <c r="B111" s="28" t="s">
         <v>216</v>
       </c>
       <c r="C111" s="14" t="s">
@@ -3428,8 +3431,8 @@
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A112" s="28"/>
-      <c r="B112" s="25"/>
+      <c r="A112" s="22"/>
+      <c r="B112" s="29"/>
       <c r="C112" s="14" t="s">
         <v>358</v>
       </c>
@@ -3444,8 +3447,8 @@
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A113" s="28"/>
-      <c r="B113" s="25"/>
+      <c r="A113" s="22"/>
+      <c r="B113" s="29"/>
       <c r="C113" s="14" t="s">
         <v>358</v>
       </c>
@@ -3460,8 +3463,8 @@
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A114" s="28"/>
-      <c r="B114" s="25"/>
+      <c r="A114" s="22"/>
+      <c r="B114" s="29"/>
       <c r="C114" s="14" t="s">
         <v>358</v>
       </c>
@@ -3476,8 +3479,8 @@
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A115" s="28"/>
-      <c r="B115" s="25"/>
+      <c r="A115" s="22"/>
+      <c r="B115" s="29"/>
       <c r="C115" s="14" t="s">
         <v>358</v>
       </c>
@@ -3492,8 +3495,8 @@
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A116" s="28"/>
-      <c r="B116" s="25"/>
+      <c r="A116" s="22"/>
+      <c r="B116" s="29"/>
       <c r="C116" s="14" t="s">
         <v>358</v>
       </c>
@@ -3508,8 +3511,8 @@
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A117" s="28"/>
-      <c r="B117" s="25"/>
+      <c r="A117" s="22"/>
+      <c r="B117" s="29"/>
       <c r="C117" s="14" t="s">
         <v>358</v>
       </c>
@@ -3524,8 +3527,8 @@
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A118" s="28"/>
-      <c r="B118" s="25"/>
+      <c r="A118" s="22"/>
+      <c r="B118" s="29"/>
       <c r="C118" s="14" t="s">
         <v>358</v>
       </c>
@@ -3540,8 +3543,8 @@
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A119" s="28"/>
-      <c r="B119" s="25"/>
+      <c r="A119" s="22"/>
+      <c r="B119" s="29"/>
       <c r="C119" s="14" t="s">
         <v>358</v>
       </c>
@@ -3556,13 +3559,13 @@
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A120" s="28"/>
-      <c r="B120" s="26"/>
+      <c r="A120" s="22"/>
+      <c r="B120" s="32"/>
       <c r="C120" s="14"/>
     </row>
     <row r="121" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A121" s="28"/>
-      <c r="B121" s="24" t="s">
+      <c r="A121" s="22"/>
+      <c r="B121" s="28" t="s">
         <v>6</v>
       </c>
       <c r="C121" s="13" t="s">
@@ -3579,8 +3582,8 @@
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A122" s="28"/>
-      <c r="B122" s="25"/>
+      <c r="A122" s="22"/>
+      <c r="B122" s="29"/>
       <c r="C122" s="14" t="s">
         <v>359</v>
       </c>
@@ -3595,8 +3598,8 @@
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A123" s="28"/>
-      <c r="B123" s="25"/>
+      <c r="A123" s="22"/>
+      <c r="B123" s="29"/>
       <c r="C123" s="14" t="s">
         <v>359</v>
       </c>
@@ -3611,8 +3614,8 @@
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A124" s="28"/>
-      <c r="B124" s="25"/>
+      <c r="A124" s="22"/>
+      <c r="B124" s="29"/>
       <c r="C124" s="14" t="s">
         <v>359</v>
       </c>
@@ -3627,8 +3630,8 @@
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A125" s="28"/>
-      <c r="B125" s="25"/>
+      <c r="A125" s="22"/>
+      <c r="B125" s="29"/>
       <c r="C125" s="14" t="s">
         <v>359</v>
       </c>
@@ -3643,8 +3646,8 @@
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A126" s="28"/>
-      <c r="B126" s="25"/>
+      <c r="A126" s="22"/>
+      <c r="B126" s="29"/>
       <c r="C126" s="14" t="s">
         <v>359</v>
       </c>
@@ -3659,8 +3662,8 @@
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A127" s="28"/>
-      <c r="B127" s="25"/>
+      <c r="A127" s="22"/>
+      <c r="B127" s="29"/>
       <c r="C127" s="14" t="s">
         <v>359</v>
       </c>
@@ -3675,8 +3678,8 @@
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A128" s="28"/>
-      <c r="B128" s="25"/>
+      <c r="A128" s="22"/>
+      <c r="B128" s="29"/>
       <c r="C128" s="14" t="s">
         <v>359</v>
       </c>
@@ -3691,8 +3694,8 @@
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A129" s="28"/>
-      <c r="B129" s="25"/>
+      <c r="A129" s="22"/>
+      <c r="B129" s="29"/>
       <c r="C129" s="14" t="s">
         <v>359</v>
       </c>
@@ -3707,8 +3710,8 @@
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A130" s="28"/>
-      <c r="B130" s="25"/>
+      <c r="A130" s="22"/>
+      <c r="B130" s="29"/>
       <c r="C130" s="14" t="s">
         <v>359</v>
       </c>
@@ -3723,8 +3726,8 @@
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A131" s="28"/>
-      <c r="B131" s="25"/>
+      <c r="A131" s="22"/>
+      <c r="B131" s="29"/>
       <c r="C131" s="14" t="s">
         <v>359</v>
       </c>
@@ -3739,18 +3742,18 @@
       </c>
     </row>
     <row r="132" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A132" s="29"/>
-      <c r="B132" s="31"/>
+      <c r="A132" s="23"/>
+      <c r="B132" s="30"/>
       <c r="C132" s="17"/>
       <c r="D132" s="8"/>
       <c r="E132" s="8"/>
       <c r="F132" s="8"/>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A133" s="27" t="s">
+      <c r="A133" s="21" t="s">
         <v>14</v>
       </c>
-      <c r="B133" s="30" t="s">
+      <c r="B133" s="27" t="s">
         <v>15</v>
       </c>
       <c r="C133" s="9" t="s">
@@ -3767,8 +3770,8 @@
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A134" s="28"/>
-      <c r="B134" s="22"/>
+      <c r="A134" s="22"/>
+      <c r="B134" s="25"/>
       <c r="C134" s="10" t="s">
         <v>360</v>
       </c>
@@ -3783,16 +3786,16 @@
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A135" s="28"/>
-      <c r="B135" s="23"/>
+      <c r="A135" s="22"/>
+      <c r="B135" s="26"/>
       <c r="C135" s="12"/>
       <c r="D135" s="7"/>
       <c r="E135" s="7"/>
       <c r="F135" s="7"/>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A136" s="28"/>
-      <c r="B136" s="21" t="s">
+      <c r="A136" s="22"/>
+      <c r="B136" s="24" t="s">
         <v>269</v>
       </c>
       <c r="C136" s="10" t="s">
@@ -3809,8 +3812,8 @@
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A137" s="28"/>
-      <c r="B137" s="22"/>
+      <c r="A137" s="22"/>
+      <c r="B137" s="25"/>
       <c r="C137" s="10" t="s">
         <v>361</v>
       </c>
@@ -3825,16 +3828,16 @@
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A138" s="28"/>
-      <c r="B138" s="23"/>
+      <c r="A138" s="22"/>
+      <c r="B138" s="26"/>
       <c r="C138" s="12"/>
       <c r="D138" s="7"/>
       <c r="E138" s="7"/>
       <c r="F138" s="7"/>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A139" s="28"/>
-      <c r="B139" s="21" t="s">
+      <c r="A139" s="22"/>
+      <c r="B139" s="24" t="s">
         <v>314</v>
       </c>
       <c r="C139" s="11" t="s">
@@ -3851,8 +3854,8 @@
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A140" s="28"/>
-      <c r="B140" s="22"/>
+      <c r="A140" s="22"/>
+      <c r="B140" s="25"/>
       <c r="C140" s="10" t="s">
         <v>362</v>
       </c>
@@ -3867,16 +3870,16 @@
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A141" s="28"/>
-      <c r="B141" s="23"/>
+      <c r="A141" s="22"/>
+      <c r="B141" s="26"/>
       <c r="C141" s="12"/>
       <c r="D141" s="7"/>
       <c r="E141" s="7"/>
       <c r="F141" s="7"/>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A142" s="28"/>
-      <c r="B142" s="21" t="s">
+      <c r="A142" s="22"/>
+      <c r="B142" s="24" t="s">
         <v>319</v>
       </c>
       <c r="C142" s="10" t="s">
@@ -3893,8 +3896,8 @@
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A143" s="28"/>
-      <c r="B143" s="22"/>
+      <c r="A143" s="22"/>
+      <c r="B143" s="25"/>
       <c r="C143" s="10" t="s">
         <v>363</v>
       </c>
@@ -3909,13 +3912,13 @@
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A144" s="28"/>
-      <c r="B144" s="23"/>
+      <c r="A144" s="22"/>
+      <c r="B144" s="26"/>
       <c r="C144" s="10"/>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A145" s="28"/>
-      <c r="B145" s="24" t="s">
+      <c r="A145" s="22"/>
+      <c r="B145" s="28" t="s">
         <v>4</v>
       </c>
       <c r="C145" s="13" t="s">
@@ -3932,8 +3935,8 @@
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A146" s="28"/>
-      <c r="B146" s="25"/>
+      <c r="A146" s="22"/>
+      <c r="B146" s="29"/>
       <c r="C146" s="14" t="s">
         <v>4</v>
       </c>
@@ -3948,8 +3951,8 @@
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A147" s="28"/>
-      <c r="B147" s="25"/>
+      <c r="A147" s="22"/>
+      <c r="B147" s="29"/>
       <c r="C147" s="14" t="s">
         <v>4</v>
       </c>
@@ -3964,8 +3967,8 @@
       </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A148" s="28"/>
-      <c r="B148" s="25"/>
+      <c r="A148" s="22"/>
+      <c r="B148" s="29"/>
       <c r="C148" s="14" t="s">
         <v>4</v>
       </c>
@@ -3980,8 +3983,8 @@
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A149" s="28"/>
-      <c r="B149" s="25"/>
+      <c r="A149" s="22"/>
+      <c r="B149" s="29"/>
       <c r="C149" s="14" t="s">
         <v>4</v>
       </c>
@@ -3996,8 +3999,8 @@
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A150" s="28"/>
-      <c r="B150" s="25"/>
+      <c r="A150" s="22"/>
+      <c r="B150" s="29"/>
       <c r="C150" s="14" t="s">
         <v>4</v>
       </c>
@@ -4012,8 +4015,8 @@
       </c>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A151" s="28"/>
-      <c r="B151" s="25"/>
+      <c r="A151" s="22"/>
+      <c r="B151" s="29"/>
       <c r="C151" s="14" t="s">
         <v>4</v>
       </c>
@@ -4028,8 +4031,8 @@
       </c>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A152" s="28"/>
-      <c r="B152" s="25"/>
+      <c r="A152" s="22"/>
+      <c r="B152" s="29"/>
       <c r="C152" s="14" t="s">
         <v>4</v>
       </c>
@@ -4044,8 +4047,8 @@
       </c>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A153" s="28"/>
-      <c r="B153" s="25"/>
+      <c r="A153" s="22"/>
+      <c r="B153" s="29"/>
       <c r="C153" s="14" t="s">
         <v>4</v>
       </c>
@@ -4060,13 +4063,13 @@
       </c>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A154" s="28"/>
-      <c r="B154" s="26"/>
+      <c r="A154" s="22"/>
+      <c r="B154" s="32"/>
       <c r="C154" s="14"/>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A155" s="28"/>
-      <c r="B155" s="24" t="s">
+      <c r="A155" s="22"/>
+      <c r="B155" s="28" t="s">
         <v>5</v>
       </c>
       <c r="C155" s="13" t="s">
@@ -4083,8 +4086,8 @@
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A156" s="28"/>
-      <c r="B156" s="25"/>
+      <c r="A156" s="22"/>
+      <c r="B156" s="29"/>
       <c r="C156" s="14" t="s">
         <v>364</v>
       </c>
@@ -4099,8 +4102,8 @@
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A157" s="28"/>
-      <c r="B157" s="25"/>
+      <c r="A157" s="22"/>
+      <c r="B157" s="29"/>
       <c r="C157" s="14" t="s">
         <v>364</v>
       </c>
@@ -4115,8 +4118,8 @@
       </c>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A158" s="28"/>
-      <c r="B158" s="25"/>
+      <c r="A158" s="22"/>
+      <c r="B158" s="29"/>
       <c r="C158" s="14" t="s">
         <v>364</v>
       </c>
@@ -4131,8 +4134,8 @@
       </c>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A159" s="28"/>
-      <c r="B159" s="25"/>
+      <c r="A159" s="22"/>
+      <c r="B159" s="29"/>
       <c r="C159" s="14" t="s">
         <v>364</v>
       </c>
@@ -4147,8 +4150,8 @@
       </c>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A160" s="28"/>
-      <c r="B160" s="25"/>
+      <c r="A160" s="22"/>
+      <c r="B160" s="29"/>
       <c r="C160" s="14" t="s">
         <v>364</v>
       </c>
@@ -4163,8 +4166,8 @@
       </c>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A161" s="28"/>
-      <c r="B161" s="25"/>
+      <c r="A161" s="22"/>
+      <c r="B161" s="29"/>
       <c r="C161" s="14" t="s">
         <v>364</v>
       </c>
@@ -4179,8 +4182,8 @@
       </c>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A162" s="28"/>
-      <c r="B162" s="25"/>
+      <c r="A162" s="22"/>
+      <c r="B162" s="29"/>
       <c r="C162" s="14" t="s">
         <v>364</v>
       </c>
@@ -4195,8 +4198,8 @@
       </c>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A163" s="28"/>
-      <c r="B163" s="25"/>
+      <c r="A163" s="22"/>
+      <c r="B163" s="29"/>
       <c r="C163" s="14" t="s">
         <v>364</v>
       </c>
@@ -4211,15 +4214,15 @@
       </c>
     </row>
     <row r="164" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A164" s="29"/>
-      <c r="B164" s="31"/>
+      <c r="A164" s="23"/>
+      <c r="B164" s="30"/>
       <c r="C164" s="14"/>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A165" s="27" t="s">
+      <c r="A165" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="B165" s="30" t="s">
+      <c r="B165" s="27" t="s">
         <v>15</v>
       </c>
       <c r="C165" s="9" t="s">
@@ -4236,8 +4239,8 @@
       </c>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A166" s="28"/>
-      <c r="B166" s="22"/>
+      <c r="A166" s="22"/>
+      <c r="B166" s="25"/>
       <c r="C166" s="10" t="s">
         <v>360</v>
       </c>
@@ -4252,8 +4255,8 @@
       </c>
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A167" s="28"/>
-      <c r="B167" s="22"/>
+      <c r="A167" s="22"/>
+      <c r="B167" s="25"/>
       <c r="C167" s="10" t="s">
         <v>360</v>
       </c>
@@ -4268,16 +4271,16 @@
       </c>
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A168" s="28"/>
-      <c r="B168" s="23"/>
+      <c r="A168" s="22"/>
+      <c r="B168" s="26"/>
       <c r="C168" s="12"/>
       <c r="D168" s="7"/>
       <c r="E168" s="7"/>
       <c r="F168" s="7"/>
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A169" s="28"/>
-      <c r="B169" s="21" t="s">
+      <c r="A169" s="22"/>
+      <c r="B169" s="24" t="s">
         <v>202</v>
       </c>
       <c r="C169" s="10" t="s">
@@ -4294,8 +4297,8 @@
       </c>
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A170" s="28"/>
-      <c r="B170" s="22"/>
+      <c r="A170" s="22"/>
+      <c r="B170" s="25"/>
       <c r="C170" s="10" t="s">
         <v>365</v>
       </c>
@@ -4310,8 +4313,8 @@
       </c>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A171" s="28"/>
-      <c r="B171" s="22"/>
+      <c r="A171" s="22"/>
+      <c r="B171" s="25"/>
       <c r="C171" s="10" t="s">
         <v>365</v>
       </c>
@@ -4326,13 +4329,13 @@
       </c>
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A172" s="28"/>
-      <c r="B172" s="23"/>
+      <c r="A172" s="22"/>
+      <c r="B172" s="26"/>
       <c r="C172" s="10"/>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A173" s="28"/>
-      <c r="B173" s="21" t="s">
+      <c r="A173" s="22"/>
+      <c r="B173" s="24" t="s">
         <v>17</v>
       </c>
       <c r="C173" s="11" t="s">
@@ -4349,8 +4352,8 @@
       </c>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A174" s="28"/>
-      <c r="B174" s="22"/>
+      <c r="A174" s="22"/>
+      <c r="B174" s="25"/>
       <c r="C174" s="10" t="s">
         <v>362</v>
       </c>
@@ -4365,16 +4368,16 @@
       </c>
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A175" s="28"/>
-      <c r="B175" s="23"/>
+      <c r="A175" s="22"/>
+      <c r="B175" s="26"/>
       <c r="C175" s="12"/>
       <c r="D175" s="7"/>
       <c r="E175" s="7"/>
       <c r="F175" s="7"/>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A176" s="28"/>
-      <c r="B176" s="21" t="s">
+      <c r="A176" s="22"/>
+      <c r="B176" s="24" t="s">
         <v>174</v>
       </c>
       <c r="C176" s="11" t="s">
@@ -4391,8 +4394,8 @@
       </c>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A177" s="28"/>
-      <c r="B177" s="22"/>
+      <c r="A177" s="22"/>
+      <c r="B177" s="25"/>
       <c r="C177" s="10" t="s">
         <v>366</v>
       </c>
@@ -4407,16 +4410,16 @@
       </c>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A178" s="28"/>
-      <c r="B178" s="23"/>
+      <c r="A178" s="22"/>
+      <c r="B178" s="26"/>
       <c r="C178" s="12"/>
       <c r="D178" s="7"/>
       <c r="E178" s="7"/>
       <c r="F178" s="7"/>
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A179" s="28"/>
-      <c r="B179" s="21" t="s">
+      <c r="A179" s="22"/>
+      <c r="B179" s="24" t="s">
         <v>270</v>
       </c>
       <c r="C179" s="10" t="s">
@@ -4433,8 +4436,8 @@
       </c>
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A180" s="28"/>
-      <c r="B180" s="22"/>
+      <c r="A180" s="22"/>
+      <c r="B180" s="25"/>
       <c r="C180" s="10" t="s">
         <v>367</v>
       </c>
@@ -4449,16 +4452,16 @@
       </c>
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A181" s="28"/>
-      <c r="B181" s="23"/>
+      <c r="A181" s="22"/>
+      <c r="B181" s="26"/>
       <c r="C181" s="12"/>
       <c r="D181" s="7"/>
       <c r="E181" s="7"/>
       <c r="F181" s="7"/>
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A182" s="28"/>
-      <c r="B182" s="21" t="s">
+      <c r="A182" s="22"/>
+      <c r="B182" s="24" t="s">
         <v>325</v>
       </c>
       <c r="C182" s="11" t="s">
@@ -4475,8 +4478,8 @@
       </c>
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A183" s="28"/>
-      <c r="B183" s="22"/>
+      <c r="A183" s="22"/>
+      <c r="B183" s="25"/>
       <c r="C183" s="10" t="s">
         <v>368</v>
       </c>
@@ -4491,16 +4494,16 @@
       </c>
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A184" s="28"/>
-      <c r="B184" s="23"/>
+      <c r="A184" s="22"/>
+      <c r="B184" s="26"/>
       <c r="C184" s="12"/>
       <c r="D184" s="7"/>
       <c r="E184" s="7"/>
       <c r="F184" s="7"/>
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A185" s="28"/>
-      <c r="B185" s="21" t="s">
+      <c r="A185" s="22"/>
+      <c r="B185" s="24" t="s">
         <v>330</v>
       </c>
       <c r="C185" s="11" t="s">
@@ -4517,8 +4520,8 @@
       </c>
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A186" s="28"/>
-      <c r="B186" s="22"/>
+      <c r="A186" s="22"/>
+      <c r="B186" s="25"/>
       <c r="C186" s="10" t="s">
         <v>369</v>
       </c>
@@ -4533,16 +4536,16 @@
       </c>
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A187" s="28"/>
-      <c r="B187" s="23"/>
+      <c r="A187" s="22"/>
+      <c r="B187" s="26"/>
       <c r="C187" s="12"/>
       <c r="D187" s="7"/>
       <c r="E187" s="7"/>
       <c r="F187" s="7"/>
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A188" s="28"/>
-      <c r="B188" s="22" t="s">
+      <c r="A188" s="22"/>
+      <c r="B188" s="25" t="s">
         <v>390</v>
       </c>
       <c r="C188" s="10" t="s">
@@ -4559,8 +4562,8 @@
       </c>
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A189" s="28"/>
-      <c r="B189" s="22"/>
+      <c r="A189" s="22"/>
+      <c r="B189" s="25"/>
       <c r="C189" s="10" t="s">
         <v>395</v>
       </c>
@@ -4575,7 +4578,7 @@
       </c>
     </row>
     <row r="190" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A190" s="29"/>
+      <c r="A190" s="23"/>
       <c r="B190" s="20"/>
       <c r="C190" s="18"/>
       <c r="D190" s="8"/>
@@ -4583,10 +4586,10 @@
       <c r="F190" s="8"/>
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A191" s="27" t="s">
+      <c r="A191" s="21" t="s">
         <v>85</v>
       </c>
-      <c r="B191" s="30" t="s">
+      <c r="B191" s="27" t="s">
         <v>7</v>
       </c>
       <c r="C191" s="9" t="s">
@@ -4603,8 +4606,8 @@
       </c>
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A192" s="28"/>
-      <c r="B192" s="22"/>
+      <c r="A192" s="22"/>
+      <c r="B192" s="25"/>
       <c r="C192" s="10" t="s">
         <v>370</v>
       </c>
@@ -4619,16 +4622,16 @@
       </c>
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A193" s="28"/>
-      <c r="B193" s="23"/>
+      <c r="A193" s="22"/>
+      <c r="B193" s="26"/>
       <c r="C193" s="12"/>
       <c r="D193" s="7"/>
       <c r="E193" s="7"/>
       <c r="F193" s="7"/>
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A194" s="28"/>
-      <c r="B194" s="21" t="s">
+      <c r="A194" s="22"/>
+      <c r="B194" s="24" t="s">
         <v>105</v>
       </c>
       <c r="C194" s="10" t="s">
@@ -4645,8 +4648,8 @@
       </c>
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A195" s="28"/>
-      <c r="B195" s="22"/>
+      <c r="A195" s="22"/>
+      <c r="B195" s="25"/>
       <c r="C195" s="10" t="s">
         <v>370</v>
       </c>
@@ -4661,8 +4664,8 @@
       </c>
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A196" s="28"/>
-      <c r="B196" s="22"/>
+      <c r="A196" s="22"/>
+      <c r="B196" s="25"/>
       <c r="C196" s="10" t="s">
         <v>370</v>
       </c>
@@ -4677,8 +4680,8 @@
       </c>
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A197" s="28"/>
-      <c r="B197" s="22"/>
+      <c r="A197" s="22"/>
+      <c r="B197" s="25"/>
       <c r="C197" s="10" t="s">
         <v>370</v>
       </c>
@@ -4693,8 +4696,8 @@
       </c>
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A198" s="28"/>
-      <c r="B198" s="22"/>
+      <c r="A198" s="22"/>
+      <c r="B198" s="25"/>
       <c r="C198" s="10" t="s">
         <v>370</v>
       </c>
@@ -4709,8 +4712,8 @@
       </c>
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A199" s="28"/>
-      <c r="B199" s="22"/>
+      <c r="A199" s="22"/>
+      <c r="B199" s="25"/>
       <c r="C199" s="10" t="s">
         <v>370</v>
       </c>
@@ -4725,13 +4728,13 @@
       </c>
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A200" s="28"/>
-      <c r="B200" s="23"/>
+      <c r="A200" s="22"/>
+      <c r="B200" s="26"/>
       <c r="C200" s="10"/>
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A201" s="28"/>
-      <c r="B201" s="21" t="s">
+      <c r="A201" s="22"/>
+      <c r="B201" s="24" t="s">
         <v>126</v>
       </c>
       <c r="C201" s="11" t="s">
@@ -4748,8 +4751,8 @@
       </c>
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A202" s="28"/>
-      <c r="B202" s="22"/>
+      <c r="A202" s="22"/>
+      <c r="B202" s="25"/>
       <c r="C202" s="10" t="s">
         <v>371</v>
       </c>
@@ -4764,8 +4767,8 @@
       </c>
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A203" s="28"/>
-      <c r="B203" s="22"/>
+      <c r="A203" s="22"/>
+      <c r="B203" s="25"/>
       <c r="C203" s="10" t="s">
         <v>371</v>
       </c>
@@ -4780,8 +4783,8 @@
       </c>
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A204" s="28"/>
-      <c r="B204" s="22"/>
+      <c r="A204" s="22"/>
+      <c r="B204" s="25"/>
       <c r="C204" s="10" t="s">
         <v>371</v>
       </c>
@@ -4796,8 +4799,8 @@
       </c>
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A205" s="28"/>
-      <c r="B205" s="22"/>
+      <c r="A205" s="22"/>
+      <c r="B205" s="25"/>
       <c r="C205" s="10" t="s">
         <v>371</v>
       </c>
@@ -4812,8 +4815,8 @@
       </c>
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A206" s="28"/>
-      <c r="B206" s="22"/>
+      <c r="A206" s="22"/>
+      <c r="B206" s="25"/>
       <c r="C206" s="10" t="s">
         <v>371</v>
       </c>
@@ -4828,8 +4831,8 @@
       </c>
     </row>
     <row r="207" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A207" s="28"/>
-      <c r="B207" s="22"/>
+      <c r="A207" s="22"/>
+      <c r="B207" s="25"/>
       <c r="C207" s="10" t="s">
         <v>371</v>
       </c>
@@ -4844,8 +4847,8 @@
       </c>
     </row>
     <row r="208" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A208" s="28"/>
-      <c r="B208" s="22"/>
+      <c r="A208" s="22"/>
+      <c r="B208" s="25"/>
       <c r="C208" s="10" t="s">
         <v>371</v>
       </c>
@@ -4860,8 +4863,8 @@
       </c>
     </row>
     <row r="209" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A209" s="28"/>
-      <c r="B209" s="22"/>
+      <c r="A209" s="22"/>
+      <c r="B209" s="25"/>
       <c r="C209" s="10" t="s">
         <v>371</v>
       </c>
@@ -4876,8 +4879,8 @@
       </c>
     </row>
     <row r="210" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A210" s="28"/>
-      <c r="B210" s="22"/>
+      <c r="A210" s="22"/>
+      <c r="B210" s="25"/>
       <c r="C210" s="10" t="s">
         <v>371</v>
       </c>
@@ -4892,8 +4895,8 @@
       </c>
     </row>
     <row r="211" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A211" s="28"/>
-      <c r="B211" s="22"/>
+      <c r="A211" s="22"/>
+      <c r="B211" s="25"/>
       <c r="C211" s="10" t="s">
         <v>371</v>
       </c>
@@ -4908,8 +4911,8 @@
       </c>
     </row>
     <row r="212" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A212" s="28"/>
-      <c r="B212" s="22"/>
+      <c r="A212" s="22"/>
+      <c r="B212" s="25"/>
       <c r="C212" s="10" t="s">
         <v>371</v>
       </c>
@@ -4924,8 +4927,8 @@
       </c>
     </row>
     <row r="213" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A213" s="28"/>
-      <c r="B213" s="22"/>
+      <c r="A213" s="22"/>
+      <c r="B213" s="25"/>
       <c r="C213" s="10" t="s">
         <v>371</v>
       </c>
@@ -4940,8 +4943,8 @@
       </c>
     </row>
     <row r="214" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A214" s="28"/>
-      <c r="B214" s="22"/>
+      <c r="A214" s="22"/>
+      <c r="B214" s="25"/>
       <c r="C214" s="10" t="s">
         <v>371</v>
       </c>
@@ -4956,8 +4959,8 @@
       </c>
     </row>
     <row r="215" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A215" s="28"/>
-      <c r="B215" s="22"/>
+      <c r="A215" s="22"/>
+      <c r="B215" s="25"/>
       <c r="C215" s="10" t="s">
         <v>371</v>
       </c>
@@ -4972,8 +4975,8 @@
       </c>
     </row>
     <row r="216" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A216" s="28"/>
-      <c r="B216" s="22"/>
+      <c r="A216" s="22"/>
+      <c r="B216" s="25"/>
       <c r="C216" s="10" t="s">
         <v>371</v>
       </c>
@@ -4988,8 +4991,8 @@
       </c>
     </row>
     <row r="217" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A217" s="28"/>
-      <c r="B217" s="22"/>
+      <c r="A217" s="22"/>
+      <c r="B217" s="25"/>
       <c r="C217" s="10" t="s">
         <v>371</v>
       </c>
@@ -5004,8 +5007,8 @@
       </c>
     </row>
     <row r="218" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A218" s="28"/>
-      <c r="B218" s="22"/>
+      <c r="A218" s="22"/>
+      <c r="B218" s="25"/>
       <c r="C218" s="10" t="s">
         <v>371</v>
       </c>
@@ -5020,8 +5023,8 @@
       </c>
     </row>
     <row r="219" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A219" s="28"/>
-      <c r="B219" s="22"/>
+      <c r="A219" s="22"/>
+      <c r="B219" s="25"/>
       <c r="C219" s="10" t="s">
         <v>371</v>
       </c>
@@ -5036,8 +5039,8 @@
       </c>
     </row>
     <row r="220" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A220" s="28"/>
-      <c r="B220" s="22"/>
+      <c r="A220" s="22"/>
+      <c r="B220" s="25"/>
       <c r="C220" s="10" t="s">
         <v>371</v>
       </c>
@@ -5052,8 +5055,8 @@
       </c>
     </row>
     <row r="221" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A221" s="28"/>
-      <c r="B221" s="22"/>
+      <c r="A221" s="22"/>
+      <c r="B221" s="25"/>
       <c r="C221" s="10" t="s">
         <v>371</v>
       </c>
@@ -5068,13 +5071,13 @@
       </c>
     </row>
     <row r="222" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A222" s="28"/>
-      <c r="B222" s="23"/>
+      <c r="A222" s="22"/>
+      <c r="B222" s="26"/>
       <c r="C222" s="10"/>
     </row>
     <row r="223" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A223" s="28"/>
-      <c r="B223" s="21" t="s">
+      <c r="A223" s="22"/>
+      <c r="B223" s="24" t="s">
         <v>142</v>
       </c>
       <c r="C223" s="11" t="s">
@@ -5091,8 +5094,8 @@
       </c>
     </row>
     <row r="224" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A224" s="28"/>
-      <c r="B224" s="22"/>
+      <c r="A224" s="22"/>
+      <c r="B224" s="25"/>
       <c r="C224" s="10" t="s">
         <v>372</v>
       </c>
@@ -5107,8 +5110,8 @@
       </c>
     </row>
     <row r="225" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A225" s="28"/>
-      <c r="B225" s="22"/>
+      <c r="A225" s="22"/>
+      <c r="B225" s="25"/>
       <c r="C225" s="10" t="s">
         <v>372</v>
       </c>
@@ -5123,8 +5126,8 @@
       </c>
     </row>
     <row r="226" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A226" s="28"/>
-      <c r="B226" s="22"/>
+      <c r="A226" s="22"/>
+      <c r="B226" s="25"/>
       <c r="C226" s="10" t="s">
         <v>372</v>
       </c>
@@ -5139,8 +5142,8 @@
       </c>
     </row>
     <row r="227" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A227" s="28"/>
-      <c r="B227" s="22"/>
+      <c r="A227" s="22"/>
+      <c r="B227" s="25"/>
       <c r="C227" s="10" t="s">
         <v>372</v>
       </c>
@@ -5155,8 +5158,8 @@
       </c>
     </row>
     <row r="228" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A228" s="28"/>
-      <c r="B228" s="22"/>
+      <c r="A228" s="22"/>
+      <c r="B228" s="25"/>
       <c r="C228" s="10" t="s">
         <v>372</v>
       </c>
@@ -5171,8 +5174,8 @@
       </c>
     </row>
     <row r="229" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A229" s="28"/>
-      <c r="B229" s="22"/>
+      <c r="A229" s="22"/>
+      <c r="B229" s="25"/>
       <c r="C229" s="10" t="s">
         <v>372</v>
       </c>
@@ -5187,8 +5190,8 @@
       </c>
     </row>
     <row r="230" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A230" s="28"/>
-      <c r="B230" s="22"/>
+      <c r="A230" s="22"/>
+      <c r="B230" s="25"/>
       <c r="C230" s="10" t="s">
         <v>372</v>
       </c>
@@ -5203,8 +5206,8 @@
       </c>
     </row>
     <row r="231" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A231" s="28"/>
-      <c r="B231" s="22"/>
+      <c r="A231" s="22"/>
+      <c r="B231" s="25"/>
       <c r="C231" s="10" t="s">
         <v>372</v>
       </c>
@@ -5219,13 +5222,13 @@
       </c>
     </row>
     <row r="232" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A232" s="28"/>
-      <c r="B232" s="23"/>
+      <c r="A232" s="22"/>
+      <c r="B232" s="26"/>
       <c r="C232" s="10"/>
     </row>
     <row r="233" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A233" s="28"/>
-      <c r="B233" s="21" t="s">
+      <c r="A233" s="22"/>
+      <c r="B233" s="24" t="s">
         <v>232</v>
       </c>
       <c r="C233" s="11" t="s">
@@ -5242,8 +5245,8 @@
       </c>
     </row>
     <row r="234" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A234" s="28"/>
-      <c r="B234" s="22"/>
+      <c r="A234" s="22"/>
+      <c r="B234" s="25"/>
       <c r="C234" s="10" t="s">
         <v>373</v>
       </c>
@@ -5259,15 +5262,17 @@
     </row>
   </sheetData>
   <mergeCells count="36">
-    <mergeCell ref="A165:A190"/>
-    <mergeCell ref="B173:B175"/>
-    <mergeCell ref="B165:B168"/>
-    <mergeCell ref="B169:B172"/>
-    <mergeCell ref="B179:B181"/>
-    <mergeCell ref="B176:B178"/>
-    <mergeCell ref="B182:B184"/>
-    <mergeCell ref="B188:B189"/>
-    <mergeCell ref="B185:B187"/>
+    <mergeCell ref="B44:B55"/>
+    <mergeCell ref="B56:B68"/>
+    <mergeCell ref="B79:B89"/>
+    <mergeCell ref="B90:B99"/>
+    <mergeCell ref="B233:B234"/>
+    <mergeCell ref="B145:B154"/>
+    <mergeCell ref="B155:B164"/>
+    <mergeCell ref="B139:B141"/>
+    <mergeCell ref="B142:B144"/>
+    <mergeCell ref="B136:B138"/>
+    <mergeCell ref="B133:B135"/>
     <mergeCell ref="A191:A234"/>
     <mergeCell ref="A2:A100"/>
     <mergeCell ref="B2:B11"/>
@@ -5284,17 +5289,15 @@
     <mergeCell ref="B23:B33"/>
     <mergeCell ref="B34:B43"/>
     <mergeCell ref="A133:A164"/>
-    <mergeCell ref="B44:B55"/>
-    <mergeCell ref="B56:B68"/>
-    <mergeCell ref="B79:B89"/>
-    <mergeCell ref="B90:B99"/>
-    <mergeCell ref="B233:B234"/>
-    <mergeCell ref="B145:B154"/>
-    <mergeCell ref="B155:B164"/>
-    <mergeCell ref="B139:B141"/>
-    <mergeCell ref="B142:B144"/>
-    <mergeCell ref="B136:B138"/>
-    <mergeCell ref="B133:B135"/>
+    <mergeCell ref="A165:A190"/>
+    <mergeCell ref="B173:B175"/>
+    <mergeCell ref="B165:B168"/>
+    <mergeCell ref="B169:B172"/>
+    <mergeCell ref="B179:B181"/>
+    <mergeCell ref="B176:B178"/>
+    <mergeCell ref="B182:B184"/>
+    <mergeCell ref="B188:B189"/>
+    <mergeCell ref="B185:B187"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
